--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2907,6 +2907,3664 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127782139</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Näset, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>660662</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6642152</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127782239</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>660682</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6641961</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127782069</v>
+      </c>
+      <c r="B21" t="n">
+        <v>95770</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>660571</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6642126</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127782148</v>
+      </c>
+      <c r="B22" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>660674</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6642146</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127781902</v>
+      </c>
+      <c r="B23" t="n">
+        <v>105400</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Näsudden, Funbosjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>660601</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6641916</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127782049</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91309</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>252387</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Almrostöra</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hymenochaete ulmicola</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Corfixen &amp; Parmasto</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>660581</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6642052</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127782101</v>
+      </c>
+      <c r="B25" t="n">
+        <v>95770</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>660572</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6642152</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127781893</v>
+      </c>
+      <c r="B26" t="n">
+        <v>95770</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Näsudden, Funbosjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>660601</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6641916</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127781942</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92010</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1527</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Prakttagging</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Steccherinum robustius</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>660593</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6641939</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127782073</v>
+      </c>
+      <c r="B28" t="n">
+        <v>100632</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>660571</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6642126</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127781986</v>
+      </c>
+      <c r="B29" t="n">
+        <v>95770</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>660653</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6641997</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127781925</v>
+      </c>
+      <c r="B30" t="n">
+        <v>100539</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>660590</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6641920</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127782226</v>
+      </c>
+      <c r="B31" t="n">
+        <v>100539</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>660709</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6642092</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127782055</v>
+      </c>
+      <c r="B32" t="n">
+        <v>100539</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>660581</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6642052</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127782149</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>660677</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6642142</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127782095</v>
+      </c>
+      <c r="B34" t="n">
+        <v>95770</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>660568</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6642142</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127781996</v>
+      </c>
+      <c r="B35" t="n">
+        <v>95770</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>660644</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6642016</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127782137</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91628</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>658</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Näset, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>660662</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6642152</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127781949</v>
+      </c>
+      <c r="B37" t="n">
+        <v>103895</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>660593</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6641939</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127781945</v>
+      </c>
+      <c r="B38" t="n">
+        <v>100539</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>660593</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6641939</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127782086</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>660568</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6642132</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127782042</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>660581</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6642052</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127782135</v>
+      </c>
+      <c r="B41" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Näset, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>660662</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6642152</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127781882</v>
+      </c>
+      <c r="B42" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Näsudden, Funbosjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>660605</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6641899</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127781920</v>
+      </c>
+      <c r="B43" t="n">
+        <v>92097</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>366</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Artomyces pyxidatus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>660590</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6641920</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127781944</v>
+      </c>
+      <c r="B44" t="n">
+        <v>90936</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>3086</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Svartöra</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Auricularia mesenterica</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Dicks.:Fr.) Pers.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>660593</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6641939</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127781868</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57779</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>232224</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tjocknäbbad nötkråka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Nucifraga caryocatactes caryocatactes</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Näsudden, Funbosjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>660576</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6642193</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127781932</v>
+      </c>
+      <c r="B46" t="n">
+        <v>92010</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1527</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Prakttagging</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Steccherinum robustius</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>660580</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6641918</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127781984</v>
+      </c>
+      <c r="B47" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>660653</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6641997</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127782079</v>
+      </c>
+      <c r="B48" t="n">
+        <v>95770</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>660568</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6642132</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127782017</v>
+      </c>
+      <c r="B49" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>660620</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6642029</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127782232</v>
+      </c>
+      <c r="B50" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>660691</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6642071</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127782030</v>
+      </c>
+      <c r="B51" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>660611</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6642055</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127782136</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57821</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Näset, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>660662</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6642152</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -3219,10 +3219,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127782148</v>
+        <v>127781902</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>105400</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3230,43 +3230,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>221141</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>660674</v>
+        <v>660601</v>
       </c>
       <c r="R22" t="n">
-        <v>6642146</v>
+        <v>6641916</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3326,10 +3321,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127781902</v>
+        <v>127782148</v>
       </c>
       <c r="B23" t="n">
-        <v>105400</v>
+        <v>5177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3337,38 +3332,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221141</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>660601</v>
+        <v>660674</v>
       </c>
       <c r="R23" t="n">
-        <v>6641916</v>
+        <v>6642146</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3428,37 +3428,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127782049</v>
+        <v>127782101</v>
       </c>
       <c r="B24" t="n">
-        <v>91309</v>
+        <v>95770</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>252387</v>
+        <v>2671</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Almrostöra</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hymenochaete ulmicola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Corfixen &amp; Parmasto</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3466,10 +3467,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>660581</v>
+        <v>660572</v>
       </c>
       <c r="R24" t="n">
-        <v>6642052</v>
+        <v>6642152</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3513,21 +3514,6 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3544,38 +3530,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127782101</v>
+        <v>127782049</v>
       </c>
       <c r="B25" t="n">
-        <v>95770</v>
+        <v>91309</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2671</v>
+        <v>252387</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Almrostöra</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hymenochaete ulmicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Corfixen &amp; Parmasto</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3583,10 +3568,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>660572</v>
+        <v>660581</v>
       </c>
       <c r="R25" t="n">
-        <v>6642152</v>
+        <v>6642052</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3630,6 +3615,21 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3646,10 +3646,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127781893</v>
+        <v>127782073</v>
       </c>
       <c r="B26" t="n">
-        <v>95770</v>
+        <v>100632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3657,21 +3657,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3681,14 +3681,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>660601</v>
+        <v>660571</v>
       </c>
       <c r="R26" t="n">
-        <v>6641916</v>
+        <v>6642126</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3864,10 +3864,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127782073</v>
+        <v>127781893</v>
       </c>
       <c r="B28" t="n">
-        <v>100632</v>
+        <v>95770</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3875,21 +3875,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3899,14 +3899,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>660571</v>
+        <v>660601</v>
       </c>
       <c r="R28" t="n">
-        <v>6642126</v>
+        <v>6641916</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4577,52 +4577,59 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127781996</v>
+        <v>127782137</v>
       </c>
       <c r="B35" t="n">
-        <v>95770</v>
+        <v>91628</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2671</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näset, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>660644</v>
+        <v>660662</v>
       </c>
       <c r="R35" t="n">
-        <v>6642016</v>
+        <v>6642152</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4663,6 +4670,26 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4679,59 +4706,52 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127782137</v>
+        <v>127781996</v>
       </c>
       <c r="B36" t="n">
-        <v>91628</v>
+        <v>95770</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>2671</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Näset, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>660662</v>
+        <v>660644</v>
       </c>
       <c r="R36" t="n">
-        <v>6642152</v>
+        <v>6642016</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4772,26 +4792,6 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4808,38 +4808,46 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127781949</v>
+        <v>127782086</v>
       </c>
       <c r="B37" t="n">
-        <v>103895</v>
+        <v>57823</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222412</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4847,10 +4855,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>660593</v>
+        <v>660568</v>
       </c>
       <c r="R37" t="n">
-        <v>6641939</v>
+        <v>6642132</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4891,7 +4899,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5012,46 +5019,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127782086</v>
+        <v>127781949</v>
       </c>
       <c r="B39" t="n">
-        <v>57823</v>
+        <v>103895</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>222412</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5059,10 +5058,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>660568</v>
+        <v>660593</v>
       </c>
       <c r="R39" t="n">
-        <v>6642132</v>
+        <v>6641939</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5103,6 +5102,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5693,57 +5693,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127781868</v>
+        <v>127781932</v>
       </c>
       <c r="B45" t="n">
-        <v>57779</v>
+        <v>92010</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>232224</v>
+        <v>1527</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjocknäbbad nötkråka</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes caryocatactes</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>660576</v>
+        <v>660580</v>
       </c>
       <c r="R45" t="n">
-        <v>6642193</v>
+        <v>6641918</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5773,29 +5764,35 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5812,48 +5809,57 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127781932</v>
+        <v>127781868</v>
       </c>
       <c r="B46" t="n">
-        <v>92010</v>
+        <v>57779</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1527</v>
+        <v>232224</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Tjocknäbbad nötkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Nucifraga caryocatactes caryocatactes</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>660580</v>
+        <v>660576</v>
       </c>
       <c r="R46" t="n">
-        <v>6641918</v>
+        <v>6642193</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5883,35 +5889,29 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6137,10 +6137,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127782017</v>
+        <v>127782232</v>
       </c>
       <c r="B49" t="n">
-        <v>4779</v>
+        <v>8439</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,21 +6148,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102306</v>
+        <v>106554</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6181,10 +6181,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>660620</v>
+        <v>660691</v>
       </c>
       <c r="R49" t="n">
-        <v>6642029</v>
+        <v>6642071</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6244,10 +6244,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127782232</v>
+        <v>127782017</v>
       </c>
       <c r="B50" t="n">
-        <v>8439</v>
+        <v>4779</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6255,21 +6255,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106554</v>
+        <v>102306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6288,10 +6288,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>660691</v>
+        <v>660620</v>
       </c>
       <c r="R50" t="n">
-        <v>6642071</v>
+        <v>6642029</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6351,57 +6351,60 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127782030</v>
+        <v>127782136</v>
       </c>
       <c r="B51" t="n">
-        <v>8439</v>
+        <v>57821</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106554</v>
+        <v>103020</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näset, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>660611</v>
+        <v>660662</v>
       </c>
       <c r="R51" t="n">
-        <v>6642055</v>
+        <v>6642152</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6439,7 +6442,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6458,60 +6460,57 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127782136</v>
+        <v>127782030</v>
       </c>
       <c r="B52" t="n">
-        <v>57821</v>
+        <v>8439</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103020</v>
+        <v>106554</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Näset, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>660662</v>
+        <v>660611</v>
       </c>
       <c r="R52" t="n">
-        <v>6642152</v>
+        <v>6642055</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6549,6 +6548,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -2912,7 +2912,7 @@
         <v>127782139</v>
       </c>
       <c r="B19" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>127782069</v>
       </c>
       <c r="B21" t="n">
-        <v>95770</v>
+        <v>95776</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>127781902</v>
       </c>
       <c r="B22" t="n">
-        <v>105400</v>
+        <v>105406</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>127782101</v>
       </c>
       <c r="B24" t="n">
-        <v>95770</v>
+        <v>95776</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>127782049</v>
       </c>
       <c r="B25" t="n">
-        <v>91309</v>
+        <v>91315</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,38 +3646,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127782073</v>
+        <v>127781942</v>
       </c>
       <c r="B26" t="n">
-        <v>100632</v>
+        <v>92016</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>1527</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3685,10 +3684,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>660571</v>
+        <v>660593</v>
       </c>
       <c r="R26" t="n">
-        <v>6642126</v>
+        <v>6641939</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3732,6 +3731,21 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3748,48 +3762,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127781942</v>
+        <v>127781893</v>
       </c>
       <c r="B27" t="n">
-        <v>92010</v>
+        <v>95776</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1527</v>
+        <v>2671</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>660593</v>
+        <v>660601</v>
       </c>
       <c r="R27" t="n">
-        <v>6641939</v>
+        <v>6641916</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3833,21 +3848,6 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3864,10 +3864,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127781893</v>
+        <v>127781986</v>
       </c>
       <c r="B28" t="n">
-        <v>95770</v>
+        <v>95776</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3899,14 +3899,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>660601</v>
+        <v>660653</v>
       </c>
       <c r="R28" t="n">
-        <v>6641916</v>
+        <v>6641997</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127781986</v>
+        <v>127782073</v>
       </c>
       <c r="B29" t="n">
-        <v>95770</v>
+        <v>100638</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3977,21 +3977,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>660653</v>
+        <v>660571</v>
       </c>
       <c r="R29" t="n">
-        <v>6641997</v>
+        <v>6642126</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4071,7 +4071,7 @@
         <v>127781925</v>
       </c>
       <c r="B30" t="n">
-        <v>100539</v>
+        <v>100545</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4170,10 +4170,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127782226</v>
+        <v>127782055</v>
       </c>
       <c r="B31" t="n">
-        <v>100539</v>
+        <v>100545</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>660709</v>
+        <v>660581</v>
       </c>
       <c r="R31" t="n">
-        <v>6642092</v>
+        <v>6642052</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4272,10 +4272,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127782055</v>
+        <v>127782226</v>
       </c>
       <c r="B32" t="n">
-        <v>100539</v>
+        <v>100545</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>660581</v>
+        <v>660709</v>
       </c>
       <c r="R32" t="n">
-        <v>6642052</v>
+        <v>6642092</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4377,7 +4377,7 @@
         <v>127782149</v>
       </c>
       <c r="B33" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>127782095</v>
       </c>
       <c r="B34" t="n">
-        <v>95770</v>
+        <v>95776</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>127782137</v>
       </c>
       <c r="B35" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>127781996</v>
       </c>
       <c r="B36" t="n">
-        <v>95770</v>
+        <v>95776</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4808,46 +4808,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127782086</v>
+        <v>127781949</v>
       </c>
       <c r="B37" t="n">
-        <v>57823</v>
+        <v>103901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>222412</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4855,10 +4847,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>660568</v>
+        <v>660593</v>
       </c>
       <c r="R37" t="n">
-        <v>6642132</v>
+        <v>6641939</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4899,6 +4891,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4920,7 +4913,7 @@
         <v>127781945</v>
       </c>
       <c r="B38" t="n">
-        <v>100539</v>
+        <v>100545</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5019,38 +5012,46 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127781949</v>
+        <v>127782086</v>
       </c>
       <c r="B39" t="n">
-        <v>103895</v>
+        <v>57823</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222412</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5058,10 +5059,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>660593</v>
+        <v>660568</v>
       </c>
       <c r="R39" t="n">
-        <v>6641939</v>
+        <v>6642132</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5102,7 +5103,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5121,51 +5121,57 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127782042</v>
+        <v>127782135</v>
       </c>
       <c r="B40" t="n">
-        <v>91332</v>
+        <v>5177</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näset, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>660581</v>
+        <v>660662</v>
       </c>
       <c r="R40" t="n">
-        <v>6642052</v>
+        <v>6642152</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5217,9 +5223,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5237,10 +5248,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127782135</v>
+        <v>127781882</v>
       </c>
       <c r="B41" t="n">
-        <v>5177</v>
+        <v>8439</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5248,21 +5259,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5277,17 +5288,17 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Näset, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>660662</v>
+        <v>660605</v>
       </c>
       <c r="R41" t="n">
-        <v>6642152</v>
+        <v>6641899</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5328,26 +5339,6 @@
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5364,54 +5355,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127781882</v>
+        <v>127782042</v>
       </c>
       <c r="B42" t="n">
-        <v>8439</v>
+        <v>91338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>660605</v>
+        <v>660581</v>
       </c>
       <c r="R42" t="n">
-        <v>6641899</v>
+        <v>6642052</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5455,6 +5440,21 @@
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5474,7 +5474,7 @@
         <v>127781920</v>
       </c>
       <c r="B43" t="n">
-        <v>92097</v>
+        <v>92103</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>127781944</v>
       </c>
       <c r="B44" t="n">
-        <v>90936</v>
+        <v>90942</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>127781932</v>
       </c>
       <c r="B45" t="n">
-        <v>92010</v>
+        <v>92016</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>127782079</v>
       </c>
       <c r="B48" t="n">
-        <v>95770</v>
+        <v>95776</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6351,60 +6351,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127782136</v>
+        <v>127782030</v>
       </c>
       <c r="B51" t="n">
-        <v>57821</v>
+        <v>8439</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103020</v>
+        <v>106554</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Näset, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>660662</v>
+        <v>660611</v>
       </c>
       <c r="R51" t="n">
-        <v>6642152</v>
+        <v>6642055</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6442,6 +6439,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6460,57 +6458,60 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127782030</v>
+        <v>127782136</v>
       </c>
       <c r="B52" t="n">
-        <v>8439</v>
+        <v>57821</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106554</v>
+        <v>103020</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näset, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>660611</v>
+        <v>660662</v>
       </c>
       <c r="R52" t="n">
-        <v>6642055</v>
+        <v>6642152</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6548,7 +6549,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -2912,7 +2912,7 @@
         <v>127782139</v>
       </c>
       <c r="B19" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>127782069</v>
       </c>
       <c r="B21" t="n">
-        <v>95776</v>
+        <v>95779</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127781902</v>
+        <v>127782148</v>
       </c>
       <c r="B22" t="n">
-        <v>105406</v>
+        <v>5177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3230,38 +3230,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221141</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>660601</v>
+        <v>660674</v>
       </c>
       <c r="R22" t="n">
-        <v>6641916</v>
+        <v>6642146</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3321,10 +3326,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127782148</v>
+        <v>127781902</v>
       </c>
       <c r="B23" t="n">
-        <v>5177</v>
+        <v>105409</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3332,43 +3337,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>221141</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>660674</v>
+        <v>660601</v>
       </c>
       <c r="R23" t="n">
-        <v>6642146</v>
+        <v>6641916</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3431,7 +3431,7 @@
         <v>127782101</v>
       </c>
       <c r="B24" t="n">
-        <v>95776</v>
+        <v>95779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>127782049</v>
       </c>
       <c r="B25" t="n">
-        <v>91315</v>
+        <v>91318</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>127781942</v>
       </c>
       <c r="B26" t="n">
-        <v>92016</v>
+        <v>92019</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>127781893</v>
       </c>
       <c r="B27" t="n">
-        <v>95776</v>
+        <v>95779</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>127781986</v>
       </c>
       <c r="B28" t="n">
-        <v>95776</v>
+        <v>95779</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>127782073</v>
       </c>
       <c r="B29" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>127781925</v>
       </c>
       <c r="B30" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4170,10 +4170,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127782055</v>
+        <v>127782226</v>
       </c>
       <c r="B31" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>660581</v>
+        <v>660709</v>
       </c>
       <c r="R31" t="n">
-        <v>6642052</v>
+        <v>6642092</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4272,10 +4272,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127782226</v>
+        <v>127782055</v>
       </c>
       <c r="B32" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>660709</v>
+        <v>660581</v>
       </c>
       <c r="R32" t="n">
-        <v>6642092</v>
+        <v>6642052</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4377,7 +4377,7 @@
         <v>127782149</v>
       </c>
       <c r="B33" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>127782095</v>
       </c>
       <c r="B34" t="n">
-        <v>95776</v>
+        <v>95779</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4577,59 +4577,52 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127782137</v>
+        <v>127781996</v>
       </c>
       <c r="B35" t="n">
-        <v>91634</v>
+        <v>95779</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>2671</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Näset, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>660662</v>
+        <v>660644</v>
       </c>
       <c r="R35" t="n">
-        <v>6642152</v>
+        <v>6642016</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4670,26 +4663,6 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4706,52 +4679,59 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127781996</v>
+        <v>127782137</v>
       </c>
       <c r="B36" t="n">
-        <v>95776</v>
+        <v>91637</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2671</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näset, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>660644</v>
+        <v>660662</v>
       </c>
       <c r="R36" t="n">
-        <v>6642016</v>
+        <v>6642152</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4792,6 +4772,26 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4808,38 +4808,46 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127781949</v>
+        <v>127782086</v>
       </c>
       <c r="B37" t="n">
-        <v>103901</v>
+        <v>57826</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222412</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4847,10 +4855,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>660593</v>
+        <v>660568</v>
       </c>
       <c r="R37" t="n">
-        <v>6641939</v>
+        <v>6642132</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4891,7 +4899,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4910,10 +4917,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127781945</v>
+        <v>127781949</v>
       </c>
       <c r="B38" t="n">
-        <v>100545</v>
+        <v>103904</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4921,16 +4928,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5012,46 +5019,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127782086</v>
+        <v>127781945</v>
       </c>
       <c r="B39" t="n">
-        <v>57823</v>
+        <v>100548</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>222771</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5059,10 +5058,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>660568</v>
+        <v>660593</v>
       </c>
       <c r="R39" t="n">
-        <v>6642132</v>
+        <v>6641939</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5103,6 +5102,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5358,7 +5358,7 @@
         <v>127782042</v>
       </c>
       <c r="B42" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>127781920</v>
       </c>
       <c r="B43" t="n">
-        <v>92103</v>
+        <v>92106</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>127781944</v>
       </c>
       <c r="B44" t="n">
-        <v>90942</v>
+        <v>90945</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>127781932</v>
       </c>
       <c r="B45" t="n">
-        <v>92016</v>
+        <v>92019</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>127781868</v>
       </c>
       <c r="B46" t="n">
-        <v>57779</v>
+        <v>57782</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5928,10 +5928,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127781984</v>
+        <v>127782079</v>
       </c>
       <c r="B47" t="n">
-        <v>4779</v>
+        <v>95779</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5939,32 +5939,27 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102306</v>
+        <v>2671</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5972,10 +5967,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>660653</v>
+        <v>660568</v>
       </c>
       <c r="R47" t="n">
-        <v>6641997</v>
+        <v>6642132</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6035,10 +6030,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127782079</v>
+        <v>127781984</v>
       </c>
       <c r="B48" t="n">
-        <v>95776</v>
+        <v>4779</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6046,27 +6041,32 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2671</v>
+        <v>102306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>660568</v>
+        <v>660653</v>
       </c>
       <c r="R48" t="n">
-        <v>6642132</v>
+        <v>6641997</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6137,10 +6137,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127782232</v>
+        <v>127782017</v>
       </c>
       <c r="B49" t="n">
-        <v>8439</v>
+        <v>4779</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,21 +6148,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106554</v>
+        <v>102306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6181,10 +6181,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>660691</v>
+        <v>660620</v>
       </c>
       <c r="R49" t="n">
-        <v>6642071</v>
+        <v>6642029</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6244,10 +6244,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127782017</v>
+        <v>127782232</v>
       </c>
       <c r="B50" t="n">
-        <v>4779</v>
+        <v>8439</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6255,21 +6255,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102306</v>
+        <v>106554</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6288,10 +6288,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>660620</v>
+        <v>660691</v>
       </c>
       <c r="R50" t="n">
-        <v>6642029</v>
+        <v>6642071</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6351,57 +6351,60 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127782030</v>
+        <v>127782136</v>
       </c>
       <c r="B51" t="n">
-        <v>8439</v>
+        <v>57824</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106554</v>
+        <v>103020</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näset, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>660611</v>
+        <v>660662</v>
       </c>
       <c r="R51" t="n">
-        <v>6642055</v>
+        <v>6642152</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6439,7 +6442,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6458,60 +6460,57 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127782136</v>
+        <v>127782030</v>
       </c>
       <c r="B52" t="n">
-        <v>57821</v>
+        <v>8439</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103020</v>
+        <v>106554</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Näset, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>660662</v>
+        <v>660611</v>
       </c>
       <c r="R52" t="n">
-        <v>6642152</v>
+        <v>6642055</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6549,6 +6548,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -2912,7 +2912,7 @@
         <v>127782139</v>
       </c>
       <c r="B19" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>127782069</v>
       </c>
       <c r="B21" t="n">
-        <v>95779</v>
+        <v>95787</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>127781902</v>
       </c>
       <c r="B23" t="n">
-        <v>105409</v>
+        <v>105417</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3428,38 +3428,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127782101</v>
+        <v>127782049</v>
       </c>
       <c r="B24" t="n">
-        <v>95779</v>
+        <v>91326</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2671</v>
+        <v>252387</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Almrostöra</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hymenochaete ulmicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Corfixen &amp; Parmasto</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3467,10 +3466,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>660572</v>
+        <v>660581</v>
       </c>
       <c r="R24" t="n">
-        <v>6642152</v>
+        <v>6642052</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3514,6 +3513,21 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3530,37 +3544,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127782049</v>
+        <v>127782101</v>
       </c>
       <c r="B25" t="n">
-        <v>91318</v>
+        <v>95787</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>252387</v>
+        <v>2671</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Almrostöra</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hymenochaete ulmicola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Corfixen &amp; Parmasto</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3568,10 +3583,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>660581</v>
+        <v>660572</v>
       </c>
       <c r="R25" t="n">
-        <v>6642052</v>
+        <v>6642152</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3615,21 +3630,6 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3646,48 +3646,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127781942</v>
+        <v>127781893</v>
       </c>
       <c r="B26" t="n">
-        <v>92019</v>
+        <v>95787</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1527</v>
+        <v>2671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>660593</v>
+        <v>660601</v>
       </c>
       <c r="R26" t="n">
-        <v>6641939</v>
+        <v>6641916</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3731,21 +3732,6 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3762,10 +3748,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127781893</v>
+        <v>127781986</v>
       </c>
       <c r="B27" t="n">
-        <v>95779</v>
+        <v>95787</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3797,14 +3783,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>660601</v>
+        <v>660653</v>
       </c>
       <c r="R27" t="n">
-        <v>6641916</v>
+        <v>6641997</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3864,38 +3850,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127781986</v>
+        <v>127781942</v>
       </c>
       <c r="B28" t="n">
-        <v>95779</v>
+        <v>92027</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2671</v>
+        <v>1527</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3903,10 +3888,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>660653</v>
+        <v>660593</v>
       </c>
       <c r="R28" t="n">
-        <v>6641997</v>
+        <v>6641939</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3950,6 +3935,21 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3969,7 +3969,7 @@
         <v>127782073</v>
       </c>
       <c r="B29" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>127781925</v>
       </c>
       <c r="B30" t="n">
-        <v>100548</v>
+        <v>100556</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>127782226</v>
       </c>
       <c r="B31" t="n">
-        <v>100548</v>
+        <v>100556</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>127782055</v>
       </c>
       <c r="B32" t="n">
-        <v>100548</v>
+        <v>100556</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4374,37 +4374,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127782149</v>
+        <v>127782095</v>
       </c>
       <c r="B33" t="n">
-        <v>91341</v>
+        <v>95787</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>2671</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4412,7 +4413,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>660677</v>
+        <v>660568</v>
       </c>
       <c r="R33" t="n">
         <v>6642142</v>
@@ -4475,38 +4476,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127782095</v>
+        <v>127782149</v>
       </c>
       <c r="B34" t="n">
-        <v>95779</v>
+        <v>91349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2671</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>660568</v>
+        <v>660677</v>
       </c>
       <c r="R34" t="n">
         <v>6642142</v>
@@ -4577,52 +4577,59 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127781996</v>
+        <v>127782137</v>
       </c>
       <c r="B35" t="n">
-        <v>95779</v>
+        <v>91645</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2671</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näset, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>660644</v>
+        <v>660662</v>
       </c>
       <c r="R35" t="n">
-        <v>6642016</v>
+        <v>6642152</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4663,6 +4670,26 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4679,59 +4706,52 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127782137</v>
+        <v>127781996</v>
       </c>
       <c r="B36" t="n">
-        <v>91637</v>
+        <v>95787</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>2671</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Näset, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>660662</v>
+        <v>660644</v>
       </c>
       <c r="R36" t="n">
-        <v>6642152</v>
+        <v>6642016</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4772,26 +4792,6 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4811,7 +4811,7 @@
         <v>127782086</v>
       </c>
       <c r="B37" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>127781949</v>
       </c>
       <c r="B38" t="n">
-        <v>103904</v>
+        <v>103912</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>127781945</v>
       </c>
       <c r="B39" t="n">
-        <v>100548</v>
+        <v>100556</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5121,57 +5121,51 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127782135</v>
+        <v>127782042</v>
       </c>
       <c r="B40" t="n">
-        <v>5177</v>
+        <v>91349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Näset, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>660662</v>
+        <v>660581</v>
       </c>
       <c r="R40" t="n">
-        <v>6642152</v>
+        <v>6642052</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5223,14 +5217,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5248,10 +5237,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127781882</v>
+        <v>127782135</v>
       </c>
       <c r="B41" t="n">
-        <v>8439</v>
+        <v>5177</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5259,21 +5248,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5288,17 +5277,17 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näset, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>660605</v>
+        <v>660662</v>
       </c>
       <c r="R41" t="n">
-        <v>6641899</v>
+        <v>6642152</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5339,6 +5328,26 @@
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5355,48 +5364,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127782042</v>
+        <v>127781882</v>
       </c>
       <c r="B42" t="n">
-        <v>91341</v>
+        <v>8439</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>660581</v>
+        <v>660605</v>
       </c>
       <c r="R42" t="n">
-        <v>6642052</v>
+        <v>6641899</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5440,21 +5455,6 @@
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5474,7 +5474,7 @@
         <v>127781920</v>
       </c>
       <c r="B43" t="n">
-        <v>92106</v>
+        <v>92114</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>127781944</v>
       </c>
       <c r="B44" t="n">
-        <v>90945</v>
+        <v>90953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>127781932</v>
       </c>
       <c r="B45" t="n">
-        <v>92019</v>
+        <v>92027</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>127781868</v>
       </c>
       <c r="B46" t="n">
-        <v>57782</v>
+        <v>57788</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>127782079</v>
       </c>
       <c r="B47" t="n">
-        <v>95779</v>
+        <v>95787</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6351,60 +6351,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127782136</v>
+        <v>127782030</v>
       </c>
       <c r="B51" t="n">
-        <v>57824</v>
+        <v>8439</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103020</v>
+        <v>106554</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Näset, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>660662</v>
+        <v>660611</v>
       </c>
       <c r="R51" t="n">
-        <v>6642152</v>
+        <v>6642055</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6442,6 +6439,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6460,57 +6458,60 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127782030</v>
+        <v>127782136</v>
       </c>
       <c r="B52" t="n">
-        <v>8439</v>
+        <v>57830</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106554</v>
+        <v>103020</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näset, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>660611</v>
+        <v>660662</v>
       </c>
       <c r="R52" t="n">
-        <v>6642055</v>
+        <v>6642152</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6548,7 +6549,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -2912,7 +2912,7 @@
         <v>127782139</v>
       </c>
       <c r="B19" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>127782069</v>
       </c>
       <c r="B21" t="n">
-        <v>95787</v>
+        <v>95788</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>127781902</v>
       </c>
       <c r="B23" t="n">
-        <v>105417</v>
+        <v>105418</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>127782049</v>
       </c>
       <c r="B24" t="n">
-        <v>91326</v>
+        <v>91327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>127782101</v>
       </c>
       <c r="B25" t="n">
-        <v>95787</v>
+        <v>95788</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,49 +3646,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127781893</v>
+        <v>127781942</v>
       </c>
       <c r="B26" t="n">
-        <v>95787</v>
+        <v>92028</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2671</v>
+        <v>1527</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>660601</v>
+        <v>660593</v>
       </c>
       <c r="R26" t="n">
-        <v>6641916</v>
+        <v>6641939</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3732,6 +3731,21 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3748,10 +3762,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127781986</v>
+        <v>127781893</v>
       </c>
       <c r="B27" t="n">
-        <v>95787</v>
+        <v>95788</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3783,14 +3797,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>660653</v>
+        <v>660601</v>
       </c>
       <c r="R27" t="n">
-        <v>6641997</v>
+        <v>6641916</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3850,37 +3864,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127781942</v>
+        <v>127781986</v>
       </c>
       <c r="B28" t="n">
-        <v>92027</v>
+        <v>95788</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1527</v>
+        <v>2671</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3888,10 +3903,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>660593</v>
+        <v>660653</v>
       </c>
       <c r="R28" t="n">
-        <v>6641939</v>
+        <v>6641997</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3935,21 +3950,6 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3969,7 +3969,7 @@
         <v>127782073</v>
       </c>
       <c r="B29" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>127781925</v>
       </c>
       <c r="B30" t="n">
-        <v>100556</v>
+        <v>100557</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>127782226</v>
       </c>
       <c r="B31" t="n">
-        <v>100556</v>
+        <v>100557</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>127782055</v>
       </c>
       <c r="B32" t="n">
-        <v>100556</v>
+        <v>100557</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4374,38 +4374,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127782095</v>
+        <v>127782149</v>
       </c>
       <c r="B33" t="n">
-        <v>95787</v>
+        <v>91350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2671</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4413,7 +4412,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>660568</v>
+        <v>660677</v>
       </c>
       <c r="R33" t="n">
         <v>6642142</v>
@@ -4476,37 +4475,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127782149</v>
+        <v>127782095</v>
       </c>
       <c r="B34" t="n">
-        <v>91349</v>
+        <v>95788</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>2671</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>660677</v>
+        <v>660568</v>
       </c>
       <c r="R34" t="n">
         <v>6642142</v>
@@ -4577,59 +4577,52 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127782137</v>
+        <v>127781996</v>
       </c>
       <c r="B35" t="n">
-        <v>91645</v>
+        <v>95788</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>2671</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Näset, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>660662</v>
+        <v>660644</v>
       </c>
       <c r="R35" t="n">
-        <v>6642152</v>
+        <v>6642016</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4670,26 +4663,6 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4706,52 +4679,59 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127781996</v>
+        <v>127782137</v>
       </c>
       <c r="B36" t="n">
-        <v>95787</v>
+        <v>91646</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2671</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näset, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>660644</v>
+        <v>660662</v>
       </c>
       <c r="R36" t="n">
-        <v>6642016</v>
+        <v>6642152</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4792,6 +4772,26 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4920,7 +4920,7 @@
         <v>127781949</v>
       </c>
       <c r="B38" t="n">
-        <v>103912</v>
+        <v>103913</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>127781945</v>
       </c>
       <c r="B39" t="n">
-        <v>100556</v>
+        <v>100557</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>127782042</v>
       </c>
       <c r="B40" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>127781920</v>
       </c>
       <c r="B43" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>127781944</v>
       </c>
       <c r="B44" t="n">
-        <v>90953</v>
+        <v>90954</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5693,48 +5693,57 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127781932</v>
+        <v>127781868</v>
       </c>
       <c r="B45" t="n">
-        <v>92027</v>
+        <v>57788</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1527</v>
+        <v>232224</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Tjocknäbbad nötkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Nucifraga caryocatactes caryocatactes</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>660580</v>
+        <v>660576</v>
       </c>
       <c r="R45" t="n">
-        <v>6641918</v>
+        <v>6642193</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5764,35 +5773,29 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5809,57 +5812,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127781868</v>
+        <v>127781932</v>
       </c>
       <c r="B46" t="n">
-        <v>57788</v>
+        <v>92028</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>232224</v>
+        <v>1527</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjocknäbbad nötkråka</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes caryocatactes</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>660576</v>
+        <v>660580</v>
       </c>
       <c r="R46" t="n">
-        <v>6642193</v>
+        <v>6641918</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5889,29 +5883,35 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5931,7 +5931,7 @@
         <v>127782079</v>
       </c>
       <c r="B47" t="n">
-        <v>95787</v>
+        <v>95788</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6137,10 +6137,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127782017</v>
+        <v>127782232</v>
       </c>
       <c r="B49" t="n">
-        <v>4779</v>
+        <v>8439</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,21 +6148,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102306</v>
+        <v>106554</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6181,10 +6181,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>660620</v>
+        <v>660691</v>
       </c>
       <c r="R49" t="n">
-        <v>6642029</v>
+        <v>6642071</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6244,10 +6244,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127782232</v>
+        <v>127782017</v>
       </c>
       <c r="B50" t="n">
-        <v>8439</v>
+        <v>4779</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6255,21 +6255,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106554</v>
+        <v>102306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6288,10 +6288,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>660691</v>
+        <v>660620</v>
       </c>
       <c r="R50" t="n">
-        <v>6642071</v>
+        <v>6642029</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6351,57 +6351,60 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127782030</v>
+        <v>127782136</v>
       </c>
       <c r="B51" t="n">
-        <v>8439</v>
+        <v>57830</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106554</v>
+        <v>103020</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näset, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>660611</v>
+        <v>660662</v>
       </c>
       <c r="R51" t="n">
-        <v>6642055</v>
+        <v>6642152</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6439,7 +6442,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6458,60 +6460,57 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127782136</v>
+        <v>127782030</v>
       </c>
       <c r="B52" t="n">
-        <v>57830</v>
+        <v>8439</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103020</v>
+        <v>106554</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Näset, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>660662</v>
+        <v>660611</v>
       </c>
       <c r="R52" t="n">
-        <v>6642152</v>
+        <v>6642055</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6549,6 +6548,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -3219,10 +3219,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127782148</v>
+        <v>127781902</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>105418</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3230,43 +3230,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>221141</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>660674</v>
+        <v>660601</v>
       </c>
       <c r="R22" t="n">
-        <v>6642146</v>
+        <v>6641916</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3326,10 +3321,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127781902</v>
+        <v>127782148</v>
       </c>
       <c r="B23" t="n">
-        <v>105418</v>
+        <v>5177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3337,38 +3332,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221141</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>660601</v>
+        <v>660674</v>
       </c>
       <c r="R23" t="n">
-        <v>6641916</v>
+        <v>6642146</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3428,37 +3428,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127782049</v>
+        <v>127782101</v>
       </c>
       <c r="B24" t="n">
-        <v>91327</v>
+        <v>95788</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>252387</v>
+        <v>2671</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Almrostöra</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hymenochaete ulmicola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Corfixen &amp; Parmasto</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3466,10 +3467,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>660581</v>
+        <v>660572</v>
       </c>
       <c r="R24" t="n">
-        <v>6642052</v>
+        <v>6642152</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3513,21 +3514,6 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3544,38 +3530,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127782101</v>
+        <v>127782049</v>
       </c>
       <c r="B25" t="n">
-        <v>95788</v>
+        <v>91327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2671</v>
+        <v>252387</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Almrostöra</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hymenochaete ulmicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Corfixen &amp; Parmasto</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3583,10 +3568,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>660572</v>
+        <v>660581</v>
       </c>
       <c r="R25" t="n">
-        <v>6642152</v>
+        <v>6642052</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3630,6 +3615,21 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -5471,10 +5471,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127781920</v>
+        <v>127781944</v>
       </c>
       <c r="B43" t="n">
-        <v>92115</v>
+        <v>90954</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5482,21 +5482,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>366</v>
+        <v>3086</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Auricularia mesenterica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Dicks.:Fr.) Pers.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>660590</v>
+        <v>660593</v>
       </c>
       <c r="R43" t="n">
-        <v>6641920</v>
+        <v>6641939</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5556,26 +5556,6 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Populus tremula</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5592,10 +5572,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127781944</v>
+        <v>127781920</v>
       </c>
       <c r="B44" t="n">
-        <v>90954</v>
+        <v>92115</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5603,21 +5583,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3086</v>
+        <v>366</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Auricularia mesenterica</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.:Fr.) Pers.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5630,10 +5610,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>660593</v>
+        <v>660590</v>
       </c>
       <c r="R44" t="n">
-        <v>6641939</v>
+        <v>6641920</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5677,6 +5657,26 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5693,57 +5693,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127781868</v>
+        <v>127781932</v>
       </c>
       <c r="B45" t="n">
-        <v>57788</v>
+        <v>92028</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>232224</v>
+        <v>1527</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjocknäbbad nötkråka</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes caryocatactes</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>660576</v>
+        <v>660580</v>
       </c>
       <c r="R45" t="n">
-        <v>6642193</v>
+        <v>6641918</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5773,29 +5764,35 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5812,48 +5809,57 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127781932</v>
+        <v>127781868</v>
       </c>
       <c r="B46" t="n">
-        <v>92028</v>
+        <v>57788</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1527</v>
+        <v>232224</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Tjocknäbbad nötkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Nucifraga caryocatactes caryocatactes</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>660580</v>
+        <v>660576</v>
       </c>
       <c r="R46" t="n">
-        <v>6641918</v>
+        <v>6642193</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5883,35 +5889,29 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6137,10 +6137,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127782232</v>
+        <v>127782017</v>
       </c>
       <c r="B49" t="n">
-        <v>8439</v>
+        <v>4779</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,21 +6148,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106554</v>
+        <v>102306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6181,10 +6181,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>660691</v>
+        <v>660620</v>
       </c>
       <c r="R49" t="n">
-        <v>6642071</v>
+        <v>6642029</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6244,10 +6244,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127782017</v>
+        <v>127782232</v>
       </c>
       <c r="B50" t="n">
-        <v>4779</v>
+        <v>8439</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6255,21 +6255,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102306</v>
+        <v>106554</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6288,10 +6288,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>660620</v>
+        <v>660691</v>
       </c>
       <c r="R50" t="n">
-        <v>6642029</v>
+        <v>6642071</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6351,60 +6351,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127782136</v>
+        <v>127782030</v>
       </c>
       <c r="B51" t="n">
-        <v>57830</v>
+        <v>8439</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103020</v>
+        <v>106554</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Näset, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>660662</v>
+        <v>660611</v>
       </c>
       <c r="R51" t="n">
-        <v>6642152</v>
+        <v>6642055</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6442,6 +6439,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6460,57 +6458,60 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127782030</v>
+        <v>127782136</v>
       </c>
       <c r="B52" t="n">
-        <v>8439</v>
+        <v>57830</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106554</v>
+        <v>103020</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näset, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>660611</v>
+        <v>660662</v>
       </c>
       <c r="R52" t="n">
-        <v>6642055</v>
+        <v>6642152</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6548,7 +6549,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -2912,7 +2912,7 @@
         <v>127782139</v>
       </c>
       <c r="B19" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>127782069</v>
       </c>
       <c r="B21" t="n">
-        <v>95788</v>
+        <v>95789</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127781902</v>
+        <v>127782148</v>
       </c>
       <c r="B22" t="n">
-        <v>105418</v>
+        <v>5177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3230,38 +3230,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221141</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>660601</v>
+        <v>660674</v>
       </c>
       <c r="R22" t="n">
-        <v>6641916</v>
+        <v>6642146</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3321,10 +3326,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127782148</v>
+        <v>127781902</v>
       </c>
       <c r="B23" t="n">
-        <v>5177</v>
+        <v>105419</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3332,43 +3337,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>221141</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>660674</v>
+        <v>660601</v>
       </c>
       <c r="R23" t="n">
-        <v>6642146</v>
+        <v>6641916</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3431,7 +3431,7 @@
         <v>127782101</v>
       </c>
       <c r="B24" t="n">
-        <v>95788</v>
+        <v>95789</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>127782049</v>
       </c>
       <c r="B25" t="n">
-        <v>91327</v>
+        <v>91328</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,37 +3646,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127781942</v>
+        <v>127782073</v>
       </c>
       <c r="B26" t="n">
-        <v>92028</v>
+        <v>100651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1527</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3684,10 +3685,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>660593</v>
+        <v>660571</v>
       </c>
       <c r="R26" t="n">
-        <v>6641939</v>
+        <v>6642126</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3731,21 +3732,6 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3762,49 +3748,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127781893</v>
+        <v>127781942</v>
       </c>
       <c r="B27" t="n">
-        <v>95788</v>
+        <v>92029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2671</v>
+        <v>1527</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>660601</v>
+        <v>660593</v>
       </c>
       <c r="R27" t="n">
-        <v>6641916</v>
+        <v>6641939</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3848,6 +3833,21 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3864,10 +3864,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127781986</v>
+        <v>127781893</v>
       </c>
       <c r="B28" t="n">
-        <v>95788</v>
+        <v>95789</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3899,14 +3899,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>660653</v>
+        <v>660601</v>
       </c>
       <c r="R28" t="n">
-        <v>6641997</v>
+        <v>6641916</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127782073</v>
+        <v>127781986</v>
       </c>
       <c r="B29" t="n">
-        <v>100650</v>
+        <v>95789</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3977,21 +3977,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>660571</v>
+        <v>660653</v>
       </c>
       <c r="R29" t="n">
-        <v>6642126</v>
+        <v>6641997</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4071,7 +4071,7 @@
         <v>127781925</v>
       </c>
       <c r="B30" t="n">
-        <v>100557</v>
+        <v>100558</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>127782226</v>
       </c>
       <c r="B31" t="n">
-        <v>100557</v>
+        <v>100558</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>127782055</v>
       </c>
       <c r="B32" t="n">
-        <v>100557</v>
+        <v>100558</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4374,37 +4374,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127782149</v>
+        <v>127782095</v>
       </c>
       <c r="B33" t="n">
-        <v>91350</v>
+        <v>95789</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>2671</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4412,7 +4413,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>660677</v>
+        <v>660568</v>
       </c>
       <c r="R33" t="n">
         <v>6642142</v>
@@ -4475,38 +4476,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127782095</v>
+        <v>127782149</v>
       </c>
       <c r="B34" t="n">
-        <v>95788</v>
+        <v>91351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2671</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>660568</v>
+        <v>660677</v>
       </c>
       <c r="R34" t="n">
         <v>6642142</v>
@@ -4580,7 +4580,7 @@
         <v>127781996</v>
       </c>
       <c r="B35" t="n">
-        <v>95788</v>
+        <v>95789</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>127782137</v>
       </c>
       <c r="B36" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4808,46 +4808,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127782086</v>
+        <v>127781949</v>
       </c>
       <c r="B37" t="n">
-        <v>57832</v>
+        <v>103914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>222412</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4855,10 +4847,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>660568</v>
+        <v>660593</v>
       </c>
       <c r="R37" t="n">
-        <v>6642132</v>
+        <v>6641939</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4899,6 +4891,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4917,38 +4910,46 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127781949</v>
+        <v>127782086</v>
       </c>
       <c r="B38" t="n">
-        <v>103913</v>
+        <v>57832</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222412</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4956,10 +4957,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>660593</v>
+        <v>660568</v>
       </c>
       <c r="R38" t="n">
-        <v>6641939</v>
+        <v>6642132</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5000,7 +5001,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5022,7 +5022,7 @@
         <v>127781945</v>
       </c>
       <c r="B39" t="n">
-        <v>100557</v>
+        <v>100558</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5121,48 +5121,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127782042</v>
+        <v>127781882</v>
       </c>
       <c r="B40" t="n">
-        <v>91350</v>
+        <v>8439</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>660581</v>
+        <v>660605</v>
       </c>
       <c r="R40" t="n">
-        <v>6642052</v>
+        <v>6641899</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5206,21 +5212,6 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5237,57 +5228,51 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127782135</v>
+        <v>127782042</v>
       </c>
       <c r="B41" t="n">
-        <v>5177</v>
+        <v>91351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Näset, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>660662</v>
+        <v>660581</v>
       </c>
       <c r="R41" t="n">
-        <v>6642152</v>
+        <v>6642052</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5339,14 +5324,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5364,10 +5344,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127781882</v>
+        <v>127782135</v>
       </c>
       <c r="B42" t="n">
-        <v>8439</v>
+        <v>5177</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5375,21 +5355,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5404,17 +5384,17 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näset, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>660605</v>
+        <v>660662</v>
       </c>
       <c r="R42" t="n">
-        <v>6641899</v>
+        <v>6642152</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5455,6 +5435,26 @@
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5474,7 +5474,7 @@
         <v>127781944</v>
       </c>
       <c r="B43" t="n">
-        <v>90954</v>
+        <v>90955</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>127781920</v>
       </c>
       <c r="B44" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>127781932</v>
       </c>
       <c r="B45" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>127782079</v>
       </c>
       <c r="B47" t="n">
-        <v>95788</v>
+        <v>95789</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6137,10 +6137,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127782017</v>
+        <v>127782232</v>
       </c>
       <c r="B49" t="n">
-        <v>4779</v>
+        <v>8439</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,21 +6148,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102306</v>
+        <v>106554</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6181,10 +6181,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>660620</v>
+        <v>660691</v>
       </c>
       <c r="R49" t="n">
-        <v>6642029</v>
+        <v>6642071</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6244,10 +6244,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127782232</v>
+        <v>127782017</v>
       </c>
       <c r="B50" t="n">
-        <v>8439</v>
+        <v>4779</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6255,21 +6255,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106554</v>
+        <v>102306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6288,10 +6288,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>660691</v>
+        <v>660620</v>
       </c>
       <c r="R50" t="n">
-        <v>6642071</v>
+        <v>6642029</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -2912,7 +2912,7 @@
         <v>127782139</v>
       </c>
       <c r="B19" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>127782069</v>
       </c>
       <c r="B21" t="n">
-        <v>95789</v>
+        <v>95790</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127782148</v>
+        <v>127781902</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>105420</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3230,43 +3230,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>221141</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>660674</v>
+        <v>660601</v>
       </c>
       <c r="R22" t="n">
-        <v>6642146</v>
+        <v>6641916</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3326,10 +3321,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127781902</v>
+        <v>127782148</v>
       </c>
       <c r="B23" t="n">
-        <v>105419</v>
+        <v>5177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3337,38 +3332,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221141</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>660601</v>
+        <v>660674</v>
       </c>
       <c r="R23" t="n">
-        <v>6641916</v>
+        <v>6642146</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3431,7 +3431,7 @@
         <v>127782101</v>
       </c>
       <c r="B24" t="n">
-        <v>95789</v>
+        <v>95790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>127782049</v>
       </c>
       <c r="B25" t="n">
-        <v>91328</v>
+        <v>91329</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,38 +3646,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127782073</v>
+        <v>127781942</v>
       </c>
       <c r="B26" t="n">
-        <v>100651</v>
+        <v>92030</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>1527</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3685,10 +3684,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>660571</v>
+        <v>660593</v>
       </c>
       <c r="R26" t="n">
-        <v>6642126</v>
+        <v>6641939</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3732,6 +3731,21 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3748,48 +3762,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127781942</v>
+        <v>127781893</v>
       </c>
       <c r="B27" t="n">
-        <v>92029</v>
+        <v>95790</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1527</v>
+        <v>2671</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>660593</v>
+        <v>660601</v>
       </c>
       <c r="R27" t="n">
-        <v>6641939</v>
+        <v>6641916</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3833,21 +3848,6 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3864,10 +3864,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127781893</v>
+        <v>127781986</v>
       </c>
       <c r="B28" t="n">
-        <v>95789</v>
+        <v>95790</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3899,14 +3899,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>660601</v>
+        <v>660653</v>
       </c>
       <c r="R28" t="n">
-        <v>6641916</v>
+        <v>6641997</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127781986</v>
+        <v>127782073</v>
       </c>
       <c r="B29" t="n">
-        <v>95789</v>
+        <v>100652</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3977,21 +3977,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>660653</v>
+        <v>660571</v>
       </c>
       <c r="R29" t="n">
-        <v>6641997</v>
+        <v>6642126</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4071,7 +4071,7 @@
         <v>127781925</v>
       </c>
       <c r="B30" t="n">
-        <v>100558</v>
+        <v>100559</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>127782226</v>
       </c>
       <c r="B31" t="n">
-        <v>100558</v>
+        <v>100559</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>127782055</v>
       </c>
       <c r="B32" t="n">
-        <v>100558</v>
+        <v>100559</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4374,38 +4374,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127782095</v>
+        <v>127782149</v>
       </c>
       <c r="B33" t="n">
-        <v>95789</v>
+        <v>91352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2671</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4413,7 +4412,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>660568</v>
+        <v>660677</v>
       </c>
       <c r="R33" t="n">
         <v>6642142</v>
@@ -4476,37 +4475,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127782149</v>
+        <v>127782095</v>
       </c>
       <c r="B34" t="n">
-        <v>91351</v>
+        <v>95790</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>2671</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>660677</v>
+        <v>660568</v>
       </c>
       <c r="R34" t="n">
         <v>6642142</v>
@@ -4577,52 +4577,59 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127781996</v>
+        <v>127782137</v>
       </c>
       <c r="B35" t="n">
-        <v>95789</v>
+        <v>91648</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2671</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näset, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>660644</v>
+        <v>660662</v>
       </c>
       <c r="R35" t="n">
-        <v>6642016</v>
+        <v>6642152</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4663,6 +4670,26 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4679,59 +4706,52 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127782137</v>
+        <v>127781996</v>
       </c>
       <c r="B36" t="n">
-        <v>91647</v>
+        <v>95790</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>2671</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Näset, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>660662</v>
+        <v>660644</v>
       </c>
       <c r="R36" t="n">
-        <v>6642152</v>
+        <v>6642016</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4772,26 +4792,6 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4808,38 +4808,46 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127781949</v>
+        <v>127782086</v>
       </c>
       <c r="B37" t="n">
-        <v>103914</v>
+        <v>57832</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222412</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4847,10 +4855,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>660593</v>
+        <v>660568</v>
       </c>
       <c r="R37" t="n">
-        <v>6641939</v>
+        <v>6642132</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4891,7 +4899,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4910,46 +4917,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127782086</v>
+        <v>127781945</v>
       </c>
       <c r="B38" t="n">
-        <v>57832</v>
+        <v>100559</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>222771</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4957,10 +4956,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>660568</v>
+        <v>660593</v>
       </c>
       <c r="R38" t="n">
-        <v>6642132</v>
+        <v>6641939</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5001,6 +5000,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127781945</v>
+        <v>127781949</v>
       </c>
       <c r="B39" t="n">
-        <v>100558</v>
+        <v>103915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5231,7 +5231,7 @@
         <v>127782042</v>
       </c>
       <c r="B41" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5471,10 +5471,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127781944</v>
+        <v>127781920</v>
       </c>
       <c r="B43" t="n">
-        <v>90955</v>
+        <v>92117</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5482,21 +5482,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3086</v>
+        <v>366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Auricularia mesenterica</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.:Fr.) Pers.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>660593</v>
+        <v>660590</v>
       </c>
       <c r="R43" t="n">
-        <v>6641939</v>
+        <v>6641920</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5556,6 +5556,26 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5572,10 +5592,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127781920</v>
+        <v>127781944</v>
       </c>
       <c r="B44" t="n">
-        <v>92116</v>
+        <v>90956</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5583,21 +5603,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>366</v>
+        <v>3086</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Auricularia mesenterica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Dicks.:Fr.) Pers.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5610,10 +5630,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>660590</v>
+        <v>660593</v>
       </c>
       <c r="R44" t="n">
-        <v>6641920</v>
+        <v>6641939</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5657,26 +5677,6 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Populus tremula</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5696,7 +5696,7 @@
         <v>127781932</v>
       </c>
       <c r="B45" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5928,10 +5928,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127782079</v>
+        <v>127781984</v>
       </c>
       <c r="B47" t="n">
-        <v>95789</v>
+        <v>4779</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5939,27 +5939,32 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2671</v>
+        <v>102306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5967,10 +5972,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>660568</v>
+        <v>660653</v>
       </c>
       <c r="R47" t="n">
-        <v>6642132</v>
+        <v>6641997</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6030,10 +6035,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127781984</v>
+        <v>127782079</v>
       </c>
       <c r="B48" t="n">
-        <v>4779</v>
+        <v>95790</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6041,32 +6046,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102306</v>
+        <v>2671</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>660653</v>
+        <v>660568</v>
       </c>
       <c r="R48" t="n">
-        <v>6641997</v>
+        <v>6642132</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6351,57 +6351,60 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127782030</v>
+        <v>127782136</v>
       </c>
       <c r="B51" t="n">
-        <v>8439</v>
+        <v>57830</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106554</v>
+        <v>103020</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näset, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>660611</v>
+        <v>660662</v>
       </c>
       <c r="R51" t="n">
-        <v>6642055</v>
+        <v>6642152</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6439,7 +6442,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6458,60 +6460,57 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127782136</v>
+        <v>127782030</v>
       </c>
       <c r="B52" t="n">
-        <v>57830</v>
+        <v>8439</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103020</v>
+        <v>106554</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Näset, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>660662</v>
+        <v>660611</v>
       </c>
       <c r="R52" t="n">
-        <v>6642152</v>
+        <v>6642055</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6549,6 +6548,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -3219,10 +3219,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127781902</v>
+        <v>127782148</v>
       </c>
       <c r="B22" t="n">
-        <v>105420</v>
+        <v>5177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3230,38 +3230,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221141</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>660601</v>
+        <v>660674</v>
       </c>
       <c r="R22" t="n">
-        <v>6641916</v>
+        <v>6642146</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3321,10 +3326,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127782148</v>
+        <v>127781902</v>
       </c>
       <c r="B23" t="n">
-        <v>5177</v>
+        <v>105420</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3332,43 +3337,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>221141</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>660674</v>
+        <v>660601</v>
       </c>
       <c r="R23" t="n">
-        <v>6642146</v>
+        <v>6641916</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127782226</v>
+        <v>127782055</v>
       </c>
       <c r="B31" t="n">
         <v>100559</v>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>660709</v>
+        <v>660581</v>
       </c>
       <c r="R31" t="n">
-        <v>6642092</v>
+        <v>6642052</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127782055</v>
+        <v>127782226</v>
       </c>
       <c r="B32" t="n">
         <v>100559</v>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>660581</v>
+        <v>660709</v>
       </c>
       <c r="R32" t="n">
-        <v>6642052</v>
+        <v>6642092</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4577,59 +4577,52 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127782137</v>
+        <v>127781996</v>
       </c>
       <c r="B35" t="n">
-        <v>91648</v>
+        <v>95790</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>2671</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Näset, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>660662</v>
+        <v>660644</v>
       </c>
       <c r="R35" t="n">
-        <v>6642152</v>
+        <v>6642016</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4670,26 +4663,6 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4706,52 +4679,59 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127781996</v>
+        <v>127782137</v>
       </c>
       <c r="B36" t="n">
-        <v>95790</v>
+        <v>91648</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2671</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näset, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>660644</v>
+        <v>660662</v>
       </c>
       <c r="R36" t="n">
-        <v>6642016</v>
+        <v>6642152</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4792,6 +4772,26 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4808,46 +4808,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127782086</v>
+        <v>127781945</v>
       </c>
       <c r="B37" t="n">
-        <v>57832</v>
+        <v>100559</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>222771</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4855,10 +4847,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>660568</v>
+        <v>660593</v>
       </c>
       <c r="R37" t="n">
-        <v>6642132</v>
+        <v>6641939</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4899,6 +4891,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4917,38 +4910,46 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127781945</v>
+        <v>127782086</v>
       </c>
       <c r="B38" t="n">
-        <v>100559</v>
+        <v>57832</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222771</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4956,10 +4957,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>660593</v>
+        <v>660568</v>
       </c>
       <c r="R38" t="n">
-        <v>6641939</v>
+        <v>6642132</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5000,7 +5001,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5121,54 +5121,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127781882</v>
+        <v>127782042</v>
       </c>
       <c r="B40" t="n">
-        <v>8439</v>
+        <v>91352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>660605</v>
+        <v>660581</v>
       </c>
       <c r="R40" t="n">
-        <v>6641899</v>
+        <v>6642052</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5212,6 +5206,21 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5228,51 +5237,57 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127782042</v>
+        <v>127782135</v>
       </c>
       <c r="B41" t="n">
-        <v>91352</v>
+        <v>5177</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näset, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>660581</v>
+        <v>660662</v>
       </c>
       <c r="R41" t="n">
-        <v>6642052</v>
+        <v>6642152</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5324,9 +5339,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5344,10 +5364,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127782135</v>
+        <v>127781882</v>
       </c>
       <c r="B42" t="n">
-        <v>5177</v>
+        <v>8439</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5355,21 +5375,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5384,17 +5404,17 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Näset, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>660662</v>
+        <v>660605</v>
       </c>
       <c r="R42" t="n">
-        <v>6642152</v>
+        <v>6641899</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5435,26 +5455,6 @@
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5471,10 +5471,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127781920</v>
+        <v>127781944</v>
       </c>
       <c r="B43" t="n">
-        <v>92117</v>
+        <v>90956</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5482,21 +5482,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>366</v>
+        <v>3086</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Auricularia mesenterica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Dicks.:Fr.) Pers.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>660590</v>
+        <v>660593</v>
       </c>
       <c r="R43" t="n">
-        <v>6641920</v>
+        <v>6641939</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5556,26 +5556,6 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Populus tremula</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5592,10 +5572,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127781944</v>
+        <v>127781920</v>
       </c>
       <c r="B44" t="n">
-        <v>90956</v>
+        <v>92117</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5603,21 +5583,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3086</v>
+        <v>366</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Auricularia mesenterica</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.:Fr.) Pers.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5630,10 +5610,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>660593</v>
+        <v>660590</v>
       </c>
       <c r="R44" t="n">
-        <v>6641939</v>
+        <v>6641920</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5677,6 +5657,26 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6137,10 +6137,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127782232</v>
+        <v>127782017</v>
       </c>
       <c r="B49" t="n">
-        <v>8439</v>
+        <v>4779</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,21 +6148,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106554</v>
+        <v>102306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6181,10 +6181,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>660691</v>
+        <v>660620</v>
       </c>
       <c r="R49" t="n">
-        <v>6642071</v>
+        <v>6642029</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6244,10 +6244,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127782017</v>
+        <v>127782232</v>
       </c>
       <c r="B50" t="n">
-        <v>4779</v>
+        <v>8439</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6255,21 +6255,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102306</v>
+        <v>106554</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6288,10 +6288,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>660620</v>
+        <v>660691</v>
       </c>
       <c r="R50" t="n">
-        <v>6642029</v>
+        <v>6642071</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -3646,48 +3646,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127781942</v>
+        <v>127781893</v>
       </c>
       <c r="B26" t="n">
-        <v>92030</v>
+        <v>95790</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1527</v>
+        <v>2671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>660593</v>
+        <v>660601</v>
       </c>
       <c r="R26" t="n">
-        <v>6641939</v>
+        <v>6641916</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3731,21 +3732,6 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3762,7 +3748,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127781893</v>
+        <v>127781986</v>
       </c>
       <c r="B27" t="n">
         <v>95790</v>
@@ -3797,14 +3783,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>660601</v>
+        <v>660653</v>
       </c>
       <c r="R27" t="n">
-        <v>6641916</v>
+        <v>6641997</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3864,38 +3850,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127781986</v>
+        <v>127781942</v>
       </c>
       <c r="B28" t="n">
-        <v>95790</v>
+        <v>92030</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2671</v>
+        <v>1527</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3903,10 +3888,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>660653</v>
+        <v>660593</v>
       </c>
       <c r="R28" t="n">
-        <v>6641997</v>
+        <v>6641939</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3950,6 +3935,21 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -5471,10 +5471,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127781944</v>
+        <v>127781920</v>
       </c>
       <c r="B43" t="n">
-        <v>90956</v>
+        <v>92117</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5482,21 +5482,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3086</v>
+        <v>366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Auricularia mesenterica</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.:Fr.) Pers.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>660593</v>
+        <v>660590</v>
       </c>
       <c r="R43" t="n">
-        <v>6641939</v>
+        <v>6641920</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5556,6 +5556,26 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5572,10 +5592,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127781920</v>
+        <v>127781944</v>
       </c>
       <c r="B44" t="n">
-        <v>92117</v>
+        <v>90956</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5583,21 +5603,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>366</v>
+        <v>3086</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Auricularia mesenterica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Dicks.:Fr.) Pers.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5610,10 +5630,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>660590</v>
+        <v>660593</v>
       </c>
       <c r="R44" t="n">
-        <v>6641920</v>
+        <v>6641939</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5657,26 +5677,6 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Populus tremula</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5928,10 +5928,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127781984</v>
+        <v>127782079</v>
       </c>
       <c r="B47" t="n">
-        <v>4779</v>
+        <v>95790</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5939,32 +5939,27 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102306</v>
+        <v>2671</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5972,10 +5967,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>660653</v>
+        <v>660568</v>
       </c>
       <c r="R47" t="n">
-        <v>6641997</v>
+        <v>6642132</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6035,10 +6030,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127782079</v>
+        <v>127781984</v>
       </c>
       <c r="B48" t="n">
-        <v>95790</v>
+        <v>4779</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6046,27 +6041,32 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2671</v>
+        <v>102306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>660568</v>
+        <v>660653</v>
       </c>
       <c r="R48" t="n">
-        <v>6642132</v>
+        <v>6641997</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -3646,49 +3646,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127781893</v>
+        <v>127781942</v>
       </c>
       <c r="B26" t="n">
-        <v>95790</v>
+        <v>92030</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2671</v>
+        <v>1527</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>660601</v>
+        <v>660593</v>
       </c>
       <c r="R26" t="n">
-        <v>6641916</v>
+        <v>6641939</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3732,6 +3731,21 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3748,7 +3762,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127781986</v>
+        <v>127781893</v>
       </c>
       <c r="B27" t="n">
         <v>95790</v>
@@ -3783,14 +3797,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>660653</v>
+        <v>660601</v>
       </c>
       <c r="R27" t="n">
-        <v>6641997</v>
+        <v>6641916</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3850,37 +3864,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127781942</v>
+        <v>127781986</v>
       </c>
       <c r="B28" t="n">
-        <v>92030</v>
+        <v>95790</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1527</v>
+        <v>2671</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3888,10 +3903,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>660593</v>
+        <v>660653</v>
       </c>
       <c r="R28" t="n">
-        <v>6641939</v>
+        <v>6641997</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3935,21 +3950,6 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -3646,48 +3646,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127781942</v>
+        <v>127781893</v>
       </c>
       <c r="B26" t="n">
-        <v>92030</v>
+        <v>95790</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1527</v>
+        <v>2671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>660593</v>
+        <v>660601</v>
       </c>
       <c r="R26" t="n">
-        <v>6641939</v>
+        <v>6641916</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3731,21 +3732,6 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3762,7 +3748,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127781893</v>
+        <v>127781986</v>
       </c>
       <c r="B27" t="n">
         <v>95790</v>
@@ -3797,14 +3783,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>660601</v>
+        <v>660653</v>
       </c>
       <c r="R27" t="n">
-        <v>6641916</v>
+        <v>6641997</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3864,38 +3850,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127781986</v>
+        <v>127781942</v>
       </c>
       <c r="B28" t="n">
-        <v>95790</v>
+        <v>92030</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2671</v>
+        <v>1527</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3903,10 +3888,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>660653</v>
+        <v>660593</v>
       </c>
       <c r="R28" t="n">
-        <v>6641997</v>
+        <v>6641939</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3950,6 +3935,21 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4808,38 +4808,46 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127781945</v>
+        <v>127782086</v>
       </c>
       <c r="B37" t="n">
-        <v>100559</v>
+        <v>57832</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222771</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4847,10 +4855,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>660593</v>
+        <v>660568</v>
       </c>
       <c r="R37" t="n">
-        <v>6641939</v>
+        <v>6642132</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4891,7 +4899,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4910,46 +4917,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127782086</v>
+        <v>127781949</v>
       </c>
       <c r="B38" t="n">
-        <v>57832</v>
+        <v>103915</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>222412</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4957,10 +4956,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>660568</v>
+        <v>660593</v>
       </c>
       <c r="R38" t="n">
-        <v>6642132</v>
+        <v>6641939</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5001,6 +5000,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127781949</v>
+        <v>127781945</v>
       </c>
       <c r="B39" t="n">
-        <v>103915</v>
+        <v>100559</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6137,10 +6137,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127782017</v>
+        <v>127782232</v>
       </c>
       <c r="B49" t="n">
-        <v>4779</v>
+        <v>8439</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,21 +6148,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102306</v>
+        <v>106554</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6181,10 +6181,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>660620</v>
+        <v>660691</v>
       </c>
       <c r="R49" t="n">
-        <v>6642029</v>
+        <v>6642071</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6244,10 +6244,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127782232</v>
+        <v>127782017</v>
       </c>
       <c r="B50" t="n">
-        <v>8439</v>
+        <v>4779</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6255,21 +6255,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106554</v>
+        <v>102306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6288,10 +6288,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>660691</v>
+        <v>660620</v>
       </c>
       <c r="R50" t="n">
-        <v>6642071</v>
+        <v>6642029</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -4577,52 +4577,59 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127781996</v>
+        <v>127782137</v>
       </c>
       <c r="B35" t="n">
-        <v>95790</v>
+        <v>91648</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2671</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näset, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>660644</v>
+        <v>660662</v>
       </c>
       <c r="R35" t="n">
-        <v>6642016</v>
+        <v>6642152</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4663,6 +4670,26 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4679,59 +4706,52 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127782137</v>
+        <v>127781996</v>
       </c>
       <c r="B36" t="n">
-        <v>91648</v>
+        <v>95790</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>2671</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Näset, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>660662</v>
+        <v>660644</v>
       </c>
       <c r="R36" t="n">
-        <v>6642152</v>
+        <v>6642016</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4772,26 +4792,6 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -5471,10 +5471,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127781920</v>
+        <v>127781944</v>
       </c>
       <c r="B43" t="n">
-        <v>92117</v>
+        <v>90956</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5482,21 +5482,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>366</v>
+        <v>3086</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Auricularia mesenterica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Dicks.:Fr.) Pers.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>660590</v>
+        <v>660593</v>
       </c>
       <c r="R43" t="n">
-        <v>6641920</v>
+        <v>6641939</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5556,26 +5556,6 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Populus tremula</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5592,10 +5572,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127781944</v>
+        <v>127781920</v>
       </c>
       <c r="B44" t="n">
-        <v>90956</v>
+        <v>92117</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5603,21 +5583,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3086</v>
+        <v>366</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Auricularia mesenterica</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.:Fr.) Pers.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5630,10 +5610,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>660593</v>
+        <v>660590</v>
       </c>
       <c r="R44" t="n">
-        <v>6641939</v>
+        <v>6641920</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5677,6 +5657,26 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -2912,7 +2912,7 @@
         <v>127782139</v>
       </c>
       <c r="B19" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>127782069</v>
       </c>
       <c r="B21" t="n">
-        <v>95790</v>
+        <v>95798</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127782148</v>
+        <v>127781902</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>105428</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3230,43 +3230,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>221141</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>660674</v>
+        <v>660601</v>
       </c>
       <c r="R22" t="n">
-        <v>6642146</v>
+        <v>6641916</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3326,10 +3321,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127781902</v>
+        <v>127782148</v>
       </c>
       <c r="B23" t="n">
-        <v>105420</v>
+        <v>5177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3337,38 +3332,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221141</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>660601</v>
+        <v>660674</v>
       </c>
       <c r="R23" t="n">
-        <v>6641916</v>
+        <v>6642146</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3431,7 +3431,7 @@
         <v>127782101</v>
       </c>
       <c r="B24" t="n">
-        <v>95790</v>
+        <v>95798</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>127782049</v>
       </c>
       <c r="B25" t="n">
-        <v>91329</v>
+        <v>91337</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,37 +3646,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127781942</v>
+        <v>127782073</v>
       </c>
       <c r="B26" t="n">
-        <v>92030</v>
+        <v>100660</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1527</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3684,10 +3685,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>660593</v>
+        <v>660571</v>
       </c>
       <c r="R26" t="n">
-        <v>6641939</v>
+        <v>6642126</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3731,21 +3732,6 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3762,49 +3748,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127781893</v>
+        <v>127781942</v>
       </c>
       <c r="B27" t="n">
-        <v>95790</v>
+        <v>92038</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2671</v>
+        <v>1527</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>660601</v>
+        <v>660593</v>
       </c>
       <c r="R27" t="n">
-        <v>6641916</v>
+        <v>6641939</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3848,6 +3833,21 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3864,10 +3864,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127781986</v>
+        <v>127781893</v>
       </c>
       <c r="B28" t="n">
-        <v>95790</v>
+        <v>95798</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3899,14 +3899,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>660653</v>
+        <v>660601</v>
       </c>
       <c r="R28" t="n">
-        <v>6641997</v>
+        <v>6641916</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127782073</v>
+        <v>127781986</v>
       </c>
       <c r="B29" t="n">
-        <v>100652</v>
+        <v>95798</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3977,21 +3977,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>660571</v>
+        <v>660653</v>
       </c>
       <c r="R29" t="n">
-        <v>6642126</v>
+        <v>6641997</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4071,7 +4071,7 @@
         <v>127781925</v>
       </c>
       <c r="B30" t="n">
-        <v>100559</v>
+        <v>100567</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4170,10 +4170,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127782055</v>
+        <v>127782226</v>
       </c>
       <c r="B31" t="n">
-        <v>100559</v>
+        <v>100567</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>660581</v>
+        <v>660709</v>
       </c>
       <c r="R31" t="n">
-        <v>6642052</v>
+        <v>6642092</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4272,10 +4272,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127782226</v>
+        <v>127782055</v>
       </c>
       <c r="B32" t="n">
-        <v>100559</v>
+        <v>100567</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>660709</v>
+        <v>660581</v>
       </c>
       <c r="R32" t="n">
-        <v>6642092</v>
+        <v>6642052</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4377,7 +4377,7 @@
         <v>127782149</v>
       </c>
       <c r="B33" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>127782095</v>
       </c>
       <c r="B34" t="n">
-        <v>95790</v>
+        <v>95798</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>127782137</v>
       </c>
       <c r="B35" t="n">
-        <v>91648</v>
+        <v>91656</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>127781996</v>
       </c>
       <c r="B36" t="n">
-        <v>95790</v>
+        <v>95798</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4808,46 +4808,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127782086</v>
+        <v>127781945</v>
       </c>
       <c r="B37" t="n">
-        <v>57832</v>
+        <v>100567</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>222771</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4855,10 +4847,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>660568</v>
+        <v>660593</v>
       </c>
       <c r="R37" t="n">
-        <v>6642132</v>
+        <v>6641939</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4899,6 +4891,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4920,7 +4913,7 @@
         <v>127781949</v>
       </c>
       <c r="B38" t="n">
-        <v>103915</v>
+        <v>103923</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5019,38 +5012,46 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127781945</v>
+        <v>127782086</v>
       </c>
       <c r="B39" t="n">
-        <v>100559</v>
+        <v>57833</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222771</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5058,10 +5059,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>660593</v>
+        <v>660568</v>
       </c>
       <c r="R39" t="n">
-        <v>6641939</v>
+        <v>6642132</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5102,7 +5103,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5124,7 +5124,7 @@
         <v>127782042</v>
       </c>
       <c r="B40" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5471,10 +5471,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127781944</v>
+        <v>127781920</v>
       </c>
       <c r="B43" t="n">
-        <v>90956</v>
+        <v>92125</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5482,21 +5482,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3086</v>
+        <v>366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Auricularia mesenterica</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.:Fr.) Pers.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>660593</v>
+        <v>660590</v>
       </c>
       <c r="R43" t="n">
-        <v>6641939</v>
+        <v>6641920</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5556,6 +5556,26 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5572,10 +5592,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127781920</v>
+        <v>127781944</v>
       </c>
       <c r="B44" t="n">
-        <v>92117</v>
+        <v>90962</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5583,21 +5603,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>366</v>
+        <v>3086</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Auricularia mesenterica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Dicks.:Fr.) Pers.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5610,10 +5630,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>660590</v>
+        <v>660593</v>
       </c>
       <c r="R44" t="n">
-        <v>6641920</v>
+        <v>6641939</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5657,26 +5677,6 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Populus tremula</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5693,48 +5693,57 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127781932</v>
+        <v>127781868</v>
       </c>
       <c r="B45" t="n">
-        <v>92030</v>
+        <v>57789</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1527</v>
+        <v>232224</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Tjocknäbbad nötkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Nucifraga caryocatactes caryocatactes</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>660580</v>
+        <v>660576</v>
       </c>
       <c r="R45" t="n">
-        <v>6641918</v>
+        <v>6642193</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5764,35 +5773,29 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5809,57 +5812,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127781868</v>
+        <v>127781932</v>
       </c>
       <c r="B46" t="n">
-        <v>57788</v>
+        <v>92038</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>232224</v>
+        <v>1527</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjocknäbbad nötkråka</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes caryocatactes</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>660576</v>
+        <v>660580</v>
       </c>
       <c r="R46" t="n">
-        <v>6642193</v>
+        <v>6641918</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5889,29 +5883,35 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5928,10 +5928,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127782079</v>
+        <v>127781984</v>
       </c>
       <c r="B47" t="n">
-        <v>95790</v>
+        <v>4779</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5939,27 +5939,32 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2671</v>
+        <v>102306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5967,10 +5972,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>660568</v>
+        <v>660653</v>
       </c>
       <c r="R47" t="n">
-        <v>6642132</v>
+        <v>6641997</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6030,10 +6035,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127781984</v>
+        <v>127782079</v>
       </c>
       <c r="B48" t="n">
-        <v>4779</v>
+        <v>95798</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6041,32 +6046,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102306</v>
+        <v>2671</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>660653</v>
+        <v>660568</v>
       </c>
       <c r="R48" t="n">
-        <v>6641997</v>
+        <v>6642132</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6137,10 +6137,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127782232</v>
+        <v>127782017</v>
       </c>
       <c r="B49" t="n">
-        <v>8439</v>
+        <v>4779</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,21 +6148,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106554</v>
+        <v>102306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6181,10 +6181,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>660691</v>
+        <v>660620</v>
       </c>
       <c r="R49" t="n">
-        <v>6642071</v>
+        <v>6642029</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6244,10 +6244,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127782017</v>
+        <v>127782232</v>
       </c>
       <c r="B50" t="n">
-        <v>4779</v>
+        <v>8439</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6255,21 +6255,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102306</v>
+        <v>106554</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6288,10 +6288,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>660620</v>
+        <v>660691</v>
       </c>
       <c r="R50" t="n">
-        <v>6642029</v>
+        <v>6642071</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6351,60 +6351,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127782136</v>
+        <v>127782030</v>
       </c>
       <c r="B51" t="n">
-        <v>57830</v>
+        <v>8439</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103020</v>
+        <v>106554</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Näset, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>660662</v>
+        <v>660611</v>
       </c>
       <c r="R51" t="n">
-        <v>6642152</v>
+        <v>6642055</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6442,6 +6439,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6460,57 +6458,60 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127782030</v>
+        <v>127782136</v>
       </c>
       <c r="B52" t="n">
-        <v>8439</v>
+        <v>57831</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106554</v>
+        <v>103020</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näset, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>660611</v>
+        <v>660662</v>
       </c>
       <c r="R52" t="n">
-        <v>6642055</v>
+        <v>6642152</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6548,7 +6549,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -3219,10 +3219,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127781902</v>
+        <v>127782148</v>
       </c>
       <c r="B22" t="n">
-        <v>105428</v>
+        <v>5177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3230,38 +3230,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221141</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>660601</v>
+        <v>660674</v>
       </c>
       <c r="R22" t="n">
-        <v>6641916</v>
+        <v>6642146</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3321,10 +3326,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127782148</v>
+        <v>127781902</v>
       </c>
       <c r="B23" t="n">
-        <v>5177</v>
+        <v>105428</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3332,43 +3337,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>221141</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>660674</v>
+        <v>660601</v>
       </c>
       <c r="R23" t="n">
-        <v>6642146</v>
+        <v>6641916</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2912,7 +2912,7 @@
         <v>127782139</v>
       </c>
       <c r="B19" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>127782069</v>
       </c>
       <c r="B21" t="n">
-        <v>95798</v>
+        <v>95891</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127782148</v>
+        <v>127781902</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>105521</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3230,43 +3230,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>221141</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>660674</v>
+        <v>660601</v>
       </c>
       <c r="R22" t="n">
-        <v>6642146</v>
+        <v>6641916</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3326,10 +3321,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127781902</v>
+        <v>127782148</v>
       </c>
       <c r="B23" t="n">
-        <v>105428</v>
+        <v>5177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3337,38 +3332,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221141</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>660601</v>
+        <v>660674</v>
       </c>
       <c r="R23" t="n">
-        <v>6641916</v>
+        <v>6642146</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3431,7 +3431,7 @@
         <v>127782101</v>
       </c>
       <c r="B24" t="n">
-        <v>95798</v>
+        <v>95891</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>127782049</v>
       </c>
       <c r="B25" t="n">
-        <v>91337</v>
+        <v>91429</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,38 +3646,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127782073</v>
+        <v>127781942</v>
       </c>
       <c r="B26" t="n">
-        <v>100660</v>
+        <v>92130</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>1527</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3685,10 +3684,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>660571</v>
+        <v>660593</v>
       </c>
       <c r="R26" t="n">
-        <v>6642126</v>
+        <v>6641939</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3732,6 +3731,21 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3748,48 +3762,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127781942</v>
+        <v>127781893</v>
       </c>
       <c r="B27" t="n">
-        <v>92038</v>
+        <v>95891</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1527</v>
+        <v>2671</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>660593</v>
+        <v>660601</v>
       </c>
       <c r="R27" t="n">
-        <v>6641939</v>
+        <v>6641916</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3833,21 +3848,6 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3864,10 +3864,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127781893</v>
+        <v>127781986</v>
       </c>
       <c r="B28" t="n">
-        <v>95798</v>
+        <v>95891</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3899,14 +3899,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>660601</v>
+        <v>660653</v>
       </c>
       <c r="R28" t="n">
-        <v>6641916</v>
+        <v>6641997</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127781986</v>
+        <v>127782073</v>
       </c>
       <c r="B29" t="n">
-        <v>95798</v>
+        <v>100753</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3977,21 +3977,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>660653</v>
+        <v>660571</v>
       </c>
       <c r="R29" t="n">
-        <v>6641997</v>
+        <v>6642126</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4071,7 +4071,7 @@
         <v>127781925</v>
       </c>
       <c r="B30" t="n">
-        <v>100567</v>
+        <v>100660</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>127782226</v>
       </c>
       <c r="B31" t="n">
-        <v>100567</v>
+        <v>100660</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>127782055</v>
       </c>
       <c r="B32" t="n">
-        <v>100567</v>
+        <v>100660</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4374,37 +4374,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127782149</v>
+        <v>127782095</v>
       </c>
       <c r="B33" t="n">
-        <v>91360</v>
+        <v>95891</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>2671</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4412,7 +4413,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>660677</v>
+        <v>660568</v>
       </c>
       <c r="R33" t="n">
         <v>6642142</v>
@@ -4475,38 +4476,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127782095</v>
+        <v>127782149</v>
       </c>
       <c r="B34" t="n">
-        <v>95798</v>
+        <v>91452</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2671</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>660568</v>
+        <v>660677</v>
       </c>
       <c r="R34" t="n">
         <v>6642142</v>
@@ -4577,59 +4577,52 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127782137</v>
+        <v>127781996</v>
       </c>
       <c r="B35" t="n">
-        <v>91656</v>
+        <v>95891</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>2671</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Näset, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>660662</v>
+        <v>660644</v>
       </c>
       <c r="R35" t="n">
-        <v>6642152</v>
+        <v>6642016</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4670,26 +4663,6 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4706,52 +4679,59 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127781996</v>
+        <v>127782137</v>
       </c>
       <c r="B36" t="n">
-        <v>95798</v>
+        <v>91748</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2671</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näset, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>660644</v>
+        <v>660662</v>
       </c>
       <c r="R36" t="n">
-        <v>6642016</v>
+        <v>6642152</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4792,6 +4772,26 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4808,38 +4808,46 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127781945</v>
+        <v>127782086</v>
       </c>
       <c r="B37" t="n">
-        <v>100567</v>
+        <v>57845</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222771</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4847,10 +4855,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>660593</v>
+        <v>660568</v>
       </c>
       <c r="R37" t="n">
-        <v>6641939</v>
+        <v>6642132</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4891,7 +4899,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4910,10 +4917,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127781949</v>
+        <v>127781945</v>
       </c>
       <c r="B38" t="n">
-        <v>103923</v>
+        <v>100660</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4921,16 +4928,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5012,46 +5019,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127782086</v>
+        <v>127781949</v>
       </c>
       <c r="B39" t="n">
-        <v>57833</v>
+        <v>104016</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>222412</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5059,10 +5058,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>660568</v>
+        <v>660593</v>
       </c>
       <c r="R39" t="n">
-        <v>6642132</v>
+        <v>6641939</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5103,6 +5102,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5124,7 +5124,7 @@
         <v>127782042</v>
       </c>
       <c r="B40" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5471,10 +5471,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127781920</v>
+        <v>127781944</v>
       </c>
       <c r="B43" t="n">
-        <v>92125</v>
+        <v>91054</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5482,21 +5482,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>366</v>
+        <v>3086</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Auricularia mesenterica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Dicks.:Fr.) Pers.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>660590</v>
+        <v>660593</v>
       </c>
       <c r="R43" t="n">
-        <v>6641920</v>
+        <v>6641939</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5556,26 +5556,6 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Populus tremula</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5592,10 +5572,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127781944</v>
+        <v>127781920</v>
       </c>
       <c r="B44" t="n">
-        <v>90962</v>
+        <v>92217</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5603,21 +5583,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3086</v>
+        <v>366</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Auricularia mesenterica</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.:Fr.) Pers.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5630,10 +5610,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>660593</v>
+        <v>660590</v>
       </c>
       <c r="R44" t="n">
-        <v>6641939</v>
+        <v>6641920</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5677,6 +5657,26 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5693,57 +5693,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127781868</v>
+        <v>127781932</v>
       </c>
       <c r="B45" t="n">
-        <v>57789</v>
+        <v>92130</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>232224</v>
+        <v>1527</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjocknäbbad nötkråka</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes caryocatactes</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>660576</v>
+        <v>660580</v>
       </c>
       <c r="R45" t="n">
-        <v>6642193</v>
+        <v>6641918</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5773,29 +5764,35 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5812,48 +5809,57 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127781932</v>
+        <v>127781868</v>
       </c>
       <c r="B46" t="n">
-        <v>92038</v>
+        <v>57801</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1527</v>
+        <v>232224</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Tjocknäbbad nötkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Nucifraga caryocatactes caryocatactes</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>660580</v>
+        <v>660576</v>
       </c>
       <c r="R46" t="n">
-        <v>6641918</v>
+        <v>6642193</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5883,35 +5889,29 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6038,7 +6038,7 @@
         <v>127782079</v>
       </c>
       <c r="B48" t="n">
-        <v>95798</v>
+        <v>95891</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>127782136</v>
       </c>
       <c r="B52" t="n">
-        <v>57831</v>
+        <v>57843</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6564,6 +6564,3503 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128577897</v>
+      </c>
+      <c r="B53" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>660601</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6642004</v>
+      </c>
+      <c r="S53" t="n">
+        <v>20</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128577820</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>660679</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6642144</v>
+      </c>
+      <c r="S54" t="n">
+        <v>20</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128577858</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91005</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>901</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Narrtagging</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hydnocristella himantia</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>660708</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6642196</v>
+      </c>
+      <c r="S55" t="n">
+        <v>20</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128577905</v>
+      </c>
+      <c r="B56" t="n">
+        <v>92122</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>898</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>660680</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6642150</v>
+      </c>
+      <c r="S56" t="n">
+        <v>20</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128577843</v>
+      </c>
+      <c r="B57" t="n">
+        <v>92130</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1527</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Prakttagging</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Steccherinum robustius</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>660556</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6642090</v>
+      </c>
+      <c r="S57" t="n">
+        <v>20</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128577885</v>
+      </c>
+      <c r="B58" t="n">
+        <v>90913</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>660621</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6642044</v>
+      </c>
+      <c r="S58" t="n">
+        <v>20</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128577892</v>
+      </c>
+      <c r="B59" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>660554</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6642138</v>
+      </c>
+      <c r="S59" t="n">
+        <v>20</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128577882</v>
+      </c>
+      <c r="B60" t="n">
+        <v>95891</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>660709</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6642203</v>
+      </c>
+      <c r="S60" t="n">
+        <v>20</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128577853</v>
+      </c>
+      <c r="B61" t="n">
+        <v>86944</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>660617</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6642063</v>
+      </c>
+      <c r="S61" t="n">
+        <v>20</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128577816</v>
+      </c>
+      <c r="B62" t="n">
+        <v>86944</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>660612</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6642049</v>
+      </c>
+      <c r="S62" t="n">
+        <v>20</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128577817</v>
+      </c>
+      <c r="B63" t="n">
+        <v>92738</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>4363</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hydnellum concrescens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>660620</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6642049</v>
+      </c>
+      <c r="S63" t="n">
+        <v>20</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128577884</v>
+      </c>
+      <c r="B64" t="n">
+        <v>95891</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>660554</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6642138</v>
+      </c>
+      <c r="S64" t="n">
+        <v>20</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128577889</v>
+      </c>
+      <c r="B65" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>660614</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6642042</v>
+      </c>
+      <c r="S65" t="n">
+        <v>20</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128577881</v>
+      </c>
+      <c r="B66" t="n">
+        <v>95891</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>660699</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6642205</v>
+      </c>
+      <c r="S66" t="n">
+        <v>20</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128577878</v>
+      </c>
+      <c r="B67" t="n">
+        <v>95891</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>660701</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6642183</v>
+      </c>
+      <c r="S67" t="n">
+        <v>20</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128577833</v>
+      </c>
+      <c r="B68" t="n">
+        <v>100660</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>660698</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6642170</v>
+      </c>
+      <c r="S68" t="n">
+        <v>20</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128577828</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91054</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>3086</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Svartöra</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Auricularia mesenterica</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Dicks.:Fr.) Pers.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>660702</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6642212</v>
+      </c>
+      <c r="S69" t="n">
+        <v>20</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128577904</v>
+      </c>
+      <c r="B70" t="n">
+        <v>92081</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>660641</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6642025</v>
+      </c>
+      <c r="S70" t="n">
+        <v>20</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128577824</v>
+      </c>
+      <c r="B71" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>660682</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6642193</v>
+      </c>
+      <c r="S71" t="n">
+        <v>20</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128577894</v>
+      </c>
+      <c r="B72" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>660638</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6641974</v>
+      </c>
+      <c r="S72" t="n">
+        <v>20</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128577886</v>
+      </c>
+      <c r="B73" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>660635</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6641930</v>
+      </c>
+      <c r="S73" t="n">
+        <v>20</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128577871</v>
+      </c>
+      <c r="B74" t="n">
+        <v>95891</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>660627</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6642017</v>
+      </c>
+      <c r="S74" t="n">
+        <v>20</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128577908</v>
+      </c>
+      <c r="B75" t="n">
+        <v>90725</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>749</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Alsopp</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Gyrodon lividus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Bull.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>660712</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6642212</v>
+      </c>
+      <c r="S75" t="n">
+        <v>20</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128577825</v>
+      </c>
+      <c r="B76" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>660562</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6642094</v>
+      </c>
+      <c r="S76" t="n">
+        <v>20</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128577893</v>
+      </c>
+      <c r="B77" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>660559</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6642135</v>
+      </c>
+      <c r="S77" t="n">
+        <v>20</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128577875</v>
+      </c>
+      <c r="B78" t="n">
+        <v>95891</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>660658</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6642168</v>
+      </c>
+      <c r="S78" t="n">
+        <v>20</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128577818</v>
+      </c>
+      <c r="B79" t="n">
+        <v>92738</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>4363</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hydnellum concrescens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>660559</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6642143</v>
+      </c>
+      <c r="S79" t="n">
+        <v>20</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>20 fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128577888</v>
+      </c>
+      <c r="B80" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>660615</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6642026</v>
+      </c>
+      <c r="S80" t="n">
+        <v>20</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128577896</v>
+      </c>
+      <c r="B81" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>660619</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6642007</v>
+      </c>
+      <c r="S81" t="n">
+        <v>20</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128577823</v>
+      </c>
+      <c r="B82" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>660679</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6642181</v>
+      </c>
+      <c r="S82" t="n">
+        <v>20</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128577880</v>
+      </c>
+      <c r="B83" t="n">
+        <v>95891</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>660697</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6642175</v>
+      </c>
+      <c r="S83" t="n">
+        <v>20</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128577898</v>
+      </c>
+      <c r="B84" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>660597</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6642016</v>
+      </c>
+      <c r="S84" t="n">
+        <v>20</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128577877</v>
+      </c>
+      <c r="B85" t="n">
+        <v>95891</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>660666</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6642164</v>
+      </c>
+      <c r="S85" t="n">
+        <v>20</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128577827</v>
+      </c>
+      <c r="B86" t="n">
+        <v>91054</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>3086</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Svartöra</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Auricularia mesenterica</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Dicks.:Fr.) Pers.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>660698</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6642185</v>
+      </c>
+      <c r="S86" t="n">
+        <v>20</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>128577891</v>
+      </c>
+      <c r="B87" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>660557</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6642137</v>
+      </c>
+      <c r="S87" t="n">
+        <v>20</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>128577890</v>
+      </c>
+      <c r="B88" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Näsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>660618</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6642051</v>
+      </c>
+      <c r="S88" t="n">
+        <v>20</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -3219,10 +3219,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127781902</v>
+        <v>127782148</v>
       </c>
       <c r="B22" t="n">
-        <v>105521</v>
+        <v>5177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3230,38 +3230,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221141</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Näsudden, Funbosjön, Upl</t>
+          <t>Näsudden, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>660601</v>
+        <v>660674</v>
       </c>
       <c r="R22" t="n">
-        <v>6641916</v>
+        <v>6642146</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3321,10 +3326,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127782148</v>
+        <v>127781902</v>
       </c>
       <c r="B23" t="n">
-        <v>5177</v>
+        <v>105521</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3332,43 +3337,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>221141</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Näsudden, Upl</t>
+          <t>Näsudden, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>660674</v>
+        <v>660601</v>
       </c>
       <c r="R23" t="n">
-        <v>6642146</v>
+        <v>6641916</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -4374,38 +4374,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127782095</v>
+        <v>127782149</v>
       </c>
       <c r="B33" t="n">
-        <v>95891</v>
+        <v>91452</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2671</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4413,7 +4412,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>660568</v>
+        <v>660677</v>
       </c>
       <c r="R33" t="n">
         <v>6642142</v>
@@ -4476,37 +4475,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127782149</v>
+        <v>127782095</v>
       </c>
       <c r="B34" t="n">
-        <v>91452</v>
+        <v>95891</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>2671</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>660677</v>
+        <v>660568</v>
       </c>
       <c r="R34" t="n">
         <v>6642142</v>
@@ -4917,10 +4917,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127781945</v>
+        <v>127781949</v>
       </c>
       <c r="B38" t="n">
-        <v>100660</v>
+        <v>104016</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4928,16 +4928,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5019,10 +5019,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127781949</v>
+        <v>127781945</v>
       </c>
       <c r="B39" t="n">
-        <v>104016</v>
+        <v>100660</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5928,10 +5928,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127781984</v>
+        <v>127782079</v>
       </c>
       <c r="B47" t="n">
-        <v>4779</v>
+        <v>95891</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5939,32 +5939,27 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102306</v>
+        <v>2671</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5972,10 +5967,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>660653</v>
+        <v>660568</v>
       </c>
       <c r="R47" t="n">
-        <v>6641997</v>
+        <v>6642132</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6035,10 +6030,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127782079</v>
+        <v>127781984</v>
       </c>
       <c r="B48" t="n">
-        <v>95891</v>
+        <v>4779</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6046,27 +6041,32 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2671</v>
+        <v>102306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>660568</v>
+        <v>660653</v>
       </c>
       <c r="R48" t="n">
-        <v>6642132</v>
+        <v>6641997</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -7052,32 +7052,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128577885</v>
+        <v>128577892</v>
       </c>
       <c r="B58" t="n">
-        <v>90913</v>
+        <v>92776</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3286</v>
+        <v>5964</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7087,10 +7087,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>660621</v>
+        <v>660554</v>
       </c>
       <c r="R58" t="n">
-        <v>6642044</v>
+        <v>6642138</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7149,32 +7149,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128577892</v>
+        <v>128577885</v>
       </c>
       <c r="B59" t="n">
-        <v>92776</v>
+        <v>90913</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5964</v>
+        <v>3286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>660554</v>
+        <v>660621</v>
       </c>
       <c r="R59" t="n">
-        <v>6642138</v>
+        <v>6642044</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7343,32 +7343,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128577853</v>
+        <v>128577817</v>
       </c>
       <c r="B61" t="n">
-        <v>86944</v>
+        <v>92738</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3739</v>
+        <v>4363</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>660617</v>
+        <v>660620</v>
       </c>
       <c r="R61" t="n">
-        <v>6642063</v>
+        <v>6642049</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7440,7 +7440,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128577816</v>
+        <v>128577853</v>
       </c>
       <c r="B62" t="n">
         <v>86944</v>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>660612</v>
+        <v>660617</v>
       </c>
       <c r="R62" t="n">
-        <v>6642049</v>
+        <v>6642063</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7537,32 +7537,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128577817</v>
+        <v>128577816</v>
       </c>
       <c r="B63" t="n">
-        <v>92738</v>
+        <v>86944</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4363</v>
+        <v>3739</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7572,7 +7572,7 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>660620</v>
+        <v>660612</v>
       </c>
       <c r="R63" t="n">
         <v>6642049</v>
@@ -7731,10 +7731,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128577889</v>
+        <v>128577878</v>
       </c>
       <c r="B65" t="n">
-        <v>92776</v>
+        <v>95891</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7742,21 +7742,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>660614</v>
+        <v>660701</v>
       </c>
       <c r="R65" t="n">
-        <v>6642042</v>
+        <v>6642183</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7925,10 +7925,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128577878</v>
+        <v>128577889</v>
       </c>
       <c r="B67" t="n">
-        <v>95891</v>
+        <v>92776</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7936,21 +7936,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>660701</v>
+        <v>660614</v>
       </c>
       <c r="R67" t="n">
-        <v>6642183</v>
+        <v>6642042</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -8410,10 +8410,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128577894</v>
+        <v>128577871</v>
       </c>
       <c r="B72" t="n">
-        <v>92776</v>
+        <v>95891</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8421,21 +8421,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8445,10 +8445,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>660638</v>
+        <v>660627</v>
       </c>
       <c r="R72" t="n">
-        <v>6641974</v>
+        <v>6642017</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128577886</v>
+        <v>128577908</v>
       </c>
       <c r="B73" t="n">
-        <v>92776</v>
+        <v>90725</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8518,21 +8518,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5964</v>
+        <v>749</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Alsopp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Gyrodon lividus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Bull.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8542,10 +8542,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>660635</v>
+        <v>660712</v>
       </c>
       <c r="R73" t="n">
-        <v>6641930</v>
+        <v>6642212</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8604,10 +8604,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128577871</v>
+        <v>128577894</v>
       </c>
       <c r="B74" t="n">
-        <v>95891</v>
+        <v>92776</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8615,21 +8615,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>660627</v>
+        <v>660638</v>
       </c>
       <c r="R74" t="n">
-        <v>6642017</v>
+        <v>6641974</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8701,10 +8701,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128577908</v>
+        <v>128577886</v>
       </c>
       <c r="B75" t="n">
-        <v>90725</v>
+        <v>92776</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8712,21 +8712,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>749</v>
+        <v>5964</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Alsopp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Gyrodon lividus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Bull.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>660712</v>
+        <v>660635</v>
       </c>
       <c r="R75" t="n">
-        <v>6642212</v>
+        <v>6641930</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -9288,10 +9288,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128577896</v>
+        <v>128577823</v>
       </c>
       <c r="B81" t="n">
-        <v>92776</v>
+        <v>92387</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9299,21 +9299,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>660619</v>
+        <v>660679</v>
       </c>
       <c r="R81" t="n">
-        <v>6642007</v>
+        <v>6642181</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -9385,10 +9385,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128577823</v>
+        <v>128577880</v>
       </c>
       <c r="B82" t="n">
-        <v>92387</v>
+        <v>95891</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9396,21 +9396,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4769</v>
+        <v>2671</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>660679</v>
+        <v>660697</v>
       </c>
       <c r="R82" t="n">
-        <v>6642181</v>
+        <v>6642175</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9482,10 +9482,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128577880</v>
+        <v>128577896</v>
       </c>
       <c r="B83" t="n">
-        <v>95891</v>
+        <v>92776</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9493,21 +9493,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9517,10 +9517,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>660697</v>
+        <v>660619</v>
       </c>
       <c r="R83" t="n">
-        <v>6642175</v>
+        <v>6642007</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9579,10 +9579,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128577898</v>
+        <v>128577877</v>
       </c>
       <c r="B84" t="n">
-        <v>92776</v>
+        <v>95891</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9590,21 +9590,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9614,10 +9614,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>660597</v>
+        <v>660666</v>
       </c>
       <c r="R84" t="n">
-        <v>6642016</v>
+        <v>6642164</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -9676,10 +9676,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128577877</v>
+        <v>128577898</v>
       </c>
       <c r="B85" t="n">
-        <v>95891</v>
+        <v>92776</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9687,21 +9687,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>660666</v>
+        <v>660597</v>
       </c>
       <c r="R85" t="n">
-        <v>6642164</v>
+        <v>6642016</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -6955,32 +6955,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128577843</v>
+        <v>128577885</v>
       </c>
       <c r="B57" t="n">
-        <v>92130</v>
+        <v>90913</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1527</v>
+        <v>3286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>660556</v>
+        <v>660621</v>
       </c>
       <c r="R57" t="n">
-        <v>6642090</v>
+        <v>6642044</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7052,32 +7052,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128577892</v>
+        <v>128577843</v>
       </c>
       <c r="B58" t="n">
-        <v>92776</v>
+        <v>92130</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5964</v>
+        <v>1527</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7087,10 +7087,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>660554</v>
+        <v>660556</v>
       </c>
       <c r="R58" t="n">
-        <v>6642138</v>
+        <v>6642090</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7149,32 +7149,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128577885</v>
+        <v>128577892</v>
       </c>
       <c r="B59" t="n">
-        <v>90913</v>
+        <v>92776</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3286</v>
+        <v>5964</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>660621</v>
+        <v>660554</v>
       </c>
       <c r="R59" t="n">
-        <v>6642044</v>
+        <v>6642138</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7246,32 +7246,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128577882</v>
+        <v>128577853</v>
       </c>
       <c r="B60" t="n">
-        <v>95891</v>
+        <v>86944</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2671</v>
+        <v>3739</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>660709</v>
+        <v>660617</v>
       </c>
       <c r="R60" t="n">
-        <v>6642203</v>
+        <v>6642063</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7343,32 +7343,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128577817</v>
+        <v>128577816</v>
       </c>
       <c r="B61" t="n">
-        <v>92738</v>
+        <v>86944</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4363</v>
+        <v>3739</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>660620</v>
+        <v>660612</v>
       </c>
       <c r="R61" t="n">
         <v>6642049</v>
@@ -7440,32 +7440,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128577853</v>
+        <v>128577882</v>
       </c>
       <c r="B62" t="n">
-        <v>86944</v>
+        <v>95891</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3739</v>
+        <v>2671</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>660617</v>
+        <v>660709</v>
       </c>
       <c r="R62" t="n">
-        <v>6642063</v>
+        <v>6642203</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7537,32 +7537,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128577816</v>
+        <v>128577817</v>
       </c>
       <c r="B63" t="n">
-        <v>86944</v>
+        <v>92738</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3739</v>
+        <v>4363</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7572,7 +7572,7 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>660612</v>
+        <v>660620</v>
       </c>
       <c r="R63" t="n">
         <v>6642049</v>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -6570,7 +6570,7 @@
         <v>128577897</v>
       </c>
       <c r="B53" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>128577820</v>
       </c>
       <c r="B54" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>128577858</v>
       </c>
       <c r="B55" t="n">
-        <v>91005</v>
+        <v>91011</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>128577905</v>
       </c>
       <c r="B56" t="n">
-        <v>92122</v>
+        <v>92128</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6955,32 +6955,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128577885</v>
+        <v>128577843</v>
       </c>
       <c r="B57" t="n">
-        <v>90913</v>
+        <v>92136</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3286</v>
+        <v>1527</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>660621</v>
+        <v>660556</v>
       </c>
       <c r="R57" t="n">
-        <v>6642044</v>
+        <v>6642090</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7052,32 +7052,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128577843</v>
+        <v>128577885</v>
       </c>
       <c r="B58" t="n">
-        <v>92130</v>
+        <v>90919</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1527</v>
+        <v>3286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7087,10 +7087,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>660556</v>
+        <v>660621</v>
       </c>
       <c r="R58" t="n">
-        <v>6642090</v>
+        <v>6642044</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7152,7 +7152,7 @@
         <v>128577892</v>
       </c>
       <c r="B59" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7246,32 +7246,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128577853</v>
+        <v>128577882</v>
       </c>
       <c r="B60" t="n">
-        <v>86944</v>
+        <v>95897</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3739</v>
+        <v>2671</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>660617</v>
+        <v>660709</v>
       </c>
       <c r="R60" t="n">
-        <v>6642063</v>
+        <v>6642203</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7343,32 +7343,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128577816</v>
+        <v>128577817</v>
       </c>
       <c r="B61" t="n">
-        <v>86944</v>
+        <v>92744</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3739</v>
+        <v>4363</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>660612</v>
+        <v>660620</v>
       </c>
       <c r="R61" t="n">
         <v>6642049</v>
@@ -7440,32 +7440,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128577882</v>
+        <v>128577853</v>
       </c>
       <c r="B62" t="n">
-        <v>95891</v>
+        <v>86948</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2671</v>
+        <v>3739</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>660709</v>
+        <v>660617</v>
       </c>
       <c r="R62" t="n">
-        <v>6642203</v>
+        <v>6642063</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7537,32 +7537,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128577817</v>
+        <v>128577816</v>
       </c>
       <c r="B63" t="n">
-        <v>92738</v>
+        <v>86948</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4363</v>
+        <v>3739</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7572,7 +7572,7 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>660620</v>
+        <v>660612</v>
       </c>
       <c r="R63" t="n">
         <v>6642049</v>
@@ -7637,7 +7637,7 @@
         <v>128577884</v>
       </c>
       <c r="B64" t="n">
-        <v>95891</v>
+        <v>95897</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>128577878</v>
       </c>
       <c r="B65" t="n">
-        <v>95891</v>
+        <v>95897</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>128577881</v>
       </c>
       <c r="B66" t="n">
-        <v>95891</v>
+        <v>95897</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>128577889</v>
       </c>
       <c r="B67" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>128577833</v>
       </c>
       <c r="B68" t="n">
-        <v>100660</v>
+        <v>100668</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>128577828</v>
       </c>
       <c r="B69" t="n">
-        <v>91054</v>
+        <v>91060</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>128577904</v>
       </c>
       <c r="B70" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>128577824</v>
       </c>
       <c r="B71" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8410,10 +8410,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128577871</v>
+        <v>128577908</v>
       </c>
       <c r="B72" t="n">
-        <v>95891</v>
+        <v>90731</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8421,21 +8421,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2671</v>
+        <v>749</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Alsopp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Gyrodon lividus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Bull.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8445,10 +8445,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>660627</v>
+        <v>660712</v>
       </c>
       <c r="R72" t="n">
-        <v>6642017</v>
+        <v>6642212</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128577908</v>
+        <v>128577894</v>
       </c>
       <c r="B73" t="n">
-        <v>90725</v>
+        <v>92782</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8518,21 +8518,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>749</v>
+        <v>5964</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Alsopp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gyrodon lividus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Bull.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8542,10 +8542,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>660712</v>
+        <v>660638</v>
       </c>
       <c r="R73" t="n">
-        <v>6642212</v>
+        <v>6641974</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8604,10 +8604,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128577894</v>
+        <v>128577886</v>
       </c>
       <c r="B74" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>660638</v>
+        <v>660635</v>
       </c>
       <c r="R74" t="n">
-        <v>6641974</v>
+        <v>6641930</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8701,10 +8701,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128577886</v>
+        <v>128577871</v>
       </c>
       <c r="B75" t="n">
-        <v>92776</v>
+        <v>95897</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8712,21 +8712,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>660635</v>
+        <v>660627</v>
       </c>
       <c r="R75" t="n">
-        <v>6641930</v>
+        <v>6642017</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8801,7 +8801,7 @@
         <v>128577825</v>
       </c>
       <c r="B76" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>128577893</v>
       </c>
       <c r="B77" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>128577875</v>
       </c>
       <c r="B78" t="n">
-        <v>95891</v>
+        <v>95897</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>128577818</v>
       </c>
       <c r="B79" t="n">
-        <v>92738</v>
+        <v>92744</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>128577888</v>
       </c>
       <c r="B80" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9288,10 +9288,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128577823</v>
+        <v>128577880</v>
       </c>
       <c r="B81" t="n">
-        <v>92387</v>
+        <v>95897</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9299,21 +9299,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4769</v>
+        <v>2671</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>660679</v>
+        <v>660697</v>
       </c>
       <c r="R81" t="n">
-        <v>6642181</v>
+        <v>6642175</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -9385,10 +9385,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128577880</v>
+        <v>128577823</v>
       </c>
       <c r="B82" t="n">
-        <v>95891</v>
+        <v>92393</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9396,21 +9396,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2671</v>
+        <v>4769</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>660697</v>
+        <v>660679</v>
       </c>
       <c r="R82" t="n">
-        <v>6642175</v>
+        <v>6642181</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9485,7 +9485,7 @@
         <v>128577896</v>
       </c>
       <c r="B83" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>128577877</v>
       </c>
       <c r="B84" t="n">
-        <v>95891</v>
+        <v>95897</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>128577898</v>
       </c>
       <c r="B85" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>128577827</v>
       </c>
       <c r="B86" t="n">
-        <v>91054</v>
+        <v>91060</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>128577891</v>
       </c>
       <c r="B87" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>128577890</v>
       </c>
       <c r="B88" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -6570,7 +6570,7 @@
         <v>128577897</v>
       </c>
       <c r="B53" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>128577820</v>
       </c>
       <c r="B54" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>128577858</v>
       </c>
       <c r="B55" t="n">
-        <v>91011</v>
+        <v>91017</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>128577905</v>
       </c>
       <c r="B56" t="n">
-        <v>92128</v>
+        <v>92134</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6955,32 +6955,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128577843</v>
+        <v>128577885</v>
       </c>
       <c r="B57" t="n">
-        <v>92136</v>
+        <v>90925</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1527</v>
+        <v>3286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>660556</v>
+        <v>660621</v>
       </c>
       <c r="R57" t="n">
-        <v>6642090</v>
+        <v>6642044</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7052,32 +7052,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128577885</v>
+        <v>128577892</v>
       </c>
       <c r="B58" t="n">
-        <v>90919</v>
+        <v>92788</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3286</v>
+        <v>5964</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7087,10 +7087,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>660621</v>
+        <v>660554</v>
       </c>
       <c r="R58" t="n">
-        <v>6642044</v>
+        <v>6642138</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7149,32 +7149,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128577892</v>
+        <v>128577843</v>
       </c>
       <c r="B59" t="n">
-        <v>92782</v>
+        <v>92142</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5964</v>
+        <v>1527</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>660554</v>
+        <v>660556</v>
       </c>
       <c r="R59" t="n">
-        <v>6642138</v>
+        <v>6642090</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7246,32 +7246,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128577882</v>
+        <v>128577853</v>
       </c>
       <c r="B60" t="n">
-        <v>95897</v>
+        <v>86954</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2671</v>
+        <v>3739</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>660709</v>
+        <v>660617</v>
       </c>
       <c r="R60" t="n">
-        <v>6642203</v>
+        <v>6642063</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7346,7 +7346,7 @@
         <v>128577817</v>
       </c>
       <c r="B61" t="n">
-        <v>92744</v>
+        <v>92750</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7440,10 +7440,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128577853</v>
+        <v>128577816</v>
       </c>
       <c r="B62" t="n">
-        <v>86948</v>
+        <v>86954</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>660617</v>
+        <v>660612</v>
       </c>
       <c r="R62" t="n">
-        <v>6642063</v>
+        <v>6642049</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7537,32 +7537,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128577816</v>
+        <v>128577882</v>
       </c>
       <c r="B63" t="n">
-        <v>86948</v>
+        <v>95903</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3739</v>
+        <v>2671</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>660612</v>
+        <v>660709</v>
       </c>
       <c r="R63" t="n">
-        <v>6642049</v>
+        <v>6642203</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7634,10 +7634,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128577884</v>
+        <v>128577833</v>
       </c>
       <c r="B64" t="n">
-        <v>95897</v>
+        <v>100674</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7645,21 +7645,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7669,10 +7669,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>660554</v>
+        <v>660698</v>
       </c>
       <c r="R64" t="n">
-        <v>6642138</v>
+        <v>6642170</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7731,10 +7731,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128577878</v>
+        <v>128577884</v>
       </c>
       <c r="B65" t="n">
-        <v>95897</v>
+        <v>95903</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>660701</v>
+        <v>660554</v>
       </c>
       <c r="R65" t="n">
-        <v>6642183</v>
+        <v>6642138</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7828,10 +7828,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128577881</v>
+        <v>128577878</v>
       </c>
       <c r="B66" t="n">
-        <v>95897</v>
+        <v>95903</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>660699</v>
+        <v>660701</v>
       </c>
       <c r="R66" t="n">
-        <v>6642205</v>
+        <v>6642183</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7925,10 +7925,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128577889</v>
+        <v>128577881</v>
       </c>
       <c r="B67" t="n">
-        <v>92782</v>
+        <v>95903</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7936,21 +7936,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>660614</v>
+        <v>660699</v>
       </c>
       <c r="R67" t="n">
-        <v>6642042</v>
+        <v>6642205</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -8022,10 +8022,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128577833</v>
+        <v>128577889</v>
       </c>
       <c r="B68" t="n">
-        <v>100668</v>
+        <v>92788</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8033,21 +8033,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8057,10 +8057,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>660698</v>
+        <v>660614</v>
       </c>
       <c r="R68" t="n">
-        <v>6642170</v>
+        <v>6642042</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8122,7 +8122,7 @@
         <v>128577828</v>
       </c>
       <c r="B69" t="n">
-        <v>91060</v>
+        <v>91066</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>128577904</v>
       </c>
       <c r="B70" t="n">
-        <v>92087</v>
+        <v>92093</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>128577824</v>
       </c>
       <c r="B71" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8410,10 +8410,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128577908</v>
+        <v>128577871</v>
       </c>
       <c r="B72" t="n">
-        <v>90731</v>
+        <v>95903</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8421,21 +8421,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>749</v>
+        <v>2671</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Alsopp</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Gyrodon lividus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Bull.:Fr.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8445,10 +8445,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>660712</v>
+        <v>660627</v>
       </c>
       <c r="R72" t="n">
-        <v>6642212</v>
+        <v>6642017</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128577894</v>
+        <v>128577908</v>
       </c>
       <c r="B73" t="n">
-        <v>92782</v>
+        <v>90737</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8518,21 +8518,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5964</v>
+        <v>749</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Alsopp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Gyrodon lividus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Bull.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8542,10 +8542,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>660638</v>
+        <v>660712</v>
       </c>
       <c r="R73" t="n">
-        <v>6641974</v>
+        <v>6642212</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8604,10 +8604,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128577886</v>
+        <v>128577894</v>
       </c>
       <c r="B74" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>660635</v>
+        <v>660638</v>
       </c>
       <c r="R74" t="n">
-        <v>6641930</v>
+        <v>6641974</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8701,10 +8701,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128577871</v>
+        <v>128577886</v>
       </c>
       <c r="B75" t="n">
-        <v>95897</v>
+        <v>92788</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8712,21 +8712,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>660627</v>
+        <v>660635</v>
       </c>
       <c r="R75" t="n">
-        <v>6642017</v>
+        <v>6641930</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8798,10 +8798,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128577825</v>
+        <v>128577893</v>
       </c>
       <c r="B76" t="n">
-        <v>92393</v>
+        <v>92788</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8809,21 +8809,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8833,10 +8833,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>660562</v>
+        <v>660559</v>
       </c>
       <c r="R76" t="n">
-        <v>6642094</v>
+        <v>6642135</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8895,10 +8895,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128577893</v>
+        <v>128577825</v>
       </c>
       <c r="B77" t="n">
-        <v>92782</v>
+        <v>92399</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8906,21 +8906,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>660559</v>
+        <v>660562</v>
       </c>
       <c r="R77" t="n">
-        <v>6642135</v>
+        <v>6642094</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8995,7 +8995,7 @@
         <v>128577875</v>
       </c>
       <c r="B78" t="n">
-        <v>95897</v>
+        <v>95903</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>128577818</v>
       </c>
       <c r="B79" t="n">
-        <v>92744</v>
+        <v>92750</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>128577888</v>
       </c>
       <c r="B80" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9288,10 +9288,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128577880</v>
+        <v>128577823</v>
       </c>
       <c r="B81" t="n">
-        <v>95897</v>
+        <v>92399</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9299,21 +9299,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2671</v>
+        <v>4769</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>660697</v>
+        <v>660679</v>
       </c>
       <c r="R81" t="n">
-        <v>6642175</v>
+        <v>6642181</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -9385,10 +9385,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128577823</v>
+        <v>128577896</v>
       </c>
       <c r="B82" t="n">
-        <v>92393</v>
+        <v>92788</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9396,21 +9396,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>660679</v>
+        <v>660619</v>
       </c>
       <c r="R82" t="n">
-        <v>6642181</v>
+        <v>6642007</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9482,10 +9482,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128577896</v>
+        <v>128577880</v>
       </c>
       <c r="B83" t="n">
-        <v>92782</v>
+        <v>95903</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9493,21 +9493,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9517,10 +9517,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>660619</v>
+        <v>660697</v>
       </c>
       <c r="R83" t="n">
-        <v>6642007</v>
+        <v>6642175</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9582,7 +9582,7 @@
         <v>128577877</v>
       </c>
       <c r="B84" t="n">
-        <v>95897</v>
+        <v>95903</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>128577898</v>
       </c>
       <c r="B85" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>128577827</v>
       </c>
       <c r="B86" t="n">
-        <v>91060</v>
+        <v>91066</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>128577891</v>
       </c>
       <c r="B87" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>128577890</v>
       </c>
       <c r="B88" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -7343,32 +7343,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128577817</v>
+        <v>128577816</v>
       </c>
       <c r="B61" t="n">
-        <v>92750</v>
+        <v>86954</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4363</v>
+        <v>3739</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>660620</v>
+        <v>660612</v>
       </c>
       <c r="R61" t="n">
         <v>6642049</v>
@@ -7440,32 +7440,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128577816</v>
+        <v>128577817</v>
       </c>
       <c r="B62" t="n">
-        <v>86954</v>
+        <v>92750</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3739</v>
+        <v>4363</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>660612</v>
+        <v>660620</v>
       </c>
       <c r="R62" t="n">
         <v>6642049</v>
@@ -7634,10 +7634,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128577833</v>
+        <v>128577889</v>
       </c>
       <c r="B64" t="n">
-        <v>100674</v>
+        <v>92788</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7645,21 +7645,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7669,10 +7669,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>660698</v>
+        <v>660614</v>
       </c>
       <c r="R64" t="n">
-        <v>6642170</v>
+        <v>6642042</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -8022,10 +8022,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128577889</v>
+        <v>128577833</v>
       </c>
       <c r="B68" t="n">
-        <v>92788</v>
+        <v>100674</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8033,21 +8033,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8057,10 +8057,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>660614</v>
+        <v>660698</v>
       </c>
       <c r="R68" t="n">
-        <v>6642042</v>
+        <v>6642170</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8798,10 +8798,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128577893</v>
+        <v>128577825</v>
       </c>
       <c r="B76" t="n">
-        <v>92788</v>
+        <v>92399</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8809,21 +8809,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8833,10 +8833,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>660559</v>
+        <v>660562</v>
       </c>
       <c r="R76" t="n">
-        <v>6642135</v>
+        <v>6642094</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8895,10 +8895,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128577825</v>
+        <v>128577893</v>
       </c>
       <c r="B77" t="n">
-        <v>92399</v>
+        <v>92788</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8906,21 +8906,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>660562</v>
+        <v>660559</v>
       </c>
       <c r="R77" t="n">
-        <v>6642094</v>
+        <v>6642135</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -6570,7 +6570,7 @@
         <v>128577897</v>
       </c>
       <c r="B53" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>128577820</v>
       </c>
       <c r="B54" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>128577858</v>
       </c>
       <c r="B55" t="n">
-        <v>91017</v>
+        <v>91019</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>128577905</v>
       </c>
       <c r="B56" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6955,32 +6955,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128577885</v>
+        <v>128577892</v>
       </c>
       <c r="B57" t="n">
-        <v>90925</v>
+        <v>92790</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3286</v>
+        <v>5964</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>660621</v>
+        <v>660554</v>
       </c>
       <c r="R57" t="n">
-        <v>6642044</v>
+        <v>6642138</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7052,32 +7052,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128577892</v>
+        <v>128577843</v>
       </c>
       <c r="B58" t="n">
-        <v>92788</v>
+        <v>92144</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5964</v>
+        <v>1527</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7087,10 +7087,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>660554</v>
+        <v>660556</v>
       </c>
       <c r="R58" t="n">
-        <v>6642138</v>
+        <v>6642090</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7149,32 +7149,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128577843</v>
+        <v>128577885</v>
       </c>
       <c r="B59" t="n">
-        <v>92142</v>
+        <v>90927</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1527</v>
+        <v>3286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>660556</v>
+        <v>660621</v>
       </c>
       <c r="R59" t="n">
-        <v>6642090</v>
+        <v>6642044</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7246,32 +7246,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128577853</v>
+        <v>128577882</v>
       </c>
       <c r="B60" t="n">
-        <v>86954</v>
+        <v>95905</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3739</v>
+        <v>2671</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>660617</v>
+        <v>660709</v>
       </c>
       <c r="R60" t="n">
-        <v>6642063</v>
+        <v>6642203</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7346,7 +7346,7 @@
         <v>128577816</v>
       </c>
       <c r="B61" t="n">
-        <v>86954</v>
+        <v>86956</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>128577817</v>
       </c>
       <c r="B62" t="n">
-        <v>92750</v>
+        <v>92752</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7537,32 +7537,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128577882</v>
+        <v>128577853</v>
       </c>
       <c r="B63" t="n">
-        <v>95903</v>
+        <v>86956</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2671</v>
+        <v>3739</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>660709</v>
+        <v>660617</v>
       </c>
       <c r="R63" t="n">
-        <v>6642203</v>
+        <v>6642063</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7634,10 +7634,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128577889</v>
+        <v>128577884</v>
       </c>
       <c r="B64" t="n">
-        <v>92788</v>
+        <v>95905</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7645,21 +7645,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7669,10 +7669,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>660614</v>
+        <v>660554</v>
       </c>
       <c r="R64" t="n">
-        <v>6642042</v>
+        <v>6642138</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7731,10 +7731,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128577884</v>
+        <v>128577878</v>
       </c>
       <c r="B65" t="n">
-        <v>95903</v>
+        <v>95905</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>660554</v>
+        <v>660701</v>
       </c>
       <c r="R65" t="n">
-        <v>6642138</v>
+        <v>6642183</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7828,10 +7828,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128577878</v>
+        <v>128577881</v>
       </c>
       <c r="B66" t="n">
-        <v>95903</v>
+        <v>95905</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>660701</v>
+        <v>660699</v>
       </c>
       <c r="R66" t="n">
-        <v>6642183</v>
+        <v>6642205</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7925,10 +7925,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128577881</v>
+        <v>128577889</v>
       </c>
       <c r="B67" t="n">
-        <v>95903</v>
+        <v>92790</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7936,21 +7936,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>660699</v>
+        <v>660614</v>
       </c>
       <c r="R67" t="n">
-        <v>6642205</v>
+        <v>6642042</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -8025,7 +8025,7 @@
         <v>128577833</v>
       </c>
       <c r="B68" t="n">
-        <v>100674</v>
+        <v>100679</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>128577828</v>
       </c>
       <c r="B69" t="n">
-        <v>91066</v>
+        <v>91068</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>128577904</v>
       </c>
       <c r="B70" t="n">
-        <v>92093</v>
+        <v>92095</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>128577824</v>
       </c>
       <c r="B71" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>128577871</v>
       </c>
       <c r="B72" t="n">
-        <v>95903</v>
+        <v>95905</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128577908</v>
+        <v>128577894</v>
       </c>
       <c r="B73" t="n">
-        <v>90737</v>
+        <v>92790</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8518,21 +8518,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>749</v>
+        <v>5964</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Alsopp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gyrodon lividus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Bull.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8542,10 +8542,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>660712</v>
+        <v>660638</v>
       </c>
       <c r="R73" t="n">
-        <v>6642212</v>
+        <v>6641974</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8604,10 +8604,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128577894</v>
+        <v>128577886</v>
       </c>
       <c r="B74" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>660638</v>
+        <v>660635</v>
       </c>
       <c r="R74" t="n">
-        <v>6641974</v>
+        <v>6641930</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8701,10 +8701,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128577886</v>
+        <v>128577908</v>
       </c>
       <c r="B75" t="n">
-        <v>92788</v>
+        <v>90739</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8712,21 +8712,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5964</v>
+        <v>749</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Alsopp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Gyrodon lividus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Bull.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>660635</v>
+        <v>660712</v>
       </c>
       <c r="R75" t="n">
-        <v>6641930</v>
+        <v>6642212</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8798,10 +8798,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128577825</v>
+        <v>128577893</v>
       </c>
       <c r="B76" t="n">
-        <v>92399</v>
+        <v>92790</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8809,21 +8809,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8833,10 +8833,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>660562</v>
+        <v>660559</v>
       </c>
       <c r="R76" t="n">
-        <v>6642094</v>
+        <v>6642135</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8895,10 +8895,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128577893</v>
+        <v>128577825</v>
       </c>
       <c r="B77" t="n">
-        <v>92788</v>
+        <v>92401</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8906,21 +8906,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>660559</v>
+        <v>660562</v>
       </c>
       <c r="R77" t="n">
-        <v>6642135</v>
+        <v>6642094</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8995,7 +8995,7 @@
         <v>128577875</v>
       </c>
       <c r="B78" t="n">
-        <v>95903</v>
+        <v>95905</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9089,10 +9089,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128577818</v>
+        <v>128577888</v>
       </c>
       <c r="B79" t="n">
-        <v>92750</v>
+        <v>92790</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9100,21 +9100,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4363</v>
+        <v>5964</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>660559</v>
+        <v>660615</v>
       </c>
       <c r="R79" t="n">
-        <v>6642143</v>
+        <v>6642026</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -9160,11 +9160,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-19</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>20 fruktkroppar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9191,10 +9186,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128577888</v>
+        <v>128577818</v>
       </c>
       <c r="B80" t="n">
-        <v>92788</v>
+        <v>92752</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9202,21 +9197,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5964</v>
+        <v>4363</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9226,10 +9221,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>660615</v>
+        <v>660559</v>
       </c>
       <c r="R80" t="n">
-        <v>6642026</v>
+        <v>6642143</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -9262,6 +9257,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>20 fruktkroppar</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9291,7 +9291,7 @@
         <v>128577823</v>
       </c>
       <c r="B81" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9385,10 +9385,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128577896</v>
+        <v>128577880</v>
       </c>
       <c r="B82" t="n">
-        <v>92788</v>
+        <v>95905</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9396,21 +9396,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>660619</v>
+        <v>660697</v>
       </c>
       <c r="R82" t="n">
-        <v>6642007</v>
+        <v>6642175</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9482,10 +9482,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128577880</v>
+        <v>128577896</v>
       </c>
       <c r="B83" t="n">
-        <v>95903</v>
+        <v>92790</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9493,21 +9493,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9517,10 +9517,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>660697</v>
+        <v>660619</v>
       </c>
       <c r="R83" t="n">
-        <v>6642175</v>
+        <v>6642007</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9582,7 +9582,7 @@
         <v>128577877</v>
       </c>
       <c r="B84" t="n">
-        <v>95903</v>
+        <v>95905</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>128577898</v>
       </c>
       <c r="B85" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>128577827</v>
       </c>
       <c r="B86" t="n">
-        <v>91066</v>
+        <v>91068</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>128577891</v>
       </c>
       <c r="B87" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>128577890</v>
       </c>
       <c r="B88" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -6955,32 +6955,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128577892</v>
+        <v>128577885</v>
       </c>
       <c r="B57" t="n">
-        <v>92790</v>
+        <v>90927</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5964</v>
+        <v>3286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>660554</v>
+        <v>660621</v>
       </c>
       <c r="R57" t="n">
-        <v>6642138</v>
+        <v>6642044</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7052,32 +7052,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128577843</v>
+        <v>128577892</v>
       </c>
       <c r="B58" t="n">
-        <v>92144</v>
+        <v>92790</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1527</v>
+        <v>5964</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7087,10 +7087,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>660556</v>
+        <v>660554</v>
       </c>
       <c r="R58" t="n">
-        <v>6642090</v>
+        <v>6642138</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7149,32 +7149,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128577885</v>
+        <v>128577843</v>
       </c>
       <c r="B59" t="n">
-        <v>90927</v>
+        <v>92144</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3286</v>
+        <v>1527</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>660621</v>
+        <v>660556</v>
       </c>
       <c r="R59" t="n">
-        <v>6642044</v>
+        <v>6642090</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7343,7 +7343,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128577816</v>
+        <v>128577853</v>
       </c>
       <c r="B61" t="n">
         <v>86956</v>
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>660612</v>
+        <v>660617</v>
       </c>
       <c r="R61" t="n">
-        <v>6642049</v>
+        <v>6642063</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7440,32 +7440,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128577817</v>
+        <v>128577816</v>
       </c>
       <c r="B62" t="n">
-        <v>92752</v>
+        <v>86956</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4363</v>
+        <v>3739</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>660620</v>
+        <v>660612</v>
       </c>
       <c r="R62" t="n">
         <v>6642049</v>
@@ -7537,32 +7537,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128577853</v>
+        <v>128577817</v>
       </c>
       <c r="B63" t="n">
-        <v>86956</v>
+        <v>92752</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3739</v>
+        <v>4363</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>660617</v>
+        <v>660620</v>
       </c>
       <c r="R63" t="n">
-        <v>6642063</v>
+        <v>6642049</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -8025,7 +8025,7 @@
         <v>128577833</v>
       </c>
       <c r="B68" t="n">
-        <v>100679</v>
+        <v>100685</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128577894</v>
+        <v>128577908</v>
       </c>
       <c r="B73" t="n">
-        <v>92790</v>
+        <v>90739</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8518,21 +8518,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5964</v>
+        <v>749</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Alsopp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Gyrodon lividus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Bull.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8542,10 +8542,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>660638</v>
+        <v>660712</v>
       </c>
       <c r="R73" t="n">
-        <v>6641974</v>
+        <v>6642212</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8604,7 +8604,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128577886</v>
+        <v>128577894</v>
       </c>
       <c r="B74" t="n">
         <v>92790</v>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>660635</v>
+        <v>660638</v>
       </c>
       <c r="R74" t="n">
-        <v>6641930</v>
+        <v>6641974</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8701,10 +8701,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128577908</v>
+        <v>128577886</v>
       </c>
       <c r="B75" t="n">
-        <v>90739</v>
+        <v>92790</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8712,21 +8712,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>749</v>
+        <v>5964</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Alsopp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Gyrodon lividus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Bull.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>660712</v>
+        <v>660635</v>
       </c>
       <c r="R75" t="n">
-        <v>6642212</v>
+        <v>6641930</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -9089,10 +9089,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128577888</v>
+        <v>128577818</v>
       </c>
       <c r="B79" t="n">
-        <v>92790</v>
+        <v>92752</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9100,21 +9100,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5964</v>
+        <v>4363</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>660615</v>
+        <v>660559</v>
       </c>
       <c r="R79" t="n">
-        <v>6642026</v>
+        <v>6642143</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -9160,6 +9160,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>20 fruktkroppar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9186,10 +9191,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128577818</v>
+        <v>128577888</v>
       </c>
       <c r="B80" t="n">
-        <v>92752</v>
+        <v>92790</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9197,21 +9202,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4363</v>
+        <v>5964</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9221,10 +9226,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>660559</v>
+        <v>660615</v>
       </c>
       <c r="R80" t="n">
-        <v>6642143</v>
+        <v>6642026</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -9257,11 +9262,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-19</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>20 fruktkroppar</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9288,10 +9288,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128577823</v>
+        <v>128577880</v>
       </c>
       <c r="B81" t="n">
-        <v>92401</v>
+        <v>95905</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9299,21 +9299,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4769</v>
+        <v>2671</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>660679</v>
+        <v>660697</v>
       </c>
       <c r="R81" t="n">
-        <v>6642181</v>
+        <v>6642175</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -9385,10 +9385,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128577880</v>
+        <v>128577896</v>
       </c>
       <c r="B82" t="n">
-        <v>95905</v>
+        <v>92790</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9396,21 +9396,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>660697</v>
+        <v>660619</v>
       </c>
       <c r="R82" t="n">
-        <v>6642175</v>
+        <v>6642007</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9482,10 +9482,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128577896</v>
+        <v>128577823</v>
       </c>
       <c r="B83" t="n">
-        <v>92790</v>
+        <v>92401</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9493,21 +9493,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9517,10 +9517,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>660619</v>
+        <v>660679</v>
       </c>
       <c r="R83" t="n">
-        <v>6642007</v>
+        <v>6642181</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9773,32 +9773,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128577827</v>
+        <v>128577891</v>
       </c>
       <c r="B86" t="n">
-        <v>91068</v>
+        <v>92790</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3086</v>
+        <v>5964</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Auricularia mesenterica</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Dicks.:Fr.) Pers.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9808,10 +9808,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>660698</v>
+        <v>660557</v>
       </c>
       <c r="R86" t="n">
-        <v>6642185</v>
+        <v>6642137</v>
       </c>
       <c r="S86" t="n">
         <v>20</v>
@@ -9870,7 +9870,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128577891</v>
+        <v>128577890</v>
       </c>
       <c r="B87" t="n">
         <v>92790</v>
@@ -9905,10 +9905,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>660557</v>
+        <v>660618</v>
       </c>
       <c r="R87" t="n">
-        <v>6642137</v>
+        <v>6642051</v>
       </c>
       <c r="S87" t="n">
         <v>20</v>
@@ -9967,32 +9967,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128577890</v>
+        <v>128577827</v>
       </c>
       <c r="B88" t="n">
-        <v>92790</v>
+        <v>91068</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5964</v>
+        <v>3086</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Auricularia mesenterica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Dicks.:Fr.) Pers.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10002,10 +10002,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>660618</v>
+        <v>660698</v>
       </c>
       <c r="R88" t="n">
-        <v>6642051</v>
+        <v>6642185</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -7343,32 +7343,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128577853</v>
+        <v>128577817</v>
       </c>
       <c r="B61" t="n">
-        <v>86956</v>
+        <v>92752</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3739</v>
+        <v>4363</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>660617</v>
+        <v>660620</v>
       </c>
       <c r="R61" t="n">
-        <v>6642063</v>
+        <v>6642049</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7440,7 +7440,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128577816</v>
+        <v>128577853</v>
       </c>
       <c r="B62" t="n">
         <v>86956</v>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>660612</v>
+        <v>660617</v>
       </c>
       <c r="R62" t="n">
-        <v>6642049</v>
+        <v>6642063</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7537,32 +7537,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128577817</v>
+        <v>128577816</v>
       </c>
       <c r="B63" t="n">
-        <v>92752</v>
+        <v>86956</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4363</v>
+        <v>3739</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7572,7 +7572,7 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>660620</v>
+        <v>660612</v>
       </c>
       <c r="R63" t="n">
         <v>6642049</v>
@@ -9089,10 +9089,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128577818</v>
+        <v>128577888</v>
       </c>
       <c r="B79" t="n">
-        <v>92752</v>
+        <v>92790</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9100,21 +9100,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4363</v>
+        <v>5964</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>660559</v>
+        <v>660615</v>
       </c>
       <c r="R79" t="n">
-        <v>6642143</v>
+        <v>6642026</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -9160,11 +9160,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-19</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>20 fruktkroppar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9191,10 +9186,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128577888</v>
+        <v>128577818</v>
       </c>
       <c r="B80" t="n">
-        <v>92790</v>
+        <v>92752</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9202,21 +9197,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5964</v>
+        <v>4363</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9226,10 +9221,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>660615</v>
+        <v>660559</v>
       </c>
       <c r="R80" t="n">
-        <v>6642026</v>
+        <v>6642143</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -9262,6 +9257,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>20 fruktkroppar</t>
         </is>
       </c>
       <c r="AD80" t="b">

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -6570,7 +6570,7 @@
         <v>128577897</v>
       </c>
       <c r="B53" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>128577820</v>
       </c>
       <c r="B54" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>128577858</v>
       </c>
       <c r="B55" t="n">
-        <v>91019</v>
+        <v>91020</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>128577905</v>
       </c>
       <c r="B56" t="n">
-        <v>92136</v>
+        <v>92137</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6955,32 +6955,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128577885</v>
+        <v>128577843</v>
       </c>
       <c r="B57" t="n">
-        <v>90927</v>
+        <v>92145</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3286</v>
+        <v>1527</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>660621</v>
+        <v>660556</v>
       </c>
       <c r="R57" t="n">
-        <v>6642044</v>
+        <v>6642090</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7052,32 +7052,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128577892</v>
+        <v>128577885</v>
       </c>
       <c r="B58" t="n">
-        <v>92790</v>
+        <v>90928</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5964</v>
+        <v>3286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7087,10 +7087,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>660554</v>
+        <v>660621</v>
       </c>
       <c r="R58" t="n">
-        <v>6642138</v>
+        <v>6642044</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7149,32 +7149,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128577843</v>
+        <v>128577892</v>
       </c>
       <c r="B59" t="n">
-        <v>92144</v>
+        <v>92791</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1527</v>
+        <v>5964</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>660556</v>
+        <v>660554</v>
       </c>
       <c r="R59" t="n">
-        <v>6642090</v>
+        <v>6642138</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7249,7 +7249,7 @@
         <v>128577882</v>
       </c>
       <c r="B60" t="n">
-        <v>95905</v>
+        <v>95906</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7343,32 +7343,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128577817</v>
+        <v>128577853</v>
       </c>
       <c r="B61" t="n">
-        <v>92752</v>
+        <v>86956</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4363</v>
+        <v>3739</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>660620</v>
+        <v>660617</v>
       </c>
       <c r="R61" t="n">
-        <v>6642049</v>
+        <v>6642063</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7440,7 +7440,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128577853</v>
+        <v>128577816</v>
       </c>
       <c r="B62" t="n">
         <v>86956</v>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>660617</v>
+        <v>660612</v>
       </c>
       <c r="R62" t="n">
-        <v>6642063</v>
+        <v>6642049</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7537,32 +7537,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128577816</v>
+        <v>128577817</v>
       </c>
       <c r="B63" t="n">
-        <v>86956</v>
+        <v>92753</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3739</v>
+        <v>4363</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7572,7 +7572,7 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>660612</v>
+        <v>660620</v>
       </c>
       <c r="R63" t="n">
         <v>6642049</v>
@@ -7634,10 +7634,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128577884</v>
+        <v>128577833</v>
       </c>
       <c r="B64" t="n">
-        <v>95905</v>
+        <v>100686</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7645,21 +7645,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7669,10 +7669,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>660554</v>
+        <v>660698</v>
       </c>
       <c r="R64" t="n">
-        <v>6642138</v>
+        <v>6642170</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7731,10 +7731,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128577878</v>
+        <v>128577884</v>
       </c>
       <c r="B65" t="n">
-        <v>95905</v>
+        <v>95906</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>660701</v>
+        <v>660554</v>
       </c>
       <c r="R65" t="n">
-        <v>6642183</v>
+        <v>6642138</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7828,10 +7828,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128577881</v>
+        <v>128577878</v>
       </c>
       <c r="B66" t="n">
-        <v>95905</v>
+        <v>95906</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>660699</v>
+        <v>660701</v>
       </c>
       <c r="R66" t="n">
-        <v>6642205</v>
+        <v>6642183</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7925,10 +7925,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128577889</v>
+        <v>128577881</v>
       </c>
       <c r="B67" t="n">
-        <v>92790</v>
+        <v>95906</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7936,21 +7936,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>660614</v>
+        <v>660699</v>
       </c>
       <c r="R67" t="n">
-        <v>6642042</v>
+        <v>6642205</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -8022,10 +8022,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128577833</v>
+        <v>128577889</v>
       </c>
       <c r="B68" t="n">
-        <v>100685</v>
+        <v>92791</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8033,21 +8033,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8057,10 +8057,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>660698</v>
+        <v>660614</v>
       </c>
       <c r="R68" t="n">
-        <v>6642170</v>
+        <v>6642042</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8122,7 +8122,7 @@
         <v>128577828</v>
       </c>
       <c r="B69" t="n">
-        <v>91068</v>
+        <v>91069</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>128577904</v>
       </c>
       <c r="B70" t="n">
-        <v>92095</v>
+        <v>92096</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>128577824</v>
       </c>
       <c r="B71" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>128577871</v>
       </c>
       <c r="B72" t="n">
-        <v>95905</v>
+        <v>95906</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>128577908</v>
       </c>
       <c r="B73" t="n">
-        <v>90739</v>
+        <v>90740</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>128577894</v>
       </c>
       <c r="B74" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>128577886</v>
       </c>
       <c r="B75" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8798,10 +8798,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128577893</v>
+        <v>128577825</v>
       </c>
       <c r="B76" t="n">
-        <v>92790</v>
+        <v>92402</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8809,21 +8809,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8833,10 +8833,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>660559</v>
+        <v>660562</v>
       </c>
       <c r="R76" t="n">
-        <v>6642135</v>
+        <v>6642094</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8895,10 +8895,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128577825</v>
+        <v>128577893</v>
       </c>
       <c r="B77" t="n">
-        <v>92401</v>
+        <v>92791</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8906,21 +8906,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>660562</v>
+        <v>660559</v>
       </c>
       <c r="R77" t="n">
-        <v>6642094</v>
+        <v>6642135</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8995,7 +8995,7 @@
         <v>128577875</v>
       </c>
       <c r="B78" t="n">
-        <v>95905</v>
+        <v>95906</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>128577888</v>
       </c>
       <c r="B79" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>128577818</v>
       </c>
       <c r="B80" t="n">
-        <v>92752</v>
+        <v>92753</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9288,10 +9288,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128577880</v>
+        <v>128577896</v>
       </c>
       <c r="B81" t="n">
-        <v>95905</v>
+        <v>92791</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9299,21 +9299,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>660697</v>
+        <v>660619</v>
       </c>
       <c r="R81" t="n">
-        <v>6642175</v>
+        <v>6642007</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -9385,10 +9385,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128577896</v>
+        <v>128577880</v>
       </c>
       <c r="B82" t="n">
-        <v>92790</v>
+        <v>95906</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9396,21 +9396,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>660619</v>
+        <v>660697</v>
       </c>
       <c r="R82" t="n">
-        <v>6642007</v>
+        <v>6642175</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9485,7 +9485,7 @@
         <v>128577823</v>
       </c>
       <c r="B83" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9579,10 +9579,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128577877</v>
+        <v>128577898</v>
       </c>
       <c r="B84" t="n">
-        <v>95905</v>
+        <v>92791</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9590,21 +9590,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9614,10 +9614,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>660666</v>
+        <v>660597</v>
       </c>
       <c r="R84" t="n">
-        <v>6642164</v>
+        <v>6642016</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -9676,10 +9676,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128577898</v>
+        <v>128577877</v>
       </c>
       <c r="B85" t="n">
-        <v>92790</v>
+        <v>95906</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9687,21 +9687,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>660597</v>
+        <v>660666</v>
       </c>
       <c r="R85" t="n">
-        <v>6642016</v>
+        <v>6642164</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -9773,32 +9773,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128577891</v>
+        <v>128577827</v>
       </c>
       <c r="B86" t="n">
-        <v>92790</v>
+        <v>91069</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5964</v>
+        <v>3086</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Auricularia mesenterica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Dicks.:Fr.) Pers.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9808,10 +9808,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>660557</v>
+        <v>660698</v>
       </c>
       <c r="R86" t="n">
-        <v>6642137</v>
+        <v>6642185</v>
       </c>
       <c r="S86" t="n">
         <v>20</v>
@@ -9870,10 +9870,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128577890</v>
+        <v>128577891</v>
       </c>
       <c r="B87" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9905,10 +9905,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>660618</v>
+        <v>660557</v>
       </c>
       <c r="R87" t="n">
-        <v>6642051</v>
+        <v>6642137</v>
       </c>
       <c r="S87" t="n">
         <v>20</v>
@@ -9967,32 +9967,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128577827</v>
+        <v>128577890</v>
       </c>
       <c r="B88" t="n">
-        <v>91068</v>
+        <v>92791</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3086</v>
+        <v>5964</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Auricularia mesenterica</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Dicks.:Fr.) Pers.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10002,10 +10002,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>660698</v>
+        <v>660618</v>
       </c>
       <c r="R88" t="n">
-        <v>6642185</v>
+        <v>6642051</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -6570,7 +6570,7 @@
         <v>128577897</v>
       </c>
       <c r="B53" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>128577820</v>
       </c>
       <c r="B54" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>128577858</v>
       </c>
       <c r="B55" t="n">
-        <v>91020</v>
+        <v>91047</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>128577905</v>
       </c>
       <c r="B56" t="n">
-        <v>92137</v>
+        <v>92164</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6955,32 +6955,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128577843</v>
+        <v>128577892</v>
       </c>
       <c r="B57" t="n">
-        <v>92145</v>
+        <v>92818</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1527</v>
+        <v>5964</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>660556</v>
+        <v>660554</v>
       </c>
       <c r="R57" t="n">
-        <v>6642090</v>
+        <v>6642138</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7055,7 +7055,7 @@
         <v>128577885</v>
       </c>
       <c r="B58" t="n">
-        <v>90928</v>
+        <v>90955</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7149,32 +7149,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128577892</v>
+        <v>128577843</v>
       </c>
       <c r="B59" t="n">
-        <v>92791</v>
+        <v>92172</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5964</v>
+        <v>1527</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>660554</v>
+        <v>660556</v>
       </c>
       <c r="R59" t="n">
-        <v>6642138</v>
+        <v>6642090</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7246,32 +7246,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128577882</v>
+        <v>128577853</v>
       </c>
       <c r="B60" t="n">
-        <v>95906</v>
+        <v>86983</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2671</v>
+        <v>3739</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>660709</v>
+        <v>660617</v>
       </c>
       <c r="R60" t="n">
-        <v>6642203</v>
+        <v>6642063</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7343,32 +7343,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128577853</v>
+        <v>128577817</v>
       </c>
       <c r="B61" t="n">
-        <v>86956</v>
+        <v>92780</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3739</v>
+        <v>4363</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>660617</v>
+        <v>660620</v>
       </c>
       <c r="R61" t="n">
-        <v>6642063</v>
+        <v>6642049</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7443,7 +7443,7 @@
         <v>128577816</v>
       </c>
       <c r="B62" t="n">
-        <v>86956</v>
+        <v>86983</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7537,10 +7537,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128577817</v>
+        <v>128577882</v>
       </c>
       <c r="B63" t="n">
-        <v>92753</v>
+        <v>95933</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7548,21 +7548,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4363</v>
+        <v>2671</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>660620</v>
+        <v>660709</v>
       </c>
       <c r="R63" t="n">
-        <v>6642049</v>
+        <v>6642203</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7634,10 +7634,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128577833</v>
+        <v>128577889</v>
       </c>
       <c r="B64" t="n">
-        <v>100686</v>
+        <v>92818</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7645,21 +7645,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7669,10 +7669,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>660698</v>
+        <v>660614</v>
       </c>
       <c r="R64" t="n">
-        <v>6642170</v>
+        <v>6642042</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7734,7 +7734,7 @@
         <v>128577884</v>
       </c>
       <c r="B65" t="n">
-        <v>95906</v>
+        <v>95933</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>128577878</v>
       </c>
       <c r="B66" t="n">
-        <v>95906</v>
+        <v>95933</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>128577881</v>
       </c>
       <c r="B67" t="n">
-        <v>95906</v>
+        <v>95933</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8022,10 +8022,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128577889</v>
+        <v>128577833</v>
       </c>
       <c r="B68" t="n">
-        <v>92791</v>
+        <v>100713</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8033,21 +8033,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8057,10 +8057,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>660614</v>
+        <v>660698</v>
       </c>
       <c r="R68" t="n">
-        <v>6642042</v>
+        <v>6642170</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8122,7 +8122,7 @@
         <v>128577828</v>
       </c>
       <c r="B69" t="n">
-        <v>91069</v>
+        <v>91096</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>128577904</v>
       </c>
       <c r="B70" t="n">
-        <v>92096</v>
+        <v>92123</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>128577824</v>
       </c>
       <c r="B71" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8410,10 +8410,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128577871</v>
+        <v>128577908</v>
       </c>
       <c r="B72" t="n">
-        <v>95906</v>
+        <v>90767</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8421,21 +8421,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2671</v>
+        <v>749</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Alsopp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Gyrodon lividus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Bull.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8445,10 +8445,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>660627</v>
+        <v>660712</v>
       </c>
       <c r="R72" t="n">
-        <v>6642017</v>
+        <v>6642212</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128577908</v>
+        <v>128577871</v>
       </c>
       <c r="B73" t="n">
-        <v>90740</v>
+        <v>95933</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8518,21 +8518,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>749</v>
+        <v>2671</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Alsopp</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gyrodon lividus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Bull.:Fr.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8542,10 +8542,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>660712</v>
+        <v>660627</v>
       </c>
       <c r="R73" t="n">
-        <v>6642212</v>
+        <v>6642017</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8607,7 +8607,7 @@
         <v>128577894</v>
       </c>
       <c r="B74" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>128577886</v>
       </c>
       <c r="B75" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8798,10 +8798,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128577825</v>
+        <v>128577893</v>
       </c>
       <c r="B76" t="n">
-        <v>92402</v>
+        <v>92818</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8809,21 +8809,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8833,10 +8833,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>660562</v>
+        <v>660559</v>
       </c>
       <c r="R76" t="n">
-        <v>6642094</v>
+        <v>6642135</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8895,10 +8895,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128577893</v>
+        <v>128577825</v>
       </c>
       <c r="B77" t="n">
-        <v>92791</v>
+        <v>92429</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8906,21 +8906,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>660559</v>
+        <v>660562</v>
       </c>
       <c r="R77" t="n">
-        <v>6642135</v>
+        <v>6642094</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8995,7 +8995,7 @@
         <v>128577875</v>
       </c>
       <c r="B78" t="n">
-        <v>95906</v>
+        <v>95933</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>128577888</v>
       </c>
       <c r="B79" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>128577818</v>
       </c>
       <c r="B80" t="n">
-        <v>92753</v>
+        <v>92780</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9288,10 +9288,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128577896</v>
+        <v>128577880</v>
       </c>
       <c r="B81" t="n">
-        <v>92791</v>
+        <v>95933</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9299,21 +9299,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>660619</v>
+        <v>660697</v>
       </c>
       <c r="R81" t="n">
-        <v>6642007</v>
+        <v>6642175</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -9385,10 +9385,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128577880</v>
+        <v>128577896</v>
       </c>
       <c r="B82" t="n">
-        <v>95906</v>
+        <v>92818</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9396,21 +9396,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>660697</v>
+        <v>660619</v>
       </c>
       <c r="R82" t="n">
-        <v>6642175</v>
+        <v>6642007</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9485,7 +9485,7 @@
         <v>128577823</v>
       </c>
       <c r="B83" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9579,10 +9579,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128577898</v>
+        <v>128577877</v>
       </c>
       <c r="B84" t="n">
-        <v>92791</v>
+        <v>95933</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9590,21 +9590,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9614,10 +9614,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>660597</v>
+        <v>660666</v>
       </c>
       <c r="R84" t="n">
-        <v>6642016</v>
+        <v>6642164</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -9676,10 +9676,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128577877</v>
+        <v>128577898</v>
       </c>
       <c r="B85" t="n">
-        <v>95906</v>
+        <v>92818</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9687,21 +9687,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>660666</v>
+        <v>660597</v>
       </c>
       <c r="R85" t="n">
-        <v>6642164</v>
+        <v>6642016</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -9776,7 +9776,7 @@
         <v>128577827</v>
       </c>
       <c r="B86" t="n">
-        <v>91069</v>
+        <v>91096</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>128577891</v>
       </c>
       <c r="B87" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>128577890</v>
       </c>
       <c r="B88" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -6955,32 +6955,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128577892</v>
+        <v>128577885</v>
       </c>
       <c r="B57" t="n">
-        <v>92818</v>
+        <v>90955</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5964</v>
+        <v>3286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>660554</v>
+        <v>660621</v>
       </c>
       <c r="R57" t="n">
-        <v>6642138</v>
+        <v>6642044</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7052,32 +7052,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128577885</v>
+        <v>128577843</v>
       </c>
       <c r="B58" t="n">
-        <v>90955</v>
+        <v>92172</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3286</v>
+        <v>1527</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7087,10 +7087,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>660621</v>
+        <v>660556</v>
       </c>
       <c r="R58" t="n">
-        <v>6642044</v>
+        <v>6642090</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7149,32 +7149,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128577843</v>
+        <v>128577892</v>
       </c>
       <c r="B59" t="n">
-        <v>92172</v>
+        <v>92818</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1527</v>
+        <v>5964</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>660556</v>
+        <v>660554</v>
       </c>
       <c r="R59" t="n">
-        <v>6642090</v>
+        <v>6642138</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -8798,10 +8798,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128577893</v>
+        <v>128577825</v>
       </c>
       <c r="B76" t="n">
-        <v>92818</v>
+        <v>92429</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8809,21 +8809,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8833,10 +8833,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>660559</v>
+        <v>660562</v>
       </c>
       <c r="R76" t="n">
-        <v>6642135</v>
+        <v>6642094</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8895,10 +8895,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128577825</v>
+        <v>128577893</v>
       </c>
       <c r="B77" t="n">
-        <v>92429</v>
+        <v>92818</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8906,21 +8906,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>660562</v>
+        <v>660559</v>
       </c>
       <c r="R77" t="n">
-        <v>6642094</v>
+        <v>6642135</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -6570,7 +6570,7 @@
         <v>128577897</v>
       </c>
       <c r="B53" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>128577820</v>
       </c>
       <c r="B54" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>128577858</v>
       </c>
       <c r="B55" t="n">
-        <v>91047</v>
+        <v>91052</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>128577905</v>
       </c>
       <c r="B56" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>128577885</v>
       </c>
       <c r="B57" t="n">
-        <v>90955</v>
+        <v>90960</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7052,32 +7052,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128577843</v>
+        <v>128577892</v>
       </c>
       <c r="B58" t="n">
-        <v>92172</v>
+        <v>92823</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1527</v>
+        <v>5964</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7087,10 +7087,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>660556</v>
+        <v>660554</v>
       </c>
       <c r="R58" t="n">
-        <v>6642090</v>
+        <v>6642138</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7149,32 +7149,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128577892</v>
+        <v>128577843</v>
       </c>
       <c r="B59" t="n">
-        <v>92818</v>
+        <v>92177</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5964</v>
+        <v>1527</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>660554</v>
+        <v>660556</v>
       </c>
       <c r="R59" t="n">
-        <v>6642138</v>
+        <v>6642090</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7246,32 +7246,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128577853</v>
+        <v>128577817</v>
       </c>
       <c r="B60" t="n">
-        <v>86983</v>
+        <v>92785</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3739</v>
+        <v>4363</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>660617</v>
+        <v>660620</v>
       </c>
       <c r="R60" t="n">
-        <v>6642063</v>
+        <v>6642049</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7343,10 +7343,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128577817</v>
+        <v>128577882</v>
       </c>
       <c r="B61" t="n">
-        <v>92780</v>
+        <v>95939</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7354,21 +7354,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4363</v>
+        <v>2671</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>660620</v>
+        <v>660709</v>
       </c>
       <c r="R61" t="n">
-        <v>6642049</v>
+        <v>6642203</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7440,10 +7440,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128577816</v>
+        <v>128577853</v>
       </c>
       <c r="B62" t="n">
-        <v>86983</v>
+        <v>86987</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>660612</v>
+        <v>660617</v>
       </c>
       <c r="R62" t="n">
-        <v>6642049</v>
+        <v>6642063</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7537,32 +7537,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128577882</v>
+        <v>128577816</v>
       </c>
       <c r="B63" t="n">
-        <v>95933</v>
+        <v>86987</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2671</v>
+        <v>3739</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>660709</v>
+        <v>660612</v>
       </c>
       <c r="R63" t="n">
-        <v>6642203</v>
+        <v>6642049</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7637,7 +7637,7 @@
         <v>128577889</v>
       </c>
       <c r="B64" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>128577884</v>
       </c>
       <c r="B65" t="n">
-        <v>95933</v>
+        <v>95939</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>128577878</v>
       </c>
       <c r="B66" t="n">
-        <v>95933</v>
+        <v>95939</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>128577881</v>
       </c>
       <c r="B67" t="n">
-        <v>95933</v>
+        <v>95939</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>128577833</v>
       </c>
       <c r="B68" t="n">
-        <v>100713</v>
+        <v>100719</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>128577828</v>
       </c>
       <c r="B69" t="n">
-        <v>91096</v>
+        <v>91101</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>128577904</v>
       </c>
       <c r="B70" t="n">
-        <v>92123</v>
+        <v>92128</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>128577824</v>
       </c>
       <c r="B71" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8410,10 +8410,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128577908</v>
+        <v>128577894</v>
       </c>
       <c r="B72" t="n">
-        <v>90767</v>
+        <v>92823</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8421,21 +8421,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>749</v>
+        <v>5964</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Alsopp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Gyrodon lividus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Bull.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8445,10 +8445,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>660712</v>
+        <v>660638</v>
       </c>
       <c r="R72" t="n">
-        <v>6642212</v>
+        <v>6641974</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128577871</v>
+        <v>128577886</v>
       </c>
       <c r="B73" t="n">
-        <v>95933</v>
+        <v>92823</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8518,21 +8518,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8542,10 +8542,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>660627</v>
+        <v>660635</v>
       </c>
       <c r="R73" t="n">
-        <v>6642017</v>
+        <v>6641930</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8604,10 +8604,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128577894</v>
+        <v>128577871</v>
       </c>
       <c r="B74" t="n">
-        <v>92818</v>
+        <v>95939</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8615,21 +8615,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>660638</v>
+        <v>660627</v>
       </c>
       <c r="R74" t="n">
-        <v>6641974</v>
+        <v>6642017</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8701,10 +8701,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128577886</v>
+        <v>128577908</v>
       </c>
       <c r="B75" t="n">
-        <v>92818</v>
+        <v>90772</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8712,21 +8712,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5964</v>
+        <v>749</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Alsopp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Gyrodon lividus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Bull.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>660635</v>
+        <v>660712</v>
       </c>
       <c r="R75" t="n">
-        <v>6641930</v>
+        <v>6642212</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8801,7 +8801,7 @@
         <v>128577825</v>
       </c>
       <c r="B76" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>128577893</v>
       </c>
       <c r="B77" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>128577875</v>
       </c>
       <c r="B78" t="n">
-        <v>95933</v>
+        <v>95939</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9089,10 +9089,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128577888</v>
+        <v>128577818</v>
       </c>
       <c r="B79" t="n">
-        <v>92818</v>
+        <v>92785</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9100,21 +9100,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5964</v>
+        <v>4363</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>660615</v>
+        <v>660559</v>
       </c>
       <c r="R79" t="n">
-        <v>6642026</v>
+        <v>6642143</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -9160,6 +9160,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>20 fruktkroppar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9186,10 +9191,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128577818</v>
+        <v>128577888</v>
       </c>
       <c r="B80" t="n">
-        <v>92780</v>
+        <v>92823</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9197,21 +9202,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4363</v>
+        <v>5964</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9221,10 +9226,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>660559</v>
+        <v>660615</v>
       </c>
       <c r="R80" t="n">
-        <v>6642143</v>
+        <v>6642026</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -9257,11 +9262,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-19</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>20 fruktkroppar</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9291,7 +9291,7 @@
         <v>128577880</v>
       </c>
       <c r="B81" t="n">
-        <v>95933</v>
+        <v>95939</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9385,10 +9385,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128577896</v>
+        <v>128577823</v>
       </c>
       <c r="B82" t="n">
-        <v>92818</v>
+        <v>92434</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9396,21 +9396,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>660619</v>
+        <v>660679</v>
       </c>
       <c r="R82" t="n">
-        <v>6642007</v>
+        <v>6642181</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9482,10 +9482,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128577823</v>
+        <v>128577896</v>
       </c>
       <c r="B83" t="n">
-        <v>92429</v>
+        <v>92823</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9493,21 +9493,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9517,10 +9517,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>660679</v>
+        <v>660619</v>
       </c>
       <c r="R83" t="n">
-        <v>6642181</v>
+        <v>6642007</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9582,7 +9582,7 @@
         <v>128577877</v>
       </c>
       <c r="B84" t="n">
-        <v>95933</v>
+        <v>95939</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>128577898</v>
       </c>
       <c r="B85" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>128577827</v>
       </c>
       <c r="B86" t="n">
-        <v>91096</v>
+        <v>91101</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>128577891</v>
       </c>
       <c r="B87" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>128577890</v>
       </c>
       <c r="B88" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -6570,7 +6570,7 @@
         <v>128577897</v>
       </c>
       <c r="B53" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>128577820</v>
       </c>
       <c r="B54" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>128577858</v>
       </c>
       <c r="B55" t="n">
-        <v>91052</v>
+        <v>91057</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>128577905</v>
       </c>
       <c r="B56" t="n">
-        <v>92169</v>
+        <v>92174</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6955,32 +6955,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128577885</v>
+        <v>128577843</v>
       </c>
       <c r="B57" t="n">
-        <v>90960</v>
+        <v>92182</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3286</v>
+        <v>1527</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>660621</v>
+        <v>660556</v>
       </c>
       <c r="R57" t="n">
-        <v>6642044</v>
+        <v>6642090</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7052,32 +7052,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128577892</v>
+        <v>128577885</v>
       </c>
       <c r="B58" t="n">
-        <v>92823</v>
+        <v>90965</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5964</v>
+        <v>3286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7087,10 +7087,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>660554</v>
+        <v>660621</v>
       </c>
       <c r="R58" t="n">
-        <v>6642138</v>
+        <v>6642044</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7149,32 +7149,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128577843</v>
+        <v>128577892</v>
       </c>
       <c r="B59" t="n">
-        <v>92177</v>
+        <v>92830</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1527</v>
+        <v>5964</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>660556</v>
+        <v>660554</v>
       </c>
       <c r="R59" t="n">
-        <v>6642090</v>
+        <v>6642138</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7246,10 +7246,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128577817</v>
+        <v>128577882</v>
       </c>
       <c r="B60" t="n">
-        <v>92785</v>
+        <v>95946</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7257,21 +7257,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4363</v>
+        <v>2671</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>660620</v>
+        <v>660709</v>
       </c>
       <c r="R60" t="n">
-        <v>6642049</v>
+        <v>6642203</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7343,32 +7343,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128577882</v>
+        <v>128577853</v>
       </c>
       <c r="B61" t="n">
-        <v>95939</v>
+        <v>86988</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2671</v>
+        <v>3739</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>660709</v>
+        <v>660617</v>
       </c>
       <c r="R61" t="n">
-        <v>6642203</v>
+        <v>6642063</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7440,32 +7440,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128577853</v>
+        <v>128577817</v>
       </c>
       <c r="B62" t="n">
-        <v>86987</v>
+        <v>92790</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3739</v>
+        <v>4363</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>660617</v>
+        <v>660620</v>
       </c>
       <c r="R62" t="n">
-        <v>6642063</v>
+        <v>6642049</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7540,7 +7540,7 @@
         <v>128577816</v>
       </c>
       <c r="B63" t="n">
-        <v>86987</v>
+        <v>86988</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7634,10 +7634,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128577889</v>
+        <v>128577833</v>
       </c>
       <c r="B64" t="n">
-        <v>92823</v>
+        <v>100726</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7645,21 +7645,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7669,10 +7669,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>660614</v>
+        <v>660698</v>
       </c>
       <c r="R64" t="n">
-        <v>6642042</v>
+        <v>6642170</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7734,7 +7734,7 @@
         <v>128577884</v>
       </c>
       <c r="B65" t="n">
-        <v>95939</v>
+        <v>95946</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>128577878</v>
       </c>
       <c r="B66" t="n">
-        <v>95939</v>
+        <v>95946</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>128577881</v>
       </c>
       <c r="B67" t="n">
-        <v>95939</v>
+        <v>95946</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8022,10 +8022,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128577833</v>
+        <v>128577889</v>
       </c>
       <c r="B68" t="n">
-        <v>100719</v>
+        <v>92830</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8033,21 +8033,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8057,10 +8057,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>660698</v>
+        <v>660614</v>
       </c>
       <c r="R68" t="n">
-        <v>6642170</v>
+        <v>6642042</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8122,7 +8122,7 @@
         <v>128577828</v>
       </c>
       <c r="B69" t="n">
-        <v>91101</v>
+        <v>91106</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>128577904</v>
       </c>
       <c r="B70" t="n">
-        <v>92128</v>
+        <v>92133</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>128577824</v>
       </c>
       <c r="B71" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8410,10 +8410,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128577894</v>
+        <v>128577871</v>
       </c>
       <c r="B72" t="n">
-        <v>92823</v>
+        <v>95946</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8421,21 +8421,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8445,10 +8445,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>660638</v>
+        <v>660627</v>
       </c>
       <c r="R72" t="n">
-        <v>6641974</v>
+        <v>6642017</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128577886</v>
+        <v>128577894</v>
       </c>
       <c r="B73" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8542,10 +8542,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>660635</v>
+        <v>660638</v>
       </c>
       <c r="R73" t="n">
-        <v>6641930</v>
+        <v>6641974</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8604,10 +8604,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128577871</v>
+        <v>128577886</v>
       </c>
       <c r="B74" t="n">
-        <v>95939</v>
+        <v>92830</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8615,21 +8615,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>660627</v>
+        <v>660635</v>
       </c>
       <c r="R74" t="n">
-        <v>6642017</v>
+        <v>6641930</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8704,7 +8704,7 @@
         <v>128577908</v>
       </c>
       <c r="B75" t="n">
-        <v>90772</v>
+        <v>90777</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>128577825</v>
       </c>
       <c r="B76" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>128577893</v>
       </c>
       <c r="B77" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>128577875</v>
       </c>
       <c r="B78" t="n">
-        <v>95939</v>
+        <v>95946</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9089,10 +9089,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128577818</v>
+        <v>128577888</v>
       </c>
       <c r="B79" t="n">
-        <v>92785</v>
+        <v>92830</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9100,21 +9100,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4363</v>
+        <v>5964</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>660559</v>
+        <v>660615</v>
       </c>
       <c r="R79" t="n">
-        <v>6642143</v>
+        <v>6642026</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -9160,11 +9160,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-19</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>20 fruktkroppar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9191,10 +9186,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128577888</v>
+        <v>128577818</v>
       </c>
       <c r="B80" t="n">
-        <v>92823</v>
+        <v>92790</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9202,21 +9197,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5964</v>
+        <v>4363</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9226,10 +9221,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>660615</v>
+        <v>660559</v>
       </c>
       <c r="R80" t="n">
-        <v>6642026</v>
+        <v>6642143</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -9262,6 +9257,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>20 fruktkroppar</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9291,7 +9291,7 @@
         <v>128577880</v>
       </c>
       <c r="B81" t="n">
-        <v>95939</v>
+        <v>95946</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>128577823</v>
       </c>
       <c r="B82" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>128577896</v>
       </c>
       <c r="B83" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>128577877</v>
       </c>
       <c r="B84" t="n">
-        <v>95939</v>
+        <v>95946</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>128577898</v>
       </c>
       <c r="B85" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9773,32 +9773,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128577827</v>
+        <v>128577891</v>
       </c>
       <c r="B86" t="n">
-        <v>91101</v>
+        <v>92830</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3086</v>
+        <v>5964</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Auricularia mesenterica</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Dicks.:Fr.) Pers.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9808,10 +9808,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>660698</v>
+        <v>660557</v>
       </c>
       <c r="R86" t="n">
-        <v>6642185</v>
+        <v>6642137</v>
       </c>
       <c r="S86" t="n">
         <v>20</v>
@@ -9870,10 +9870,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128577891</v>
+        <v>128577890</v>
       </c>
       <c r="B87" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9905,10 +9905,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>660557</v>
+        <v>660618</v>
       </c>
       <c r="R87" t="n">
-        <v>6642137</v>
+        <v>6642051</v>
       </c>
       <c r="S87" t="n">
         <v>20</v>
@@ -9967,32 +9967,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128577890</v>
+        <v>128577827</v>
       </c>
       <c r="B88" t="n">
-        <v>92823</v>
+        <v>91106</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5964</v>
+        <v>3086</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Auricularia mesenterica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Dicks.:Fr.) Pers.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10002,10 +10002,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>660618</v>
+        <v>660698</v>
       </c>
       <c r="R88" t="n">
-        <v>6642051</v>
+        <v>6642185</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -6955,32 +6955,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128577843</v>
+        <v>128577885</v>
       </c>
       <c r="B57" t="n">
-        <v>92182</v>
+        <v>90965</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1527</v>
+        <v>3286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>660556</v>
+        <v>660621</v>
       </c>
       <c r="R57" t="n">
-        <v>6642090</v>
+        <v>6642044</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7052,32 +7052,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128577885</v>
+        <v>128577892</v>
       </c>
       <c r="B58" t="n">
-        <v>90965</v>
+        <v>92830</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3286</v>
+        <v>5964</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7087,10 +7087,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>660621</v>
+        <v>660554</v>
       </c>
       <c r="R58" t="n">
-        <v>6642044</v>
+        <v>6642138</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7149,32 +7149,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128577892</v>
+        <v>128577843</v>
       </c>
       <c r="B59" t="n">
-        <v>92830</v>
+        <v>92182</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5964</v>
+        <v>1527</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>660554</v>
+        <v>660556</v>
       </c>
       <c r="R59" t="n">
-        <v>6642138</v>
+        <v>6642090</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7246,32 +7246,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128577882</v>
+        <v>128577853</v>
       </c>
       <c r="B60" t="n">
-        <v>95946</v>
+        <v>86988</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2671</v>
+        <v>3739</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>660709</v>
+        <v>660617</v>
       </c>
       <c r="R60" t="n">
-        <v>6642203</v>
+        <v>6642063</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7343,7 +7343,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128577853</v>
+        <v>128577816</v>
       </c>
       <c r="B61" t="n">
         <v>86988</v>
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>660617</v>
+        <v>660612</v>
       </c>
       <c r="R61" t="n">
-        <v>6642063</v>
+        <v>6642049</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7537,32 +7537,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128577816</v>
+        <v>128577882</v>
       </c>
       <c r="B63" t="n">
-        <v>86988</v>
+        <v>95946</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3739</v>
+        <v>2671</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>660612</v>
+        <v>660709</v>
       </c>
       <c r="R63" t="n">
-        <v>6642049</v>
+        <v>6642203</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7634,10 +7634,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128577833</v>
+        <v>128577881</v>
       </c>
       <c r="B64" t="n">
-        <v>100726</v>
+        <v>95946</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7645,21 +7645,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7669,10 +7669,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>660698</v>
+        <v>660699</v>
       </c>
       <c r="R64" t="n">
-        <v>6642170</v>
+        <v>6642205</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7731,10 +7731,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128577884</v>
+        <v>128577889</v>
       </c>
       <c r="B65" t="n">
-        <v>95946</v>
+        <v>92830</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7742,21 +7742,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>660554</v>
+        <v>660614</v>
       </c>
       <c r="R65" t="n">
-        <v>6642138</v>
+        <v>6642042</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7828,7 +7828,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128577878</v>
+        <v>128577884</v>
       </c>
       <c r="B66" t="n">
         <v>95946</v>
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>660701</v>
+        <v>660554</v>
       </c>
       <c r="R66" t="n">
-        <v>6642183</v>
+        <v>6642138</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7925,7 +7925,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128577881</v>
+        <v>128577878</v>
       </c>
       <c r="B67" t="n">
         <v>95946</v>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>660699</v>
+        <v>660701</v>
       </c>
       <c r="R67" t="n">
-        <v>6642205</v>
+        <v>6642183</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -8022,10 +8022,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128577889</v>
+        <v>128577833</v>
       </c>
       <c r="B68" t="n">
-        <v>92830</v>
+        <v>100726</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8033,21 +8033,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8057,10 +8057,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>660614</v>
+        <v>660698</v>
       </c>
       <c r="R68" t="n">
-        <v>6642042</v>
+        <v>6642170</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8410,10 +8410,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128577871</v>
+        <v>128577894</v>
       </c>
       <c r="B72" t="n">
-        <v>95946</v>
+        <v>92830</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8421,21 +8421,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8445,10 +8445,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>660627</v>
+        <v>660638</v>
       </c>
       <c r="R72" t="n">
-        <v>6642017</v>
+        <v>6641974</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8507,7 +8507,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128577894</v>
+        <v>128577886</v>
       </c>
       <c r="B73" t="n">
         <v>92830</v>
@@ -8542,10 +8542,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>660638</v>
+        <v>660635</v>
       </c>
       <c r="R73" t="n">
-        <v>6641974</v>
+        <v>6641930</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8604,10 +8604,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128577886</v>
+        <v>128577871</v>
       </c>
       <c r="B74" t="n">
-        <v>92830</v>
+        <v>95946</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8615,21 +8615,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>660635</v>
+        <v>660627</v>
       </c>
       <c r="R74" t="n">
-        <v>6641930</v>
+        <v>6642017</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -9089,10 +9089,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128577888</v>
+        <v>128577818</v>
       </c>
       <c r="B79" t="n">
-        <v>92830</v>
+        <v>92790</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9100,21 +9100,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5964</v>
+        <v>4363</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>660615</v>
+        <v>660559</v>
       </c>
       <c r="R79" t="n">
-        <v>6642026</v>
+        <v>6642143</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -9160,6 +9160,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>20 fruktkroppar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9186,10 +9191,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128577818</v>
+        <v>128577888</v>
       </c>
       <c r="B80" t="n">
-        <v>92790</v>
+        <v>92830</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9197,21 +9202,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4363</v>
+        <v>5964</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9221,10 +9226,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>660559</v>
+        <v>660615</v>
       </c>
       <c r="R80" t="n">
-        <v>6642143</v>
+        <v>6642026</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -9257,11 +9262,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-19</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>20 fruktkroppar</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9288,10 +9288,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128577880</v>
+        <v>128577823</v>
       </c>
       <c r="B81" t="n">
-        <v>95946</v>
+        <v>92439</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9299,21 +9299,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2671</v>
+        <v>4769</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>660697</v>
+        <v>660679</v>
       </c>
       <c r="R81" t="n">
-        <v>6642175</v>
+        <v>6642181</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -9385,10 +9385,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128577823</v>
+        <v>128577896</v>
       </c>
       <c r="B82" t="n">
-        <v>92439</v>
+        <v>92830</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9396,21 +9396,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>660679</v>
+        <v>660619</v>
       </c>
       <c r="R82" t="n">
-        <v>6642181</v>
+        <v>6642007</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9482,10 +9482,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128577896</v>
+        <v>128577880</v>
       </c>
       <c r="B83" t="n">
-        <v>92830</v>
+        <v>95946</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9493,21 +9493,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9517,10 +9517,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>660619</v>
+        <v>660697</v>
       </c>
       <c r="R83" t="n">
-        <v>6642007</v>
+        <v>6642175</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9773,32 +9773,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128577891</v>
+        <v>128577827</v>
       </c>
       <c r="B86" t="n">
-        <v>92830</v>
+        <v>91106</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5964</v>
+        <v>3086</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Auricularia mesenterica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Dicks.:Fr.) Pers.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9808,10 +9808,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>660557</v>
+        <v>660698</v>
       </c>
       <c r="R86" t="n">
-        <v>6642137</v>
+        <v>6642185</v>
       </c>
       <c r="S86" t="n">
         <v>20</v>
@@ -9870,7 +9870,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128577890</v>
+        <v>128577891</v>
       </c>
       <c r="B87" t="n">
         <v>92830</v>
@@ -9905,10 +9905,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>660618</v>
+        <v>660557</v>
       </c>
       <c r="R87" t="n">
-        <v>6642051</v>
+        <v>6642137</v>
       </c>
       <c r="S87" t="n">
         <v>20</v>
@@ -9967,32 +9967,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128577827</v>
+        <v>128577890</v>
       </c>
       <c r="B88" t="n">
-        <v>91106</v>
+        <v>92830</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3086</v>
+        <v>5964</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Auricularia mesenterica</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Dicks.:Fr.) Pers.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10002,10 +10002,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>660698</v>
+        <v>660618</v>
       </c>
       <c r="R88" t="n">
-        <v>6642185</v>
+        <v>6642051</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -6955,32 +6955,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128577885</v>
+        <v>128577843</v>
       </c>
       <c r="B57" t="n">
-        <v>90965</v>
+        <v>92182</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3286</v>
+        <v>1527</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>660621</v>
+        <v>660556</v>
       </c>
       <c r="R57" t="n">
-        <v>6642044</v>
+        <v>6642090</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7052,32 +7052,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128577892</v>
+        <v>128577885</v>
       </c>
       <c r="B58" t="n">
-        <v>92830</v>
+        <v>90965</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5964</v>
+        <v>3286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7087,10 +7087,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>660554</v>
+        <v>660621</v>
       </c>
       <c r="R58" t="n">
-        <v>6642138</v>
+        <v>6642044</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7149,32 +7149,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128577843</v>
+        <v>128577892</v>
       </c>
       <c r="B59" t="n">
-        <v>92182</v>
+        <v>92830</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1527</v>
+        <v>5964</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>660556</v>
+        <v>660554</v>
       </c>
       <c r="R59" t="n">
-        <v>6642090</v>
+        <v>6642138</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7634,10 +7634,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128577881</v>
+        <v>128577889</v>
       </c>
       <c r="B64" t="n">
-        <v>95946</v>
+        <v>92830</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7645,21 +7645,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7669,10 +7669,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>660699</v>
+        <v>660614</v>
       </c>
       <c r="R64" t="n">
-        <v>6642205</v>
+        <v>6642042</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7731,10 +7731,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128577889</v>
+        <v>128577884</v>
       </c>
       <c r="B65" t="n">
-        <v>92830</v>
+        <v>95946</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7742,21 +7742,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>660614</v>
+        <v>660554</v>
       </c>
       <c r="R65" t="n">
-        <v>6642042</v>
+        <v>6642138</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7828,7 +7828,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128577884</v>
+        <v>128577881</v>
       </c>
       <c r="B66" t="n">
         <v>95946</v>
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>660554</v>
+        <v>660699</v>
       </c>
       <c r="R66" t="n">
-        <v>6642138</v>
+        <v>6642205</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7925,10 +7925,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128577878</v>
+        <v>128577833</v>
       </c>
       <c r="B67" t="n">
-        <v>95946</v>
+        <v>100726</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7936,21 +7936,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>660701</v>
+        <v>660698</v>
       </c>
       <c r="R67" t="n">
-        <v>6642183</v>
+        <v>6642170</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -8022,10 +8022,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128577833</v>
+        <v>128577878</v>
       </c>
       <c r="B68" t="n">
-        <v>100726</v>
+        <v>95946</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8033,21 +8033,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8057,10 +8057,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>660698</v>
+        <v>660701</v>
       </c>
       <c r="R68" t="n">
-        <v>6642170</v>
+        <v>6642183</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -9579,10 +9579,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128577877</v>
+        <v>128577898</v>
       </c>
       <c r="B84" t="n">
-        <v>95946</v>
+        <v>92830</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9590,21 +9590,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9614,10 +9614,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>660666</v>
+        <v>660597</v>
       </c>
       <c r="R84" t="n">
-        <v>6642164</v>
+        <v>6642016</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -9676,10 +9676,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128577898</v>
+        <v>128577877</v>
       </c>
       <c r="B85" t="n">
-        <v>92830</v>
+        <v>95946</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9687,21 +9687,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>660597</v>
+        <v>660666</v>
       </c>
       <c r="R85" t="n">
-        <v>6642016</v>
+        <v>6642164</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -9773,32 +9773,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128577827</v>
+        <v>128577891</v>
       </c>
       <c r="B86" t="n">
-        <v>91106</v>
+        <v>92830</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3086</v>
+        <v>5964</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Auricularia mesenterica</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Dicks.:Fr.) Pers.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9808,10 +9808,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>660698</v>
+        <v>660557</v>
       </c>
       <c r="R86" t="n">
-        <v>6642185</v>
+        <v>6642137</v>
       </c>
       <c r="S86" t="n">
         <v>20</v>
@@ -9870,7 +9870,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128577891</v>
+        <v>128577890</v>
       </c>
       <c r="B87" t="n">
         <v>92830</v>
@@ -9905,10 +9905,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>660557</v>
+        <v>660618</v>
       </c>
       <c r="R87" t="n">
-        <v>6642137</v>
+        <v>6642051</v>
       </c>
       <c r="S87" t="n">
         <v>20</v>
@@ -9967,32 +9967,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128577890</v>
+        <v>128577827</v>
       </c>
       <c r="B88" t="n">
-        <v>92830</v>
+        <v>91106</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5964</v>
+        <v>3086</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Auricularia mesenterica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Dicks.:Fr.) Pers.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10002,10 +10002,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>660618</v>
+        <v>660698</v>
       </c>
       <c r="R88" t="n">
-        <v>6642051</v>
+        <v>6642185</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -6570,7 +6570,7 @@
         <v>128577897</v>
       </c>
       <c r="B53" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>128577820</v>
       </c>
       <c r="B54" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>128577858</v>
       </c>
       <c r="B55" t="n">
-        <v>91057</v>
+        <v>91061</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>128577905</v>
       </c>
       <c r="B56" t="n">
-        <v>92174</v>
+        <v>92178</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6955,32 +6955,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128577843</v>
+        <v>128577892</v>
       </c>
       <c r="B57" t="n">
-        <v>92182</v>
+        <v>92834</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1527</v>
+        <v>5964</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>660556</v>
+        <v>660554</v>
       </c>
       <c r="R57" t="n">
-        <v>6642090</v>
+        <v>6642138</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7055,7 +7055,7 @@
         <v>128577885</v>
       </c>
       <c r="B58" t="n">
-        <v>90965</v>
+        <v>90969</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7149,32 +7149,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128577892</v>
+        <v>128577843</v>
       </c>
       <c r="B59" t="n">
-        <v>92830</v>
+        <v>92186</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5964</v>
+        <v>1527</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>660554</v>
+        <v>660556</v>
       </c>
       <c r="R59" t="n">
-        <v>6642138</v>
+        <v>6642090</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7246,32 +7246,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128577853</v>
+        <v>128577817</v>
       </c>
       <c r="B60" t="n">
-        <v>86988</v>
+        <v>92794</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3739</v>
+        <v>4363</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>660617</v>
+        <v>660620</v>
       </c>
       <c r="R60" t="n">
-        <v>6642063</v>
+        <v>6642049</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7343,10 +7343,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128577816</v>
+        <v>128577853</v>
       </c>
       <c r="B61" t="n">
-        <v>86988</v>
+        <v>86992</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>660612</v>
+        <v>660617</v>
       </c>
       <c r="R61" t="n">
-        <v>6642049</v>
+        <v>6642063</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7440,32 +7440,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128577817</v>
+        <v>128577816</v>
       </c>
       <c r="B62" t="n">
-        <v>92790</v>
+        <v>86992</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4363</v>
+        <v>3739</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>660620</v>
+        <v>660612</v>
       </c>
       <c r="R62" t="n">
         <v>6642049</v>
@@ -7540,7 +7540,7 @@
         <v>128577882</v>
       </c>
       <c r="B63" t="n">
-        <v>95946</v>
+        <v>95950</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7634,10 +7634,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128577889</v>
+        <v>128577884</v>
       </c>
       <c r="B64" t="n">
-        <v>92830</v>
+        <v>95950</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7645,21 +7645,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7669,10 +7669,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>660614</v>
+        <v>660554</v>
       </c>
       <c r="R64" t="n">
-        <v>6642042</v>
+        <v>6642138</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7731,10 +7731,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128577884</v>
+        <v>128577878</v>
       </c>
       <c r="B65" t="n">
-        <v>95946</v>
+        <v>95950</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>660554</v>
+        <v>660701</v>
       </c>
       <c r="R65" t="n">
-        <v>6642138</v>
+        <v>6642183</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7831,7 +7831,7 @@
         <v>128577881</v>
       </c>
       <c r="B66" t="n">
-        <v>95946</v>
+        <v>95950</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7925,10 +7925,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128577833</v>
+        <v>128577889</v>
       </c>
       <c r="B67" t="n">
-        <v>100726</v>
+        <v>92834</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7936,21 +7936,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>660698</v>
+        <v>660614</v>
       </c>
       <c r="R67" t="n">
-        <v>6642170</v>
+        <v>6642042</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -8022,10 +8022,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128577878</v>
+        <v>128577833</v>
       </c>
       <c r="B68" t="n">
-        <v>95946</v>
+        <v>100730</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8033,21 +8033,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8057,10 +8057,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>660701</v>
+        <v>660698</v>
       </c>
       <c r="R68" t="n">
-        <v>6642183</v>
+        <v>6642170</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8122,7 +8122,7 @@
         <v>128577828</v>
       </c>
       <c r="B69" t="n">
-        <v>91106</v>
+        <v>91110</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>128577904</v>
       </c>
       <c r="B70" t="n">
-        <v>92133</v>
+        <v>92137</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>128577824</v>
       </c>
       <c r="B71" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8410,10 +8410,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128577894</v>
+        <v>128577871</v>
       </c>
       <c r="B72" t="n">
-        <v>92830</v>
+        <v>95950</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8421,21 +8421,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8445,10 +8445,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>660638</v>
+        <v>660627</v>
       </c>
       <c r="R72" t="n">
-        <v>6641974</v>
+        <v>6642017</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128577886</v>
+        <v>128577908</v>
       </c>
       <c r="B73" t="n">
-        <v>92830</v>
+        <v>90781</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8518,21 +8518,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5964</v>
+        <v>749</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Alsopp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Gyrodon lividus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Bull.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8542,10 +8542,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>660635</v>
+        <v>660712</v>
       </c>
       <c r="R73" t="n">
-        <v>6641930</v>
+        <v>6642212</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8604,10 +8604,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128577871</v>
+        <v>128577894</v>
       </c>
       <c r="B74" t="n">
-        <v>95946</v>
+        <v>92834</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8615,21 +8615,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>660627</v>
+        <v>660638</v>
       </c>
       <c r="R74" t="n">
-        <v>6642017</v>
+        <v>6641974</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8701,10 +8701,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128577908</v>
+        <v>128577886</v>
       </c>
       <c r="B75" t="n">
-        <v>90777</v>
+        <v>92834</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8712,21 +8712,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>749</v>
+        <v>5964</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Alsopp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Gyrodon lividus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Bull.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>660712</v>
+        <v>660635</v>
       </c>
       <c r="R75" t="n">
-        <v>6642212</v>
+        <v>6641930</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8801,7 +8801,7 @@
         <v>128577825</v>
       </c>
       <c r="B76" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>128577893</v>
       </c>
       <c r="B77" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>128577875</v>
       </c>
       <c r="B78" t="n">
-        <v>95946</v>
+        <v>95950</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>128577818</v>
       </c>
       <c r="B79" t="n">
-        <v>92790</v>
+        <v>92794</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>128577888</v>
       </c>
       <c r="B80" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>128577823</v>
       </c>
       <c r="B81" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9385,10 +9385,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128577896</v>
+        <v>128577880</v>
       </c>
       <c r="B82" t="n">
-        <v>92830</v>
+        <v>95950</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9396,21 +9396,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>660619</v>
+        <v>660697</v>
       </c>
       <c r="R82" t="n">
-        <v>6642007</v>
+        <v>6642175</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9482,10 +9482,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128577880</v>
+        <v>128577896</v>
       </c>
       <c r="B83" t="n">
-        <v>95946</v>
+        <v>92834</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9493,21 +9493,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9517,10 +9517,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>660697</v>
+        <v>660619</v>
       </c>
       <c r="R83" t="n">
-        <v>6642175</v>
+        <v>6642007</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9579,10 +9579,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128577898</v>
+        <v>128577877</v>
       </c>
       <c r="B84" t="n">
-        <v>92830</v>
+        <v>95950</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9590,21 +9590,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9614,10 +9614,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>660597</v>
+        <v>660666</v>
       </c>
       <c r="R84" t="n">
-        <v>6642016</v>
+        <v>6642164</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -9676,10 +9676,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128577877</v>
+        <v>128577898</v>
       </c>
       <c r="B85" t="n">
-        <v>95946</v>
+        <v>92834</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9687,21 +9687,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>660666</v>
+        <v>660597</v>
       </c>
       <c r="R85" t="n">
-        <v>6642164</v>
+        <v>6642016</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -9773,32 +9773,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128577891</v>
+        <v>128577827</v>
       </c>
       <c r="B86" t="n">
-        <v>92830</v>
+        <v>91110</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5964</v>
+        <v>3086</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Auricularia mesenterica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Dicks.:Fr.) Pers.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9808,10 +9808,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>660557</v>
+        <v>660698</v>
       </c>
       <c r="R86" t="n">
-        <v>6642137</v>
+        <v>6642185</v>
       </c>
       <c r="S86" t="n">
         <v>20</v>
@@ -9870,10 +9870,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128577890</v>
+        <v>128577891</v>
       </c>
       <c r="B87" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9905,10 +9905,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>660618</v>
+        <v>660557</v>
       </c>
       <c r="R87" t="n">
-        <v>6642051</v>
+        <v>6642137</v>
       </c>
       <c r="S87" t="n">
         <v>20</v>
@@ -9967,32 +9967,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128577827</v>
+        <v>128577890</v>
       </c>
       <c r="B88" t="n">
-        <v>91106</v>
+        <v>92834</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3086</v>
+        <v>5964</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Auricularia mesenterica</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Dicks.:Fr.) Pers.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10002,10 +10002,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>660698</v>
+        <v>660618</v>
       </c>
       <c r="R88" t="n">
-        <v>6642185</v>
+        <v>6642051</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -7246,10 +7246,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128577817</v>
+        <v>128577882</v>
       </c>
       <c r="B60" t="n">
-        <v>92794</v>
+        <v>95950</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7257,21 +7257,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4363</v>
+        <v>2671</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>660620</v>
+        <v>660709</v>
       </c>
       <c r="R60" t="n">
-        <v>6642049</v>
+        <v>6642203</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7343,32 +7343,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128577853</v>
+        <v>128577817</v>
       </c>
       <c r="B61" t="n">
-        <v>86992</v>
+        <v>92794</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3739</v>
+        <v>4363</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>660617</v>
+        <v>660620</v>
       </c>
       <c r="R61" t="n">
-        <v>6642063</v>
+        <v>6642049</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7440,7 +7440,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128577816</v>
+        <v>128577853</v>
       </c>
       <c r="B62" t="n">
         <v>86992</v>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>660612</v>
+        <v>660617</v>
       </c>
       <c r="R62" t="n">
-        <v>6642049</v>
+        <v>6642063</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7537,32 +7537,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128577882</v>
+        <v>128577816</v>
       </c>
       <c r="B63" t="n">
-        <v>95950</v>
+        <v>86992</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2671</v>
+        <v>3739</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>660709</v>
+        <v>660612</v>
       </c>
       <c r="R63" t="n">
-        <v>6642203</v>
+        <v>6642049</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -9288,10 +9288,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128577823</v>
+        <v>128577880</v>
       </c>
       <c r="B81" t="n">
-        <v>92443</v>
+        <v>95950</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9299,21 +9299,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4769</v>
+        <v>2671</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>660679</v>
+        <v>660697</v>
       </c>
       <c r="R81" t="n">
-        <v>6642181</v>
+        <v>6642175</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -9385,10 +9385,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128577880</v>
+        <v>128577896</v>
       </c>
       <c r="B82" t="n">
-        <v>95950</v>
+        <v>92834</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9396,21 +9396,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>660697</v>
+        <v>660619</v>
       </c>
       <c r="R82" t="n">
-        <v>6642175</v>
+        <v>6642007</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9482,10 +9482,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128577896</v>
+        <v>128577823</v>
       </c>
       <c r="B83" t="n">
-        <v>92834</v>
+        <v>92443</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9493,21 +9493,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9517,10 +9517,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>660619</v>
+        <v>660679</v>
       </c>
       <c r="R83" t="n">
-        <v>6642007</v>
+        <v>6642181</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -6955,32 +6955,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128577892</v>
+        <v>128577885</v>
       </c>
       <c r="B57" t="n">
-        <v>92834</v>
+        <v>90969</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5964</v>
+        <v>3286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>660554</v>
+        <v>660621</v>
       </c>
       <c r="R57" t="n">
-        <v>6642138</v>
+        <v>6642044</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7052,32 +7052,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128577885</v>
+        <v>128577892</v>
       </c>
       <c r="B58" t="n">
-        <v>90969</v>
+        <v>92834</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3286</v>
+        <v>5964</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7087,10 +7087,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>660621</v>
+        <v>660554</v>
       </c>
       <c r="R58" t="n">
-        <v>6642044</v>
+        <v>6642138</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7343,32 +7343,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128577817</v>
+        <v>128577853</v>
       </c>
       <c r="B61" t="n">
-        <v>92794</v>
+        <v>86992</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4363</v>
+        <v>3739</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>660620</v>
+        <v>660617</v>
       </c>
       <c r="R61" t="n">
-        <v>6642049</v>
+        <v>6642063</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7440,7 +7440,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128577853</v>
+        <v>128577816</v>
       </c>
       <c r="B62" t="n">
         <v>86992</v>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>660617</v>
+        <v>660612</v>
       </c>
       <c r="R62" t="n">
-        <v>6642063</v>
+        <v>6642049</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7537,32 +7537,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128577816</v>
+        <v>128577817</v>
       </c>
       <c r="B63" t="n">
-        <v>86992</v>
+        <v>92794</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3739</v>
+        <v>4363</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7572,7 +7572,7 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>660612</v>
+        <v>660620</v>
       </c>
       <c r="R63" t="n">
         <v>6642049</v>
@@ -7634,10 +7634,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128577884</v>
+        <v>128577833</v>
       </c>
       <c r="B64" t="n">
-        <v>95950</v>
+        <v>100730</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7645,21 +7645,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7669,10 +7669,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>660554</v>
+        <v>660698</v>
       </c>
       <c r="R64" t="n">
-        <v>6642138</v>
+        <v>6642170</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7731,10 +7731,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128577878</v>
+        <v>128577889</v>
       </c>
       <c r="B65" t="n">
-        <v>95950</v>
+        <v>92834</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7742,21 +7742,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>660701</v>
+        <v>660614</v>
       </c>
       <c r="R65" t="n">
-        <v>6642183</v>
+        <v>6642042</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7828,7 +7828,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128577881</v>
+        <v>128577884</v>
       </c>
       <c r="B66" t="n">
         <v>95950</v>
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>660699</v>
+        <v>660554</v>
       </c>
       <c r="R66" t="n">
-        <v>6642205</v>
+        <v>6642138</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7925,10 +7925,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128577889</v>
+        <v>128577878</v>
       </c>
       <c r="B67" t="n">
-        <v>92834</v>
+        <v>95950</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7936,21 +7936,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>660614</v>
+        <v>660701</v>
       </c>
       <c r="R67" t="n">
-        <v>6642042</v>
+        <v>6642183</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -8022,10 +8022,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128577833</v>
+        <v>128577881</v>
       </c>
       <c r="B68" t="n">
-        <v>100730</v>
+        <v>95950</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8033,21 +8033,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8057,10 +8057,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>660698</v>
+        <v>660699</v>
       </c>
       <c r="R68" t="n">
-        <v>6642170</v>
+        <v>6642205</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -9089,10 +9089,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128577818</v>
+        <v>128577888</v>
       </c>
       <c r="B79" t="n">
-        <v>92794</v>
+        <v>92834</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9100,21 +9100,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4363</v>
+        <v>5964</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>660559</v>
+        <v>660615</v>
       </c>
       <c r="R79" t="n">
-        <v>6642143</v>
+        <v>6642026</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -9160,11 +9160,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-19</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>20 fruktkroppar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9191,10 +9186,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128577888</v>
+        <v>128577818</v>
       </c>
       <c r="B80" t="n">
-        <v>92834</v>
+        <v>92794</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9202,21 +9197,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5964</v>
+        <v>4363</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9226,10 +9221,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>660615</v>
+        <v>660559</v>
       </c>
       <c r="R80" t="n">
-        <v>6642026</v>
+        <v>6642143</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -9262,6 +9257,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>20 fruktkroppar</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9579,10 +9579,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128577877</v>
+        <v>128577898</v>
       </c>
       <c r="B84" t="n">
-        <v>95950</v>
+        <v>92834</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9590,21 +9590,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9614,10 +9614,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>660666</v>
+        <v>660597</v>
       </c>
       <c r="R84" t="n">
-        <v>6642164</v>
+        <v>6642016</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -9676,10 +9676,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128577898</v>
+        <v>128577877</v>
       </c>
       <c r="B85" t="n">
-        <v>92834</v>
+        <v>95950</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9687,21 +9687,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>660597</v>
+        <v>660666</v>
       </c>
       <c r="R85" t="n">
-        <v>6642016</v>
+        <v>6642164</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -6570,7 +6570,7 @@
         <v>128577897</v>
       </c>
       <c r="B53" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>128577820</v>
       </c>
       <c r="B54" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>128577858</v>
       </c>
       <c r="B55" t="n">
-        <v>91061</v>
+        <v>91066</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>128577905</v>
       </c>
       <c r="B56" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6955,32 +6955,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128577885</v>
+        <v>128577843</v>
       </c>
       <c r="B57" t="n">
-        <v>90969</v>
+        <v>92191</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3286</v>
+        <v>1527</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>660621</v>
+        <v>660556</v>
       </c>
       <c r="R57" t="n">
-        <v>6642044</v>
+        <v>6642090</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7052,32 +7052,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128577892</v>
+        <v>128577885</v>
       </c>
       <c r="B58" t="n">
-        <v>92834</v>
+        <v>90974</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5964</v>
+        <v>3286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7087,10 +7087,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>660554</v>
+        <v>660621</v>
       </c>
       <c r="R58" t="n">
-        <v>6642138</v>
+        <v>6642044</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7149,32 +7149,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128577843</v>
+        <v>128577892</v>
       </c>
       <c r="B59" t="n">
-        <v>92186</v>
+        <v>92839</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1527</v>
+        <v>5964</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>660556</v>
+        <v>660554</v>
       </c>
       <c r="R59" t="n">
-        <v>6642090</v>
+        <v>6642138</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7249,7 +7249,7 @@
         <v>128577882</v>
       </c>
       <c r="B60" t="n">
-        <v>95950</v>
+        <v>95957</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7343,32 +7343,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128577853</v>
+        <v>128577817</v>
       </c>
       <c r="B61" t="n">
-        <v>86992</v>
+        <v>92799</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3739</v>
+        <v>4363</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>660617</v>
+        <v>660620</v>
       </c>
       <c r="R61" t="n">
-        <v>6642063</v>
+        <v>6642049</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7440,10 +7440,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128577816</v>
+        <v>128577853</v>
       </c>
       <c r="B62" t="n">
-        <v>86992</v>
+        <v>86997</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>660612</v>
+        <v>660617</v>
       </c>
       <c r="R62" t="n">
-        <v>6642049</v>
+        <v>6642063</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7537,32 +7537,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128577817</v>
+        <v>128577816</v>
       </c>
       <c r="B63" t="n">
-        <v>92794</v>
+        <v>86997</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4363</v>
+        <v>3739</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7572,7 +7572,7 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>660620</v>
+        <v>660612</v>
       </c>
       <c r="R63" t="n">
         <v>6642049</v>
@@ -7634,10 +7634,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128577833</v>
+        <v>128577884</v>
       </c>
       <c r="B64" t="n">
-        <v>100730</v>
+        <v>95957</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7645,21 +7645,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7669,10 +7669,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>660698</v>
+        <v>660554</v>
       </c>
       <c r="R64" t="n">
-        <v>6642170</v>
+        <v>6642138</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7731,10 +7731,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128577889</v>
+        <v>128577878</v>
       </c>
       <c r="B65" t="n">
-        <v>92834</v>
+        <v>95957</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7742,21 +7742,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>660614</v>
+        <v>660701</v>
       </c>
       <c r="R65" t="n">
-        <v>6642042</v>
+        <v>6642183</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7828,10 +7828,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128577884</v>
+        <v>128577881</v>
       </c>
       <c r="B66" t="n">
-        <v>95950</v>
+        <v>95957</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>660554</v>
+        <v>660699</v>
       </c>
       <c r="R66" t="n">
-        <v>6642138</v>
+        <v>6642205</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7925,10 +7925,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128577878</v>
+        <v>128577889</v>
       </c>
       <c r="B67" t="n">
-        <v>95950</v>
+        <v>92839</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7936,21 +7936,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>660701</v>
+        <v>660614</v>
       </c>
       <c r="R67" t="n">
-        <v>6642183</v>
+        <v>6642042</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -8022,10 +8022,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128577881</v>
+        <v>128577833</v>
       </c>
       <c r="B68" t="n">
-        <v>95950</v>
+        <v>100737</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8033,21 +8033,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2671</v>
+        <v>222771</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8057,10 +8057,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>660699</v>
+        <v>660698</v>
       </c>
       <c r="R68" t="n">
-        <v>6642205</v>
+        <v>6642170</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8122,7 +8122,7 @@
         <v>128577828</v>
       </c>
       <c r="B69" t="n">
-        <v>91110</v>
+        <v>91115</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>128577904</v>
       </c>
       <c r="B70" t="n">
-        <v>92137</v>
+        <v>92142</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>128577824</v>
       </c>
       <c r="B71" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8410,10 +8410,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128577871</v>
+        <v>128577908</v>
       </c>
       <c r="B72" t="n">
-        <v>95950</v>
+        <v>90786</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8421,21 +8421,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2671</v>
+        <v>749</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Alsopp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Gyrodon lividus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Bull.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8445,10 +8445,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>660627</v>
+        <v>660712</v>
       </c>
       <c r="R72" t="n">
-        <v>6642017</v>
+        <v>6642212</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128577908</v>
+        <v>128577894</v>
       </c>
       <c r="B73" t="n">
-        <v>90781</v>
+        <v>92839</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8518,21 +8518,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>749</v>
+        <v>5964</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Alsopp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gyrodon lividus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Bull.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8542,10 +8542,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>660712</v>
+        <v>660638</v>
       </c>
       <c r="R73" t="n">
-        <v>6642212</v>
+        <v>6641974</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8604,10 +8604,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128577894</v>
+        <v>128577886</v>
       </c>
       <c r="B74" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>660638</v>
+        <v>660635</v>
       </c>
       <c r="R74" t="n">
-        <v>6641974</v>
+        <v>6641930</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8701,10 +8701,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128577886</v>
+        <v>128577871</v>
       </c>
       <c r="B75" t="n">
-        <v>92834</v>
+        <v>95957</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8712,21 +8712,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>660635</v>
+        <v>660627</v>
       </c>
       <c r="R75" t="n">
-        <v>6641930</v>
+        <v>6642017</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8801,7 +8801,7 @@
         <v>128577825</v>
       </c>
       <c r="B76" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>128577893</v>
       </c>
       <c r="B77" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>128577875</v>
       </c>
       <c r="B78" t="n">
-        <v>95950</v>
+        <v>95957</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9089,10 +9089,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128577888</v>
+        <v>128577818</v>
       </c>
       <c r="B79" t="n">
-        <v>92834</v>
+        <v>92799</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9100,21 +9100,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5964</v>
+        <v>4363</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>660615</v>
+        <v>660559</v>
       </c>
       <c r="R79" t="n">
-        <v>6642026</v>
+        <v>6642143</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -9160,6 +9160,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>20 fruktkroppar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9186,10 +9191,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128577818</v>
+        <v>128577888</v>
       </c>
       <c r="B80" t="n">
-        <v>92794</v>
+        <v>92839</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9197,21 +9202,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4363</v>
+        <v>5964</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9221,10 +9226,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>660559</v>
+        <v>660615</v>
       </c>
       <c r="R80" t="n">
-        <v>6642143</v>
+        <v>6642026</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -9257,11 +9262,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-19</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>20 fruktkroppar</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9291,7 +9291,7 @@
         <v>128577880</v>
       </c>
       <c r="B81" t="n">
-        <v>95950</v>
+        <v>95957</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9385,10 +9385,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128577896</v>
+        <v>128577823</v>
       </c>
       <c r="B82" t="n">
-        <v>92834</v>
+        <v>92448</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9396,21 +9396,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>660619</v>
+        <v>660679</v>
       </c>
       <c r="R82" t="n">
-        <v>6642007</v>
+        <v>6642181</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9482,10 +9482,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128577823</v>
+        <v>128577896</v>
       </c>
       <c r="B83" t="n">
-        <v>92443</v>
+        <v>92839</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9493,21 +9493,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9517,10 +9517,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>660679</v>
+        <v>660619</v>
       </c>
       <c r="R83" t="n">
-        <v>6642181</v>
+        <v>6642007</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9579,10 +9579,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128577898</v>
+        <v>128577877</v>
       </c>
       <c r="B84" t="n">
-        <v>92834</v>
+        <v>95957</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9590,21 +9590,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9614,10 +9614,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>660597</v>
+        <v>660666</v>
       </c>
       <c r="R84" t="n">
-        <v>6642016</v>
+        <v>6642164</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -9676,10 +9676,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128577877</v>
+        <v>128577898</v>
       </c>
       <c r="B85" t="n">
-        <v>95950</v>
+        <v>92839</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9687,21 +9687,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>660666</v>
+        <v>660597</v>
       </c>
       <c r="R85" t="n">
-        <v>6642164</v>
+        <v>6642016</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -9776,7 +9776,7 @@
         <v>128577827</v>
       </c>
       <c r="B86" t="n">
-        <v>91110</v>
+        <v>91115</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>128577891</v>
       </c>
       <c r="B87" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>128577890</v>
       </c>
       <c r="B88" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -6570,7 +6570,7 @@
         <v>128577897</v>
       </c>
       <c r="B53" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>128577820</v>
       </c>
       <c r="B54" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>128577858</v>
       </c>
       <c r="B55" t="n">
-        <v>91068</v>
+        <v>91073</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>128577905</v>
       </c>
       <c r="B56" t="n">
-        <v>92186</v>
+        <v>92191</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6955,32 +6955,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128577892</v>
+        <v>128577885</v>
       </c>
       <c r="B57" t="n">
-        <v>92842</v>
+        <v>90981</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5964</v>
+        <v>3286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>660554</v>
+        <v>660621</v>
       </c>
       <c r="R57" t="n">
-        <v>6642138</v>
+        <v>6642044</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7052,32 +7052,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128577843</v>
+        <v>128577892</v>
       </c>
       <c r="B58" t="n">
-        <v>92194</v>
+        <v>92847</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1527</v>
+        <v>5964</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7087,10 +7087,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>660556</v>
+        <v>660554</v>
       </c>
       <c r="R58" t="n">
-        <v>6642090</v>
+        <v>6642138</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7149,32 +7149,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128577885</v>
+        <v>128577843</v>
       </c>
       <c r="B59" t="n">
-        <v>90976</v>
+        <v>92199</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3286</v>
+        <v>1527</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>660621</v>
+        <v>660556</v>
       </c>
       <c r="R59" t="n">
-        <v>6642044</v>
+        <v>6642090</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7249,7 +7249,7 @@
         <v>128577853</v>
       </c>
       <c r="B60" t="n">
-        <v>86999</v>
+        <v>87004</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>128577817</v>
       </c>
       <c r="B61" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>128577816</v>
       </c>
       <c r="B62" t="n">
-        <v>86999</v>
+        <v>87004</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>128577882</v>
       </c>
       <c r="B63" t="n">
-        <v>95960</v>
+        <v>95965</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>128577833</v>
       </c>
       <c r="B64" t="n">
-        <v>100740</v>
+        <v>100745</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7731,10 +7731,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128577889</v>
+        <v>128577884</v>
       </c>
       <c r="B65" t="n">
-        <v>92842</v>
+        <v>95965</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7742,21 +7742,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>660614</v>
+        <v>660554</v>
       </c>
       <c r="R65" t="n">
-        <v>6642042</v>
+        <v>6642138</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7828,10 +7828,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128577884</v>
+        <v>128577878</v>
       </c>
       <c r="B66" t="n">
-        <v>95960</v>
+        <v>95965</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>660554</v>
+        <v>660701</v>
       </c>
       <c r="R66" t="n">
-        <v>6642138</v>
+        <v>6642183</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7925,10 +7925,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128577878</v>
+        <v>128577881</v>
       </c>
       <c r="B67" t="n">
-        <v>95960</v>
+        <v>95965</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>660701</v>
+        <v>660699</v>
       </c>
       <c r="R67" t="n">
-        <v>6642183</v>
+        <v>6642205</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -8022,10 +8022,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128577881</v>
+        <v>128577889</v>
       </c>
       <c r="B68" t="n">
-        <v>95960</v>
+        <v>92847</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8033,21 +8033,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8057,10 +8057,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>660699</v>
+        <v>660614</v>
       </c>
       <c r="R68" t="n">
-        <v>6642205</v>
+        <v>6642042</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8122,7 +8122,7 @@
         <v>128577828</v>
       </c>
       <c r="B69" t="n">
-        <v>91117</v>
+        <v>91122</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>128577904</v>
       </c>
       <c r="B70" t="n">
-        <v>92145</v>
+        <v>92150</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>128577824</v>
       </c>
       <c r="B71" t="n">
-        <v>92451</v>
+        <v>92456</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8410,10 +8410,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128577886</v>
+        <v>128577908</v>
       </c>
       <c r="B72" t="n">
-        <v>92842</v>
+        <v>90793</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8421,21 +8421,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5964</v>
+        <v>749</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Alsopp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Gyrodon lividus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Bull.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8445,10 +8445,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>660635</v>
+        <v>660712</v>
       </c>
       <c r="R72" t="n">
-        <v>6641930</v>
+        <v>6642212</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128577908</v>
+        <v>128577871</v>
       </c>
       <c r="B73" t="n">
-        <v>90788</v>
+        <v>95965</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8518,21 +8518,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>749</v>
+        <v>2671</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Alsopp</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gyrodon lividus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Bull.:Fr.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8542,10 +8542,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>660712</v>
+        <v>660627</v>
       </c>
       <c r="R73" t="n">
-        <v>6642212</v>
+        <v>6642017</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8604,10 +8604,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128577871</v>
+        <v>128577894</v>
       </c>
       <c r="B74" t="n">
-        <v>95960</v>
+        <v>92847</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8615,21 +8615,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>660627</v>
+        <v>660638</v>
       </c>
       <c r="R74" t="n">
-        <v>6642017</v>
+        <v>6641974</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8701,10 +8701,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128577894</v>
+        <v>128577886</v>
       </c>
       <c r="B75" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>660638</v>
+        <v>660635</v>
       </c>
       <c r="R75" t="n">
-        <v>6641974</v>
+        <v>6641930</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8798,10 +8798,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128577893</v>
+        <v>128577825</v>
       </c>
       <c r="B76" t="n">
-        <v>92842</v>
+        <v>92456</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8809,21 +8809,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8833,10 +8833,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>660559</v>
+        <v>660562</v>
       </c>
       <c r="R76" t="n">
-        <v>6642135</v>
+        <v>6642094</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8895,10 +8895,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128577825</v>
+        <v>128577893</v>
       </c>
       <c r="B77" t="n">
-        <v>92451</v>
+        <v>92847</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8906,21 +8906,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>660562</v>
+        <v>660559</v>
       </c>
       <c r="R77" t="n">
-        <v>6642094</v>
+        <v>6642135</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8995,7 +8995,7 @@
         <v>128577875</v>
       </c>
       <c r="B78" t="n">
-        <v>95960</v>
+        <v>95965</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>128577818</v>
       </c>
       <c r="B79" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>128577888</v>
       </c>
       <c r="B80" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>128577880</v>
       </c>
       <c r="B81" t="n">
-        <v>95960</v>
+        <v>95965</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>128577896</v>
       </c>
       <c r="B82" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>128577823</v>
       </c>
       <c r="B83" t="n">
-        <v>92451</v>
+        <v>92456</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>128577877</v>
       </c>
       <c r="B84" t="n">
-        <v>95960</v>
+        <v>95965</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>128577898</v>
       </c>
       <c r="B85" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>128577827</v>
       </c>
       <c r="B86" t="n">
-        <v>91117</v>
+        <v>91122</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>128577891</v>
       </c>
       <c r="B87" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>128577890</v>
       </c>
       <c r="B88" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -6955,32 +6955,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128577885</v>
+        <v>128577843</v>
       </c>
       <c r="B57" t="n">
-        <v>90981</v>
+        <v>92199</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3286</v>
+        <v>1527</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>660621</v>
+        <v>660556</v>
       </c>
       <c r="R57" t="n">
-        <v>6642044</v>
+        <v>6642090</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7149,32 +7149,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128577843</v>
+        <v>128577885</v>
       </c>
       <c r="B59" t="n">
-        <v>92199</v>
+        <v>90981</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1527</v>
+        <v>3286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>660556</v>
+        <v>660621</v>
       </c>
       <c r="R59" t="n">
-        <v>6642090</v>
+        <v>6642044</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7246,32 +7246,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128577853</v>
+        <v>128577882</v>
       </c>
       <c r="B60" t="n">
-        <v>87004</v>
+        <v>95965</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3739</v>
+        <v>2671</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>660617</v>
+        <v>660709</v>
       </c>
       <c r="R60" t="n">
-        <v>6642063</v>
+        <v>6642203</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7343,32 +7343,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128577817</v>
+        <v>128577853</v>
       </c>
       <c r="B61" t="n">
-        <v>92807</v>
+        <v>87004</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4363</v>
+        <v>3739</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>660620</v>
+        <v>660617</v>
       </c>
       <c r="R61" t="n">
-        <v>6642049</v>
+        <v>6642063</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7537,10 +7537,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128577882</v>
+        <v>128577817</v>
       </c>
       <c r="B63" t="n">
-        <v>95965</v>
+        <v>92807</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7548,21 +7548,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2671</v>
+        <v>4363</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>660709</v>
+        <v>660620</v>
       </c>
       <c r="R63" t="n">
-        <v>6642203</v>
+        <v>6642049</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128577871</v>
+        <v>128577886</v>
       </c>
       <c r="B73" t="n">
-        <v>95965</v>
+        <v>92847</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8518,21 +8518,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8542,10 +8542,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>660627</v>
+        <v>660635</v>
       </c>
       <c r="R73" t="n">
-        <v>6642017</v>
+        <v>6641930</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8604,10 +8604,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128577894</v>
+        <v>128577871</v>
       </c>
       <c r="B74" t="n">
-        <v>92847</v>
+        <v>95965</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8615,21 +8615,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>660638</v>
+        <v>660627</v>
       </c>
       <c r="R74" t="n">
-        <v>6641974</v>
+        <v>6642017</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8701,7 +8701,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128577886</v>
+        <v>128577894</v>
       </c>
       <c r="B75" t="n">
         <v>92847</v>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>660635</v>
+        <v>660638</v>
       </c>
       <c r="R75" t="n">
-        <v>6641930</v>
+        <v>6641974</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -9288,10 +9288,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128577880</v>
+        <v>128577896</v>
       </c>
       <c r="B81" t="n">
-        <v>95965</v>
+        <v>92847</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9299,21 +9299,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>660697</v>
+        <v>660619</v>
       </c>
       <c r="R81" t="n">
-        <v>6642175</v>
+        <v>6642007</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -9385,10 +9385,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128577896</v>
+        <v>128577880</v>
       </c>
       <c r="B82" t="n">
-        <v>92847</v>
+        <v>95965</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9396,21 +9396,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>660619</v>
+        <v>660697</v>
       </c>
       <c r="R82" t="n">
-        <v>6642007</v>
+        <v>6642175</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9579,10 +9579,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128577877</v>
+        <v>128577898</v>
       </c>
       <c r="B84" t="n">
-        <v>95965</v>
+        <v>92847</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9590,21 +9590,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9614,10 +9614,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>660666</v>
+        <v>660597</v>
       </c>
       <c r="R84" t="n">
-        <v>6642164</v>
+        <v>6642016</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -9676,10 +9676,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128577898</v>
+        <v>128577877</v>
       </c>
       <c r="B85" t="n">
-        <v>92847</v>
+        <v>95965</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9687,21 +9687,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>660597</v>
+        <v>660666</v>
       </c>
       <c r="R85" t="n">
-        <v>6642016</v>
+        <v>6642164</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -6570,7 +6570,7 @@
         <v>128577897</v>
       </c>
       <c r="B53" t="n">
-        <v>92847</v>
+        <v>92855</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>128577820</v>
       </c>
       <c r="B54" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>128577858</v>
       </c>
       <c r="B55" t="n">
-        <v>91073</v>
+        <v>91079</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>128577905</v>
       </c>
       <c r="B56" t="n">
-        <v>92191</v>
+        <v>92199</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6955,32 +6955,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128577843</v>
+        <v>128577885</v>
       </c>
       <c r="B57" t="n">
-        <v>92199</v>
+        <v>90987</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1527</v>
+        <v>3286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>660556</v>
+        <v>660621</v>
       </c>
       <c r="R57" t="n">
-        <v>6642090</v>
+        <v>6642044</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7052,32 +7052,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128577892</v>
+        <v>128577843</v>
       </c>
       <c r="B58" t="n">
-        <v>92847</v>
+        <v>92207</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5964</v>
+        <v>1527</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7087,10 +7087,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>660554</v>
+        <v>660556</v>
       </c>
       <c r="R58" t="n">
-        <v>6642138</v>
+        <v>6642090</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7149,32 +7149,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128577885</v>
+        <v>128577892</v>
       </c>
       <c r="B59" t="n">
-        <v>90981</v>
+        <v>92855</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3286</v>
+        <v>5964</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>660621</v>
+        <v>660554</v>
       </c>
       <c r="R59" t="n">
-        <v>6642044</v>
+        <v>6642138</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7249,7 +7249,7 @@
         <v>128577882</v>
       </c>
       <c r="B60" t="n">
-        <v>95965</v>
+        <v>95973</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>128577853</v>
       </c>
       <c r="B61" t="n">
-        <v>87004</v>
+        <v>87010</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>128577816</v>
       </c>
       <c r="B62" t="n">
-        <v>87004</v>
+        <v>87010</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>128577817</v>
       </c>
       <c r="B63" t="n">
-        <v>92807</v>
+        <v>92815</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7634,10 +7634,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128577833</v>
+        <v>128577884</v>
       </c>
       <c r="B64" t="n">
-        <v>100745</v>
+        <v>95973</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7645,21 +7645,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222771</v>
+        <v>2671</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7669,10 +7669,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>660698</v>
+        <v>660554</v>
       </c>
       <c r="R64" t="n">
-        <v>6642170</v>
+        <v>6642138</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7731,10 +7731,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128577884</v>
+        <v>128577878</v>
       </c>
       <c r="B65" t="n">
-        <v>95965</v>
+        <v>95973</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>660554</v>
+        <v>660701</v>
       </c>
       <c r="R65" t="n">
-        <v>6642138</v>
+        <v>6642183</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7828,10 +7828,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128577878</v>
+        <v>128577881</v>
       </c>
       <c r="B66" t="n">
-        <v>95965</v>
+        <v>95973</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>660701</v>
+        <v>660699</v>
       </c>
       <c r="R66" t="n">
-        <v>6642183</v>
+        <v>6642205</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7925,10 +7925,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128577881</v>
+        <v>128577889</v>
       </c>
       <c r="B67" t="n">
-        <v>95965</v>
+        <v>92855</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7936,21 +7936,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>660699</v>
+        <v>660614</v>
       </c>
       <c r="R67" t="n">
-        <v>6642205</v>
+        <v>6642042</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -8022,10 +8022,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128577889</v>
+        <v>128577833</v>
       </c>
       <c r="B68" t="n">
-        <v>92847</v>
+        <v>100753</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8033,21 +8033,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8057,10 +8057,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>660614</v>
+        <v>660698</v>
       </c>
       <c r="R68" t="n">
-        <v>6642042</v>
+        <v>6642170</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8122,7 +8122,7 @@
         <v>128577828</v>
       </c>
       <c r="B69" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>128577904</v>
       </c>
       <c r="B70" t="n">
-        <v>92150</v>
+        <v>92158</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>128577824</v>
       </c>
       <c r="B71" t="n">
-        <v>92456</v>
+        <v>92464</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8410,10 +8410,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128577908</v>
+        <v>128577871</v>
       </c>
       <c r="B72" t="n">
-        <v>90793</v>
+        <v>95973</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8421,21 +8421,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>749</v>
+        <v>2671</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Alsopp</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Gyrodon lividus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Bull.:Fr.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8445,10 +8445,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>660712</v>
+        <v>660627</v>
       </c>
       <c r="R72" t="n">
-        <v>6642212</v>
+        <v>6642017</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128577886</v>
+        <v>128577894</v>
       </c>
       <c r="B73" t="n">
-        <v>92847</v>
+        <v>92855</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8542,10 +8542,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>660635</v>
+        <v>660638</v>
       </c>
       <c r="R73" t="n">
-        <v>6641930</v>
+        <v>6641974</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8604,10 +8604,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128577871</v>
+        <v>128577886</v>
       </c>
       <c r="B74" t="n">
-        <v>95965</v>
+        <v>92855</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8615,21 +8615,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>660627</v>
+        <v>660635</v>
       </c>
       <c r="R74" t="n">
-        <v>6642017</v>
+        <v>6641930</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8701,10 +8701,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128577894</v>
+        <v>128577908</v>
       </c>
       <c r="B75" t="n">
-        <v>92847</v>
+        <v>90799</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8712,21 +8712,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5964</v>
+        <v>749</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Alsopp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Gyrodon lividus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Bull.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>660638</v>
+        <v>660712</v>
       </c>
       <c r="R75" t="n">
-        <v>6641974</v>
+        <v>6642212</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8801,7 +8801,7 @@
         <v>128577825</v>
       </c>
       <c r="B76" t="n">
-        <v>92456</v>
+        <v>92464</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>128577893</v>
       </c>
       <c r="B77" t="n">
-        <v>92847</v>
+        <v>92855</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>128577875</v>
       </c>
       <c r="B78" t="n">
-        <v>95965</v>
+        <v>95973</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9089,10 +9089,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128577818</v>
+        <v>128577888</v>
       </c>
       <c r="B79" t="n">
-        <v>92807</v>
+        <v>92855</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9100,21 +9100,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4363</v>
+        <v>5964</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>660559</v>
+        <v>660615</v>
       </c>
       <c r="R79" t="n">
-        <v>6642143</v>
+        <v>6642026</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -9160,11 +9160,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-19</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>20 fruktkroppar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9191,10 +9186,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128577888</v>
+        <v>128577818</v>
       </c>
       <c r="B80" t="n">
-        <v>92847</v>
+        <v>92815</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9202,21 +9197,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5964</v>
+        <v>4363</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9226,10 +9221,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>660615</v>
+        <v>660559</v>
       </c>
       <c r="R80" t="n">
-        <v>6642026</v>
+        <v>6642143</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -9262,6 +9257,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>20 fruktkroppar</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9288,10 +9288,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128577896</v>
+        <v>128577880</v>
       </c>
       <c r="B81" t="n">
-        <v>92847</v>
+        <v>95973</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9299,21 +9299,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>660619</v>
+        <v>660697</v>
       </c>
       <c r="R81" t="n">
-        <v>6642007</v>
+        <v>6642175</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -9385,10 +9385,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128577880</v>
+        <v>128577823</v>
       </c>
       <c r="B82" t="n">
-        <v>95965</v>
+        <v>92464</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9396,21 +9396,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2671</v>
+        <v>4769</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>660697</v>
+        <v>660679</v>
       </c>
       <c r="R82" t="n">
-        <v>6642175</v>
+        <v>6642181</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9482,10 +9482,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128577823</v>
+        <v>128577896</v>
       </c>
       <c r="B83" t="n">
-        <v>92456</v>
+        <v>92855</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9493,21 +9493,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9517,10 +9517,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>660679</v>
+        <v>660619</v>
       </c>
       <c r="R83" t="n">
-        <v>6642181</v>
+        <v>6642007</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9579,10 +9579,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128577898</v>
+        <v>128577877</v>
       </c>
       <c r="B84" t="n">
-        <v>92847</v>
+        <v>95973</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9590,21 +9590,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9614,10 +9614,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>660597</v>
+        <v>660666</v>
       </c>
       <c r="R84" t="n">
-        <v>6642016</v>
+        <v>6642164</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -9676,10 +9676,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128577877</v>
+        <v>128577898</v>
       </c>
       <c r="B85" t="n">
-        <v>95965</v>
+        <v>92855</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9687,21 +9687,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2671</v>
+        <v>5964</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>660666</v>
+        <v>660597</v>
       </c>
       <c r="R85" t="n">
-        <v>6642164</v>
+        <v>6642016</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -9776,7 +9776,7 @@
         <v>128577827</v>
       </c>
       <c r="B86" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>128577891</v>
       </c>
       <c r="B87" t="n">
-        <v>92847</v>
+        <v>92855</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>128577890</v>
       </c>
       <c r="B88" t="n">
-        <v>92847</v>
+        <v>92855</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -8507,10 +8507,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128577894</v>
+        <v>128577908</v>
       </c>
       <c r="B73" t="n">
-        <v>92855</v>
+        <v>90799</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8518,21 +8518,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5964</v>
+        <v>749</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Alsopp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Gyrodon lividus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Bull.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8542,10 +8542,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>660638</v>
+        <v>660712</v>
       </c>
       <c r="R73" t="n">
-        <v>6641974</v>
+        <v>6642212</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8604,7 +8604,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128577886</v>
+        <v>128577894</v>
       </c>
       <c r="B74" t="n">
         <v>92855</v>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>660635</v>
+        <v>660638</v>
       </c>
       <c r="R74" t="n">
-        <v>6641930</v>
+        <v>6641974</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8701,10 +8701,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128577908</v>
+        <v>128577886</v>
       </c>
       <c r="B75" t="n">
-        <v>90799</v>
+        <v>92855</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8712,21 +8712,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>749</v>
+        <v>5964</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Alsopp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Gyrodon lividus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Bull.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>660712</v>
+        <v>660635</v>
       </c>
       <c r="R75" t="n">
-        <v>6642212</v>
+        <v>6641930</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -9089,10 +9089,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128577888</v>
+        <v>128577818</v>
       </c>
       <c r="B79" t="n">
-        <v>92855</v>
+        <v>92815</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9100,21 +9100,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5964</v>
+        <v>4363</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>660615</v>
+        <v>660559</v>
       </c>
       <c r="R79" t="n">
-        <v>6642026</v>
+        <v>6642143</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -9160,6 +9160,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>20 fruktkroppar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9186,10 +9191,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128577818</v>
+        <v>128577888</v>
       </c>
       <c r="B80" t="n">
-        <v>92815</v>
+        <v>92855</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9197,21 +9202,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4363</v>
+        <v>5964</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9221,10 +9226,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>660559</v>
+        <v>660615</v>
       </c>
       <c r="R80" t="n">
-        <v>6642143</v>
+        <v>6642026</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -9257,11 +9262,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-19</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>20 fruktkroppar</t>
         </is>
       </c>
       <c r="AD80" t="b">

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10062,6 +10062,374 @@
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>129792608</v>
+      </c>
+      <c r="B89" t="n">
+        <v>92284</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>898</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Näset, Upl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>660674</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6642137</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Återfynd. Avverkningsanmäld skog.</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>129792613</v>
+      </c>
+      <c r="B90" t="n">
+        <v>92046</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Näset, Upl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>660674</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6642137</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>129792574</v>
+      </c>
+      <c r="B91" t="n">
+        <v>91817</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Näset, Upl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>660661</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6642155</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -10067,7 +10067,7 @@
         <v>129792608</v>
       </c>
       <c r="B89" t="n">
-        <v>92284</v>
+        <v>92288</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>129792613</v>
       </c>
       <c r="B90" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>129792574</v>
       </c>
       <c r="B91" t="n">
-        <v>91817</v>
+        <v>91821</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -10067,7 +10067,7 @@
         <v>129792608</v>
       </c>
       <c r="B89" t="n">
-        <v>92288</v>
+        <v>92290</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>129792613</v>
       </c>
       <c r="B90" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>129792574</v>
       </c>
       <c r="B91" t="n">
-        <v>91821</v>
+        <v>91823</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -10067,7 +10067,7 @@
         <v>129792608</v>
       </c>
       <c r="B89" t="n">
-        <v>92290</v>
+        <v>92293</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>129792613</v>
       </c>
       <c r="B90" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>129792574</v>
       </c>
       <c r="B91" t="n">
-        <v>91823</v>
+        <v>91826</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -10067,7 +10067,7 @@
         <v>129792608</v>
       </c>
       <c r="B89" t="n">
-        <v>92293</v>
+        <v>92296</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>129792613</v>
       </c>
       <c r="B90" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>129792574</v>
       </c>
       <c r="B91" t="n">
-        <v>91826</v>
+        <v>91829</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -10067,7 +10067,7 @@
         <v>129792608</v>
       </c>
       <c r="B89" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>129792613</v>
       </c>
       <c r="B90" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>129792574</v>
       </c>
       <c r="B91" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -10067,7 +10067,7 @@
         <v>129792608</v>
       </c>
       <c r="B89" t="n">
-        <v>92297</v>
+        <v>92314</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>129792613</v>
       </c>
       <c r="B90" t="n">
-        <v>92059</v>
+        <v>92076</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>129792574</v>
       </c>
       <c r="B91" t="n">
-        <v>91830</v>
+        <v>91847</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 38208-2025 artfynd.xlsx
+++ b/artfynd/A 38208-2025 artfynd.xlsx
@@ -10067,7 +10067,7 @@
         <v>129792608</v>
       </c>
       <c r="B89" t="n">
-        <v>92330</v>
+        <v>92332</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>129792613</v>
       </c>
       <c r="B90" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>129792574</v>
       </c>
       <c r="B91" t="n">
-        <v>91863</v>
+        <v>91865</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
